--- a/xlsx/dre/DRE_04_2026.xlsx
+++ b/xlsx/dre/DRE_04_2026.xlsx
@@ -1196,6 +1196,18 @@
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>R$  1.333,58</t>
+  </si>
+  <si>
+    <t>06/02/26</t>
+  </si>
+  <si>
     <t>R$  404,67</t>
   </si>
   <si>
@@ -1205,24 +1217,12 @@
     <t>R$  424,52</t>
   </si>
   <si>
-    <t>01/06/26</t>
+    <t>R$  401,23</t>
   </si>
   <si>
     <t>R$  272,80</t>
   </si>
   <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>R$  401,23</t>
-  </si>
-  <si>
-    <t>R$  1.333,58</t>
-  </si>
-  <si>
-    <t>06/02/26</t>
-  </si>
-  <si>
     <t>23801/1</t>
   </si>
   <si>
@@ -1325,12 +1325,12 @@
     <t>DSR abr26/1</t>
   </si>
   <si>
+    <t>R$  549,59</t>
+  </si>
+  <si>
     <t>R$  736,46</t>
   </si>
   <si>
-    <t>R$  549,59</t>
-  </si>
-  <si>
     <t>4.03.03 GASTOS GERAIS COM VENDAS</t>
   </si>
   <si>
@@ -1547,21 +1547,21 @@
     <t>R$ 277,65</t>
   </si>
   <si>
+    <t>5/2</t>
+  </si>
+  <si>
+    <t>R$  92,55</t>
+  </si>
+  <si>
+    <t>Mercado Livre</t>
+  </si>
+  <si>
+    <t>5/3</t>
+  </si>
+  <si>
     <t>5/1</t>
   </si>
   <si>
-    <t>R$  92,55</t>
-  </si>
-  <si>
-    <t>Mercado Livre</t>
-  </si>
-  <si>
-    <t>5/3</t>
-  </si>
-  <si>
-    <t>5/2</t>
-  </si>
-  <si>
     <t>4.03.03.02.05 Assistência técnica - custo loja</t>
   </si>
   <si>
@@ -1592,24 +1592,24 @@
     <t>4.03.03.08.01 Brindes para clientes (CV)</t>
   </si>
   <si>
+    <t>2/2</t>
+  </si>
+  <si>
+    <t>Licoretto Bebidas</t>
+  </si>
+  <si>
+    <t>R$  79,98</t>
+  </si>
+  <si>
+    <t>Brindes clientes</t>
+  </si>
+  <si>
+    <t>2/1</t>
+  </si>
+  <si>
     <t>2/3</t>
   </si>
   <si>
-    <t>Licoretto Bebidas</t>
-  </si>
-  <si>
-    <t>R$  79,98</t>
-  </si>
-  <si>
-    <t>Brindes clientes</t>
-  </si>
-  <si>
-    <t>2/1</t>
-  </si>
-  <si>
-    <t>2/2</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -1634,6 +1634,30 @@
     <t>12/4</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>1/2</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>03/02/26</t>
+  </si>
+  <si>
+    <t>Facebook 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -1643,30 +1667,6 @@
     <t>Google 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
-    <t>1/2</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>03/02/26</t>
-  </si>
-  <si>
-    <t>Facebook 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -1709,135 +1709,135 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>658/1</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>07/05/26</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.422,07</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
     <t>Rubens - Pagamento 2026</t>
   </si>
   <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>19/04/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>627/1</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos</t>
+  </si>
+  <si>
+    <t>R$  566,67</t>
+  </si>
+  <si>
+    <t>24/04/26</t>
+  </si>
+  <si>
+    <t>17 dias</t>
+  </si>
+  <si>
+    <t>659/1</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  1.287,09</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.795,57</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>616/1</t>
+  </si>
+  <si>
+    <t>R$  241,20</t>
+  </si>
+  <si>
+    <t>Reajuste dissidio</t>
+  </si>
+  <si>
+    <t>R$  2.219,85</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
+  </si>
+  <si>
     <t>Carina Pereira</t>
   </si>
   <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
     <t>Carina - Pagamento 2026</t>
   </si>
   <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>19/04/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>658/1</t>
-  </si>
-  <si>
-    <t>EFRAIM RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>07/05/26</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.422,07</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.795,57</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
-    <t>659/1</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  1.287,09</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>627/1</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos</t>
-  </si>
-  <si>
-    <t>R$  566,67</t>
-  </si>
-  <si>
-    <t>24/04/26</t>
-  </si>
-  <si>
-    <t>17 dias</t>
-  </si>
-  <si>
-    <t>616/1</t>
-  </si>
-  <si>
-    <t>R$  241,20</t>
-  </si>
-  <si>
-    <t>Reajuste dissidio</t>
-  </si>
-  <si>
-    <t>R$  2.219,85</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -1904,19 +1904,19 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT abr26/4</t>
+  </si>
+  <si>
+    <t>R$  411,36</t>
+  </si>
+  <si>
+    <t>31/03/26</t>
+  </si>
+  <si>
     <t>VT abr26/1</t>
   </si>
   <si>
     <t>R$  290,65</t>
-  </si>
-  <si>
-    <t>31/03/26</t>
-  </si>
-  <si>
-    <t>VT abr26/4</t>
-  </si>
-  <si>
-    <t>R$  411,36</t>
   </si>
   <si>
     <t>4.04.01.07 Uniformes e crachás</t>
@@ -2098,6 +2098,18 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
+    <t>646/1</t>
+  </si>
+  <si>
+    <t>Oxxo</t>
+  </si>
+  <si>
+    <t>R$  90,07</t>
+  </si>
+  <si>
+    <t>Cafés loja</t>
+  </si>
+  <si>
     <t>644/1</t>
   </si>
   <si>
@@ -2117,6 +2129,15 @@
   </si>
   <si>
     <t>Envelope</t>
+  </si>
+  <si>
+    <t>648/1</t>
+  </si>
+  <si>
+    <t>Chaveiro Rouxinol</t>
+  </si>
+  <si>
+    <t>R$  90,00</t>
   </si>
   <si>
     <t>643/1</t>
@@ -2135,27 +2156,6 @@
 </t>
   </si>
   <si>
-    <t>646/1</t>
-  </si>
-  <si>
-    <t>Oxxo</t>
-  </si>
-  <si>
-    <t>R$  90,07</t>
-  </si>
-  <si>
-    <t>Cafés loja</t>
-  </si>
-  <si>
-    <t>648/1</t>
-  </si>
-  <si>
-    <t>Chaveiro Rouxinol</t>
-  </si>
-  <si>
-    <t>R$  90,00</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2237,6 +2237,12 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>3/3</t>
   </si>
   <si>
@@ -2247,12 +2253,6 @@
   </si>
   <si>
     <t>Promob 2026/2</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -11902,7 +11902,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F175" t="s">
         <v>183</v>
@@ -11914,13 +11914,13 @@
         <v>388</v>
       </c>
       <c r="I175" t="s">
+        <v>370</v>
+      </c>
+      <c r="J175" t="s">
         <v>389</v>
       </c>
-      <c r="J175" t="s">
-        <v>390</v>
-      </c>
       <c r="K175" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -11932,10 +11932,10 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>209</v>
+        <v>120</v>
       </c>
       <c r="P175" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="Q175" t="s">
         <v>47</v>
@@ -11958,7 +11958,7 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F176" t="s">
         <v>183</v>
@@ -11970,13 +11970,13 @@
         <v>388</v>
       </c>
       <c r="I176" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="J176" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K176" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -11988,10 +11988,10 @@
         <v>47</v>
       </c>
       <c r="O176" t="s">
-        <v>287</v>
+        <v>104</v>
       </c>
       <c r="P176" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="Q176" t="s">
         <v>47</v>
@@ -12014,7 +12014,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="F177" t="s">
         <v>183</v>
@@ -12026,13 +12026,13 @@
         <v>388</v>
       </c>
       <c r="I177" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="J177" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K177" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -12044,10 +12044,10 @@
         <v>47</v>
       </c>
       <c r="O177" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="Q177" t="s">
         <v>47</v>
@@ -12070,7 +12070,7 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F178" t="s">
         <v>183</v>
@@ -12079,16 +12079,16 @@
         <v>41</v>
       </c>
       <c r="H178" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I178" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="J178" t="s">
         <v>392</v>
       </c>
       <c r="K178" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -12100,10 +12100,10 @@
         <v>47</v>
       </c>
       <c r="O178" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="P178" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="Q178" t="s">
         <v>47</v>
@@ -12126,7 +12126,7 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F179" t="s">
         <v>183</v>
@@ -12138,13 +12138,13 @@
         <v>388</v>
       </c>
       <c r="I179" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="J179" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K179" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12156,10 +12156,10 @@
         <v>47</v>
       </c>
       <c r="O179" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P179" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="Q179" t="s">
         <v>47</v>
@@ -12182,7 +12182,7 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F180" t="s">
         <v>183</v>
@@ -12194,13 +12194,13 @@
         <v>388</v>
       </c>
       <c r="I180" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J180" t="s">
-        <v>129</v>
+        <v>394</v>
       </c>
       <c r="K180" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12212,10 +12212,10 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>72</v>
+        <v>287</v>
       </c>
       <c r="P180" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q180" t="s">
         <v>47</v>
@@ -12247,10 +12247,10 @@
         <v>41</v>
       </c>
       <c r="H181" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="I181" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J181" t="s">
         <v>129</v>
@@ -12271,7 +12271,7 @@
         <v>77</v>
       </c>
       <c r="P181" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q181" t="s">
         <v>47</v>
@@ -12294,7 +12294,7 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F182" t="s">
         <v>183</v>
@@ -12303,16 +12303,16 @@
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="I182" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J182" t="s">
-        <v>397</v>
+        <v>129</v>
       </c>
       <c r="K182" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12324,10 +12324,10 @@
         <v>47</v>
       </c>
       <c r="O182" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="P182" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q182" t="s">
         <v>47</v>
@@ -12359,7 +12359,7 @@
         <v>41</v>
       </c>
       <c r="H183" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="I183" t="s">
         <v>399</v>
@@ -12813,7 +12813,7 @@
         <v>417</v>
       </c>
       <c r="J191" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K191" t="s">
         <v>125</v>
@@ -12869,7 +12869,7 @@
         <v>415</v>
       </c>
       <c r="J192" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K192" t="s">
         <v>125</v>
@@ -13311,16 +13311,16 @@
         <v>41</v>
       </c>
       <c r="H200" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I200" t="s">
         <v>432</v>
       </c>
       <c r="J200" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="K200" t="s">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="L200" t="s">
         <v>34</v>
@@ -13367,16 +13367,16 @@
         <v>41</v>
       </c>
       <c r="H201" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="I201" t="s">
         <v>433</v>
       </c>
       <c r="J201" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K201" t="s">
-        <v>89</v>
+        <v>240</v>
       </c>
       <c r="L201" t="s">
         <v>34</v>
@@ -15206,7 +15206,7 @@
         <v>34</v>
       </c>
       <c r="E234" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F234" t="s">
         <v>40</v>
@@ -15221,10 +15221,10 @@
         <v>515</v>
       </c>
       <c r="J234" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="K234" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="L234" t="s">
         <v>34</v>
@@ -15236,7 +15236,7 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="P234" t="s">
         <v>515</v>
@@ -15262,7 +15262,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F235" t="s">
         <v>40</v>
@@ -15277,10 +15277,10 @@
         <v>515</v>
       </c>
       <c r="J235" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="K235" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15292,7 +15292,7 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="P235" t="s">
         <v>515</v>
@@ -15318,7 +15318,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="F236" t="s">
         <v>40</v>
@@ -15333,10 +15333,10 @@
         <v>515</v>
       </c>
       <c r="J236" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K236" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15348,7 +15348,7 @@
         <v>47</v>
       </c>
       <c r="O236" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="P236" t="s">
         <v>515</v>
@@ -15374,7 +15374,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F237" t="s">
         <v>40</v>
@@ -15389,10 +15389,10 @@
         <v>515</v>
       </c>
       <c r="J237" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K237" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L237" t="s">
         <v>34</v>
@@ -15404,7 +15404,7 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P237" t="s">
         <v>515</v>
@@ -15430,7 +15430,7 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="F238" t="s">
         <v>40</v>
@@ -15442,13 +15442,13 @@
         <v>514</v>
       </c>
       <c r="I238" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J238" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="K238" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15460,10 +15460,10 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="P238" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="Q238" t="s">
         <v>47</v>
@@ -15486,7 +15486,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F239" t="s">
         <v>40</v>
@@ -15501,10 +15501,10 @@
         <v>515</v>
       </c>
       <c r="J239" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="K239" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15516,7 +15516,7 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="P239" t="s">
         <v>515</v>
@@ -15542,7 +15542,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F240" t="s">
         <v>40</v>
@@ -15554,13 +15554,13 @@
         <v>514</v>
       </c>
       <c r="I240" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J240" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K240" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15572,10 +15572,10 @@
         <v>47</v>
       </c>
       <c r="O240" t="s">
-        <v>287</v>
+        <v>96</v>
       </c>
       <c r="P240" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q240" t="s">
         <v>47</v>
@@ -15598,10 +15598,10 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F241" t="s">
-        <v>40</v>
+        <v>517</v>
       </c>
       <c r="G241" t="s">
         <v>41</v>
@@ -15613,10 +15613,10 @@
         <v>515</v>
       </c>
       <c r="J241" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="K241" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15628,13 +15628,13 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="P241" t="s">
-        <v>515</v>
+        <v>34</v>
       </c>
       <c r="Q241" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R241" t="s">
         <v>34</v>
@@ -15710,10 +15710,10 @@
         <v>34</v>
       </c>
       <c r="E243" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F243" t="s">
-        <v>517</v>
+        <v>40</v>
       </c>
       <c r="G243" t="s">
         <v>41</v>
@@ -15725,10 +15725,10 @@
         <v>515</v>
       </c>
       <c r="J243" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="K243" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="L243" t="s">
         <v>34</v>
@@ -15740,13 +15740,13 @@
         <v>47</v>
       </c>
       <c r="O243" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="P243" t="s">
-        <v>34</v>
+        <v>515</v>
       </c>
       <c r="Q243" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R243" t="s">
         <v>34</v>
@@ -16117,13 +16117,13 @@
         <v>536</v>
       </c>
       <c r="J250" t="s">
-        <v>246</v>
+        <v>537</v>
       </c>
       <c r="K250" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="L250" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M250" t="s">
         <v>529</v>
@@ -16158,7 +16158,7 @@
         <v>34</v>
       </c>
       <c r="E251" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="F251" t="s">
         <v>40</v>
@@ -16167,19 +16167,19 @@
         <v>41</v>
       </c>
       <c r="H251" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I251" t="s">
-        <v>539</v>
+        <v>94</v>
       </c>
       <c r="J251" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K251" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="L251" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M251" t="s">
         <v>529</v>
@@ -16191,7 +16191,7 @@
         <v>48</v>
       </c>
       <c r="P251" t="s">
-        <v>539</v>
+        <v>94</v>
       </c>
       <c r="Q251" t="s">
         <v>47</v>
@@ -16214,7 +16214,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F252" t="s">
         <v>40</v>
@@ -16226,13 +16226,13 @@
         <v>543</v>
       </c>
       <c r="I252" t="s">
-        <v>94</v>
+        <v>544</v>
       </c>
       <c r="J252" t="s">
-        <v>544</v>
+        <v>246</v>
       </c>
       <c r="K252" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
       <c r="L252" t="s">
         <v>545</v>
@@ -16247,7 +16247,7 @@
         <v>48</v>
       </c>
       <c r="P252" t="s">
-        <v>94</v>
+        <v>544</v>
       </c>
       <c r="Q252" t="s">
         <v>47</v>
@@ -16453,7 +16453,7 @@
         <v>553</v>
       </c>
       <c r="J256" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K256" t="s">
         <v>247</v>
@@ -16606,28 +16606,28 @@
         <v>33</v>
       </c>
       <c r="E259" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="F259" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G259" t="s">
         <v>41</v>
       </c>
       <c r="H259" t="s">
-        <v>394</v>
+        <v>561</v>
       </c>
       <c r="I259" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="J259" t="s">
-        <v>246</v>
+        <v>563</v>
       </c>
       <c r="K259" t="s">
-        <v>247</v>
+        <v>124</v>
       </c>
       <c r="L259" t="s">
-        <v>560</v>
+        <v>34</v>
       </c>
       <c r="M259" t="s">
         <v>559</v>
@@ -16639,7 +16639,7 @@
         <v>48</v>
       </c>
       <c r="P259" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="Q259" t="s">
         <v>47</v>
@@ -16671,19 +16671,19 @@
         <v>41</v>
       </c>
       <c r="H260" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="I260" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="J260" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K260" t="s">
         <v>247</v>
       </c>
       <c r="L260" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M260" t="s">
         <v>559</v>
@@ -16695,7 +16695,7 @@
         <v>48</v>
       </c>
       <c r="P260" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="Q260" t="s">
         <v>47</v>
@@ -16730,16 +16730,16 @@
         <v>372</v>
       </c>
       <c r="I261" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="J261" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K261" t="s">
         <v>247</v>
       </c>
       <c r="L261" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M261" t="s">
         <v>559</v>
@@ -16751,7 +16751,7 @@
         <v>48</v>
       </c>
       <c r="P261" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="Q261" t="s">
         <v>47</v>
@@ -16774,7 +16774,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>136</v>
+        <v>534</v>
       </c>
       <c r="F262" t="s">
         <v>40</v>
@@ -16783,19 +16783,19 @@
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>567</v>
+        <v>390</v>
       </c>
       <c r="I262" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="J262" t="s">
-        <v>565</v>
+        <v>246</v>
       </c>
       <c r="K262" t="s">
-        <v>568</v>
+        <v>247</v>
       </c>
       <c r="L262" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M262" t="s">
         <v>559</v>
@@ -16807,7 +16807,7 @@
         <v>48</v>
       </c>
       <c r="P262" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="Q262" t="s">
         <v>47</v>
@@ -16830,28 +16830,28 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>570</v>
+        <v>136</v>
       </c>
       <c r="F263" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G263" t="s">
         <v>41</v>
       </c>
       <c r="H263" t="s">
+        <v>388</v>
+      </c>
+      <c r="I263" t="s">
+        <v>553</v>
+      </c>
+      <c r="J263" t="s">
         <v>571</v>
       </c>
-      <c r="I263" t="s">
+      <c r="K263" t="s">
+        <v>247</v>
+      </c>
+      <c r="L263" t="s">
         <v>572</v>
-      </c>
-      <c r="J263" t="s">
-        <v>573</v>
-      </c>
-      <c r="K263" t="s">
-        <v>124</v>
-      </c>
-      <c r="L263" t="s">
-        <v>34</v>
       </c>
       <c r="M263" t="s">
         <v>559</v>
@@ -16863,7 +16863,7 @@
         <v>48</v>
       </c>
       <c r="P263" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="Q263" t="s">
         <v>47</v>
@@ -16895,13 +16895,13 @@
         <v>41</v>
       </c>
       <c r="H264" t="s">
+        <v>573</v>
+      </c>
+      <c r="I264" t="s">
         <v>574</v>
       </c>
-      <c r="I264" t="s">
-        <v>553</v>
-      </c>
       <c r="J264" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K264" t="s">
         <v>247</v>
@@ -16919,7 +16919,7 @@
         <v>48</v>
       </c>
       <c r="P264" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="Q264" t="s">
         <v>47</v>
@@ -16942,7 +16942,7 @@
         <v>34</v>
       </c>
       <c r="E265" t="s">
-        <v>534</v>
+        <v>136</v>
       </c>
       <c r="F265" t="s">
         <v>40</v>
@@ -16954,13 +16954,13 @@
         <v>576</v>
       </c>
       <c r="I265" t="s">
+        <v>567</v>
+      </c>
+      <c r="J265" t="s">
+        <v>568</v>
+      </c>
+      <c r="K265" t="s">
         <v>577</v>
-      </c>
-      <c r="J265" t="s">
-        <v>540</v>
-      </c>
-      <c r="K265" t="s">
-        <v>247</v>
       </c>
       <c r="L265" t="s">
         <v>578</v>
@@ -16975,7 +16975,7 @@
         <v>48</v>
       </c>
       <c r="P265" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="Q265" t="s">
         <v>47</v>
@@ -16998,28 +16998,28 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>534</v>
+        <v>579</v>
       </c>
       <c r="F266" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G266" t="s">
         <v>41</v>
       </c>
       <c r="H266" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I266" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J266" t="s">
-        <v>540</v>
+        <v>582</v>
       </c>
       <c r="K266" t="s">
-        <v>247</v>
+        <v>582</v>
       </c>
       <c r="L266" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M266" t="s">
         <v>559</v>
@@ -17031,7 +17031,7 @@
         <v>48</v>
       </c>
       <c r="P266" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Q266" t="s">
         <v>47</v>
@@ -17054,28 +17054,28 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>534</v>
+        <v>584</v>
       </c>
       <c r="F267" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G267" t="s">
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="I267" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J267" t="s">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="K267" t="s">
-        <v>247</v>
+        <v>119</v>
       </c>
       <c r="L267" t="s">
-        <v>584</v>
+        <v>34</v>
       </c>
       <c r="M267" t="s">
         <v>559</v>
@@ -17087,7 +17087,7 @@
         <v>48</v>
       </c>
       <c r="P267" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="Q267" t="s">
         <v>47</v>
@@ -17110,7 +17110,7 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>136</v>
+        <v>534</v>
       </c>
       <c r="F268" t="s">
         <v>40</v>
@@ -17119,19 +17119,19 @@
         <v>41</v>
       </c>
       <c r="H268" t="s">
-        <v>388</v>
+        <v>587</v>
       </c>
       <c r="I268" t="s">
         <v>553</v>
       </c>
       <c r="J268" t="s">
-        <v>585</v>
+        <v>537</v>
       </c>
       <c r="K268" t="s">
         <v>247</v>
       </c>
       <c r="L268" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M268" t="s">
         <v>559</v>
@@ -17166,28 +17166,28 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>587</v>
+        <v>534</v>
       </c>
       <c r="F269" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G269" t="s">
         <v>41</v>
       </c>
       <c r="H269" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I269" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J269" t="s">
-        <v>573</v>
+        <v>537</v>
       </c>
       <c r="K269" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
       <c r="L269" t="s">
-        <v>34</v>
+        <v>591</v>
       </c>
       <c r="M269" t="s">
         <v>559</v>
@@ -17199,7 +17199,7 @@
         <v>48</v>
       </c>
       <c r="P269" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Q269" t="s">
         <v>47</v>
@@ -17231,19 +17231,19 @@
         <v>41</v>
       </c>
       <c r="H270" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="I270" t="s">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="J270" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K270" t="s">
         <v>247</v>
       </c>
       <c r="L270" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M270" t="s">
         <v>559</v>
@@ -17255,7 +17255,7 @@
         <v>48</v>
       </c>
       <c r="P270" t="s">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="Q270" t="s">
         <v>47</v>
@@ -17278,7 +17278,7 @@
         <v>34</v>
       </c>
       <c r="E271" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F271" t="s">
         <v>52</v>
@@ -17287,19 +17287,19 @@
         <v>41</v>
       </c>
       <c r="H271" t="s">
-        <v>593</v>
+        <v>564</v>
       </c>
       <c r="I271" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J271" t="s">
-        <v>595</v>
+        <v>60</v>
       </c>
       <c r="K271" t="s">
-        <v>595</v>
+        <v>56</v>
       </c>
       <c r="L271" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M271" t="s">
         <v>559</v>
@@ -17311,7 +17311,7 @@
         <v>48</v>
       </c>
       <c r="P271" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="Q271" t="s">
         <v>47</v>
@@ -17334,28 +17334,28 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>597</v>
+        <v>539</v>
       </c>
       <c r="F272" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G272" t="s">
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>576</v>
+        <v>336</v>
       </c>
       <c r="I272" t="s">
         <v>598</v>
       </c>
       <c r="J272" t="s">
-        <v>60</v>
+        <v>599</v>
       </c>
       <c r="K272" t="s">
-        <v>56</v>
+        <v>247</v>
       </c>
       <c r="L272" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M272" t="s">
         <v>559</v>
@@ -17390,7 +17390,7 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F273" t="s">
         <v>40</v>
@@ -17399,13 +17399,13 @@
         <v>41</v>
       </c>
       <c r="H273" t="s">
-        <v>336</v>
+        <v>601</v>
       </c>
       <c r="I273" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="J273" t="s">
-        <v>601</v>
+        <v>537</v>
       </c>
       <c r="K273" t="s">
         <v>247</v>
@@ -17423,7 +17423,7 @@
         <v>48</v>
       </c>
       <c r="P273" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -18015,7 +18015,7 @@
         <v>41</v>
       </c>
       <c r="H284" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I284" t="s">
         <v>626</v>
@@ -18024,7 +18024,7 @@
         <v>627</v>
       </c>
       <c r="K284" t="s">
-        <v>71</v>
+        <v>240</v>
       </c>
       <c r="L284" t="s">
         <v>34</v>
@@ -18071,7 +18071,7 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="I285" t="s">
         <v>629</v>
@@ -18080,7 +18080,7 @@
         <v>627</v>
       </c>
       <c r="K285" t="s">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18357,7 +18357,7 @@
         <v>646</v>
       </c>
       <c r="J290" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K290" t="s">
         <v>240</v>
@@ -18637,7 +18637,7 @@
         <v>665</v>
       </c>
       <c r="J295" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K295" t="s">
         <v>247</v>
@@ -18805,7 +18805,7 @@
         <v>677</v>
       </c>
       <c r="J298" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K298" t="s">
         <v>678</v>
@@ -18917,7 +18917,7 @@
         <v>684</v>
       </c>
       <c r="J300" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K300" t="s">
         <v>240</v>
@@ -19032,7 +19032,7 @@
         <v>129</v>
       </c>
       <c r="K302" t="s">
-        <v>71</v>
+        <v>251</v>
       </c>
       <c r="L302" t="s">
         <v>692</v>
@@ -19073,25 +19073,25 @@
         <v>693</v>
       </c>
       <c r="F303" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G303" t="s">
         <v>41</v>
       </c>
       <c r="H303" t="s">
-        <v>42</v>
+        <v>694</v>
       </c>
       <c r="I303" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="J303" t="s">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="K303" t="s">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="L303" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M303" t="s">
         <v>688</v>
@@ -19103,7 +19103,7 @@
         <v>48</v>
       </c>
       <c r="P303" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Q303" t="s">
         <v>47</v>
@@ -19126,25 +19126,25 @@
         <v>34</v>
       </c>
       <c r="E304" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F304" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G304" t="s">
         <v>41</v>
       </c>
       <c r="H304" t="s">
-        <v>697</v>
+        <v>42</v>
       </c>
       <c r="I304" t="s">
         <v>698</v>
       </c>
       <c r="J304" t="s">
-        <v>129</v>
+        <v>240</v>
       </c>
       <c r="K304" t="s">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="L304" t="s">
         <v>699</v>
@@ -19203,7 +19203,7 @@
         <v>251</v>
       </c>
       <c r="L305" t="s">
-        <v>703</v>
+        <v>34</v>
       </c>
       <c r="M305" t="s">
         <v>688</v>
@@ -19238,7 +19238,7 @@
         <v>34</v>
       </c>
       <c r="E306" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F306" t="s">
         <v>52</v>
@@ -19247,19 +19247,19 @@
         <v>41</v>
       </c>
       <c r="H306" t="s">
+        <v>704</v>
+      </c>
+      <c r="I306" t="s">
         <v>705</v>
-      </c>
-      <c r="I306" t="s">
-        <v>706</v>
       </c>
       <c r="J306" t="s">
         <v>129</v>
       </c>
       <c r="K306" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="L306" t="s">
-        <v>34</v>
+        <v>706</v>
       </c>
       <c r="M306" t="s">
         <v>688</v>
@@ -19271,7 +19271,7 @@
         <v>48</v>
       </c>
       <c r="P306" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="Q306" t="s">
         <v>47</v>
@@ -19365,7 +19365,7 @@
         <v>712</v>
       </c>
       <c r="J308" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K308" t="s">
         <v>247</v>
@@ -19686,7 +19686,7 @@
         <v>34</v>
       </c>
       <c r="E314" t="s">
-        <v>734</v>
+        <v>534</v>
       </c>
       <c r="F314" t="s">
         <v>40</v>
@@ -19698,16 +19698,16 @@
         <v>723</v>
       </c>
       <c r="I314" t="s">
+        <v>734</v>
+      </c>
+      <c r="J314" t="s">
+        <v>246</v>
+      </c>
+      <c r="K314" t="s">
+        <v>82</v>
+      </c>
+      <c r="L314" t="s">
         <v>735</v>
-      </c>
-      <c r="J314" t="s">
-        <v>736</v>
-      </c>
-      <c r="K314" t="s">
-        <v>247</v>
-      </c>
-      <c r="L314" t="s">
-        <v>737</v>
       </c>
       <c r="M314" t="s">
         <v>727</v>
@@ -19719,7 +19719,7 @@
         <v>48</v>
       </c>
       <c r="P314" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q314" t="s">
         <v>47</v>
@@ -19742,7 +19742,7 @@
         <v>34</v>
       </c>
       <c r="E315" t="s">
-        <v>534</v>
+        <v>736</v>
       </c>
       <c r="F315" t="s">
         <v>40</v>
@@ -19754,13 +19754,13 @@
         <v>723</v>
       </c>
       <c r="I315" t="s">
+        <v>737</v>
+      </c>
+      <c r="J315" t="s">
         <v>738</v>
       </c>
-      <c r="J315" t="s">
-        <v>246</v>
-      </c>
       <c r="K315" t="s">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="L315" t="s">
         <v>739</v>
@@ -19775,7 +19775,7 @@
         <v>48</v>
       </c>
       <c r="P315" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -20093,7 +20093,7 @@
         <v>762</v>
       </c>
       <c r="J321" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K321" t="s">
         <v>247</v>
@@ -20261,7 +20261,7 @@
         <v>775</v>
       </c>
       <c r="J324" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="K324" t="s">
         <v>124</v>
@@ -20373,7 +20373,7 @@
         <v>783</v>
       </c>
       <c r="J326" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="K326" t="s">
         <v>247</v>
@@ -20429,7 +20429,7 @@
         <v>788</v>
       </c>
       <c r="J327" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="K327" t="s">
         <v>247</v>
@@ -20582,7 +20582,7 @@
         <v>33</v>
       </c>
       <c r="E330" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F330" t="s">
         <v>40</v>

--- a/xlsx/dre/DRE_04_2026.xlsx
+++ b/xlsx/dre/DRE_04_2026.xlsx
@@ -1832,7 +1832,7 @@
     <t>Felipe Domingos - salário fixo 2026</t>
   </si>
   <si>
-    <t>Carina Pereira</t>
+    <t>CARINA PEREIRA</t>
   </si>
   <si>
     <t>Carina - Pagamento 2026</t>

--- a/xlsx/dre/DRE_04_2026.xlsx
+++ b/xlsx/dre/DRE_04_2026.xlsx
@@ -705,66 +705,31 @@
     <t>R$ 2.125,39</t>
   </si>
   <si>
-    <t>637/1</t>
+    <t>9/4</t>
+  </si>
+  <si>
+    <t>R$  91,87</t>
+  </si>
+  <si>
+    <t>09/01/26</t>
+  </si>
+  <si>
+    <t>05/04/26</t>
+  </si>
+  <si>
+    <t>Grapa</t>
+  </si>
+  <si>
+    <t>633/1</t>
   </si>
   <si>
     <t>FERRAGENS FLORESTA EIRELI EPP</t>
   </si>
   <si>
-    <t>R$  209,68</t>
-  </si>
-  <si>
-    <t>15/05/26</t>
+    <t>R$  205,50</t>
   </si>
   <si>
     <t>estoque</t>
-  </si>
-  <si>
-    <t>633/1</t>
-  </si>
-  <si>
-    <t>R$  205,50</t>
-  </si>
-  <si>
-    <t>632/1</t>
-  </si>
-  <si>
-    <t>Leo Madeiras</t>
-  </si>
-  <si>
-    <t>R$  284,50</t>
-  </si>
-  <si>
-    <t>01/04/26</t>
-  </si>
-  <si>
-    <t>642/1</t>
-  </si>
-  <si>
-    <t>R$  720,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor	Fornecedor	Descrição
-189	Mercado livre	caixa de tomada cliente erro Antônio
-144,36	Mercado Livre	mini rodízio estoque
-153,6	Mercado Livre	rodízios estoque
-234	Mercado Livre	caixas Bin estoque
-</t>
-  </si>
-  <si>
-    <t>9/4</t>
-  </si>
-  <si>
-    <t>R$  91,87</t>
-  </si>
-  <si>
-    <t>09/01/26</t>
-  </si>
-  <si>
-    <t>05/04/26</t>
-  </si>
-  <si>
-    <t>Grapa</t>
   </si>
   <si>
     <t>649/1</t>
@@ -785,6 +750,41 @@
 </t>
   </si>
   <si>
+    <t>632/1</t>
+  </si>
+  <si>
+    <t>Leo Madeiras</t>
+  </si>
+  <si>
+    <t>R$  284,50</t>
+  </si>
+  <si>
+    <t>01/04/26</t>
+  </si>
+  <si>
+    <t>642/1</t>
+  </si>
+  <si>
+    <t>R$  720,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor	Fornecedor	Descrição
+189	Mercado livre	caixa de tomada cliente erro Antônio
+144,36	Mercado Livre	mini rodízio estoque
+153,6	Mercado Livre	rodízios estoque
+234	Mercado Livre	caixas Bin estoque
+</t>
+  </si>
+  <si>
+    <t>637/1</t>
+  </si>
+  <si>
+    <t>R$  209,68</t>
+  </si>
+  <si>
+    <t>15/05/26</t>
+  </si>
+  <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
@@ -1040,6 +1040,9 @@
     <t>FELIPE DOMINGOS BARBOSA</t>
   </si>
   <si>
+    <t>R$  417,35</t>
+  </si>
+  <si>
     <t>R$  272,79</t>
   </si>
   <si>
@@ -1067,9 +1070,6 @@
     <t>R$  404,69</t>
   </si>
   <si>
-    <t>R$  417,35</t>
-  </si>
-  <si>
     <t>4.03.01.02.02 Comissões vendas</t>
   </si>
   <si>
@@ -1187,51 +1187,51 @@
     <t>R$ 5.521,58</t>
   </si>
   <si>
+    <t>FERNANDA DOCHVAT SILVA</t>
+  </si>
+  <si>
+    <t>R$  404,67</t>
+  </si>
+  <si>
+    <t>01/07/26</t>
+  </si>
+  <si>
+    <t>R$  424,52</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>R$  1.333,58</t>
+  </si>
+  <si>
+    <t>06/02/26</t>
+  </si>
+  <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
+    <t>R$  401,23</t>
+  </si>
+  <si>
+    <t>R$  272,80</t>
+  </si>
+  <si>
+    <t>23801/1</t>
+  </si>
+  <si>
+    <t>R$  710,09</t>
+  </si>
+  <si>
+    <t>23801AndersonLS</t>
+  </si>
+  <si>
     <t>RAYSSA BARBOSA LEMOS</t>
   </si>
   <si>
     <t>R$  758,36</t>
   </si>
   <si>
-    <t>FERNANDA DOCHVAT SILVA</t>
-  </si>
-  <si>
-    <t>01/06/26</t>
-  </si>
-  <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>R$  1.333,58</t>
-  </si>
-  <si>
-    <t>06/02/26</t>
-  </si>
-  <si>
-    <t>R$  404,67</t>
-  </si>
-  <si>
-    <t>01/07/26</t>
-  </si>
-  <si>
-    <t>R$  424,52</t>
-  </si>
-  <si>
-    <t>R$  401,23</t>
-  </si>
-  <si>
-    <t>R$  272,80</t>
-  </si>
-  <si>
-    <t>23801/1</t>
-  </si>
-  <si>
-    <t>R$  710,09</t>
-  </si>
-  <si>
-    <t>23801AndersonLS</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1337,12 +1337,12 @@
     <t>DSR abr26/1</t>
   </si>
   <si>
+    <t>R$  736,46</t>
+  </si>
+  <si>
     <t>R$  549,59</t>
   </si>
   <si>
-    <t>R$  736,46</t>
-  </si>
-  <si>
     <t>4.03.03 GASTOS GERAIS COM VENDAS</t>
   </si>
   <si>
@@ -1358,24 +1358,24 @@
     <t>4.03.03.01.01 Frete logístico - entrega a clientes</t>
   </si>
   <si>
+    <t>ADM UBER/0</t>
+  </si>
+  <si>
+    <t>Uber</t>
+  </si>
+  <si>
+    <t>R$  220,88</t>
+  </si>
+  <si>
+    <t>05/10/26</t>
+  </si>
+  <si>
     <t>71901UB/0</t>
   </si>
   <si>
-    <t>Uber</t>
-  </si>
-  <si>
     <t>R$  26,75</t>
   </si>
   <si>
-    <t>ADM UBER/0</t>
-  </si>
-  <si>
-    <t>R$  220,88</t>
-  </si>
-  <si>
-    <t>05/10/26</t>
-  </si>
-  <si>
     <t>Lalamove/2</t>
   </si>
   <si>
@@ -1397,75 +1397,75 @@
     <t>16/06/26</t>
   </si>
   <si>
+    <t>647/1</t>
+  </si>
+  <si>
+    <t>R$  70,00</t>
+  </si>
+  <si>
+    <t>Recarga</t>
+  </si>
+  <si>
+    <t>50503/0</t>
+  </si>
+  <si>
+    <t>R$  62,55</t>
+  </si>
+  <si>
+    <t>50503FABIOTN</t>
+  </si>
+  <si>
+    <t>42701/0</t>
+  </si>
+  <si>
+    <t>R$  17,99</t>
+  </si>
+  <si>
+    <t>42701ERIKA</t>
+  </si>
+  <si>
+    <t>46401/0</t>
+  </si>
+  <si>
+    <t>R$  12,65</t>
+  </si>
+  <si>
+    <t>33201BRUNALESS</t>
+  </si>
+  <si>
+    <t>45001/0</t>
+  </si>
+  <si>
+    <t>R$  95,50</t>
+  </si>
+  <si>
+    <t>45001ANACLARABLA</t>
+  </si>
+  <si>
+    <t>36902/0</t>
+  </si>
+  <si>
+    <t>R$  31,97</t>
+  </si>
+  <si>
+    <t>36902LeticiaOC</t>
+  </si>
+  <si>
+    <t>48801/2</t>
+  </si>
+  <si>
+    <t>R$  47,08</t>
+  </si>
+  <si>
+    <t>48801ANACASS</t>
+  </si>
+  <si>
     <t>ADM U/7</t>
   </si>
   <si>
     <t>R$  219,14</t>
   </si>
   <si>
-    <t>50503/0</t>
-  </si>
-  <si>
-    <t>R$  62,55</t>
-  </si>
-  <si>
-    <t>50503FABIOTN</t>
-  </si>
-  <si>
-    <t>42701/0</t>
-  </si>
-  <si>
-    <t>R$  17,99</t>
-  </si>
-  <si>
-    <t>42701ERIKA</t>
-  </si>
-  <si>
-    <t>36902/0</t>
-  </si>
-  <si>
-    <t>R$  31,97</t>
-  </si>
-  <si>
-    <t>36902LeticiaOC</t>
-  </si>
-  <si>
-    <t>46401/0</t>
-  </si>
-  <si>
-    <t>R$  12,65</t>
-  </si>
-  <si>
-    <t>33201BRUNALESS</t>
-  </si>
-  <si>
-    <t>647/1</t>
-  </si>
-  <si>
-    <t>R$  70,00</t>
-  </si>
-  <si>
-    <t>Recarga</t>
-  </si>
-  <si>
-    <t>48801/2</t>
-  </si>
-  <si>
-    <t>R$  47,08</t>
-  </si>
-  <si>
-    <t>48801ANACASS</t>
-  </si>
-  <si>
-    <t>45001/0</t>
-  </si>
-  <si>
-    <t>R$  95,50</t>
-  </si>
-  <si>
-    <t>45001ANACLARABLA</t>
-  </si>
-  <si>
     <t>15201/0</t>
   </si>
   <si>
@@ -1481,6 +1481,24 @@
     <t>R$  20,58</t>
   </si>
   <si>
+    <t>49701/0</t>
+  </si>
+  <si>
+    <t>R$  49,18</t>
+  </si>
+  <si>
+    <t>49701GABRIZANC</t>
+  </si>
+  <si>
+    <t>35901/0</t>
+  </si>
+  <si>
+    <t>R$  29,93</t>
+  </si>
+  <si>
+    <t>35901TatianaLF</t>
+  </si>
+  <si>
     <t>45901U/0</t>
   </si>
   <si>
@@ -1490,15 +1508,6 @@
     <t>45901ANAMARIDEO</t>
   </si>
   <si>
-    <t>35901/0</t>
-  </si>
-  <si>
-    <t>R$  29,93</t>
-  </si>
-  <si>
-    <t>35901TatianaLF</t>
-  </si>
-  <si>
     <t>40701/0</t>
   </si>
   <si>
@@ -1508,6 +1517,15 @@
     <t>40701julianMac</t>
   </si>
   <si>
+    <t>43601U/0</t>
+  </si>
+  <si>
+    <t>R$  58,62</t>
+  </si>
+  <si>
+    <t>43601MICHELLDSP</t>
+  </si>
+  <si>
     <t>630/1</t>
   </si>
   <si>
@@ -1529,24 +1547,6 @@
     <t>46201ANGELASC</t>
   </si>
   <si>
-    <t>43601U/0</t>
-  </si>
-  <si>
-    <t>R$  58,62</t>
-  </si>
-  <si>
-    <t>43601MICHELLDSP</t>
-  </si>
-  <si>
-    <t>49701/0</t>
-  </si>
-  <si>
-    <t>R$  49,18</t>
-  </si>
-  <si>
-    <t>49701GABRIZANC</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -1559,21 +1559,21 @@
     <t>R$ 277,65</t>
   </si>
   <si>
+    <t>5/1</t>
+  </si>
+  <si>
+    <t>R$  92,55</t>
+  </si>
+  <si>
+    <t>Mercado Livre</t>
+  </si>
+  <si>
+    <t>5/3</t>
+  </si>
+  <si>
     <t>5/2</t>
   </si>
   <si>
-    <t>R$  92,55</t>
-  </si>
-  <si>
-    <t>Mercado Livre</t>
-  </si>
-  <si>
-    <t>5/3</t>
-  </si>
-  <si>
-    <t>5/1</t>
-  </si>
-  <si>
     <t>4.03.03.02.05 Assistência técnica - custo loja</t>
   </si>
   <si>
@@ -1604,24 +1604,24 @@
     <t>4.03.03.08.01 Brindes para clientes (CV)</t>
   </si>
   <si>
+    <t>2/3</t>
+  </si>
+  <si>
+    <t>Licoretto Bebidas</t>
+  </si>
+  <si>
+    <t>R$  79,98</t>
+  </si>
+  <si>
+    <t>Brindes clientes</t>
+  </si>
+  <si>
+    <t>2/1</t>
+  </si>
+  <si>
     <t>2/2</t>
   </si>
   <si>
-    <t>Licoretto Bebidas</t>
-  </si>
-  <si>
-    <t>R$  79,98</t>
-  </si>
-  <si>
-    <t>Brindes clientes</t>
-  </si>
-  <si>
-    <t>2/1</t>
-  </si>
-  <si>
-    <t>2/3</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -1646,6 +1646,15 @@
     <t>12/4</t>
   </si>
   <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>R$  14,99</t>
+  </si>
+  <si>
+    <t>Google 2026</t>
+  </si>
+  <si>
     <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
   </si>
   <si>
@@ -1670,15 +1679,6 @@
     <t>Facebook 2026</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>R$  14,99</t>
-  </si>
-  <si>
-    <t>Google 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -1721,6 +1721,18 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>659/1</t>
+  </si>
+  <si>
+    <t>RAYSSA BARBOSA SILVA</t>
+  </si>
+  <si>
+    <t>R$  1.287,09</t>
+  </si>
+  <si>
+    <t>07/05/26</t>
+  </si>
+  <si>
     <t>658/1</t>
   </si>
   <si>
@@ -1730,7 +1742,31 @@
     <t>R$  1.060,00</t>
   </si>
   <si>
-    <t>07/05/26</t>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>19/04/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
   </si>
   <si>
     <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
@@ -1742,16 +1778,22 @@
     <t>Sabrina Braunbeck - Pagamento 2026</t>
   </si>
   <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>R$  2.219,85</t>
+  </si>
+  <si>
+    <t>18/03/26</t>
+  </si>
+  <si>
+    <t>Felipe Domingos - salário fixo 2026</t>
   </si>
   <si>
     <t>12/02/26</t>
@@ -1760,22 +1802,28 @@
     <t>Fernanda Dochvat - Fixo 2026</t>
   </si>
   <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>19/04/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.795,57</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
   </si>
   <si>
     <t>627/1</t>
@@ -1793,39 +1841,6 @@
     <t>17 dias</t>
   </si>
   <si>
-    <t>659/1</t>
-  </si>
-  <si>
-    <t>RAYSSA BARBOSA SILVA</t>
-  </si>
-  <si>
-    <t>R$  1.287,09</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
-  </si>
-  <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.795,57</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
     <t>616/1</t>
   </si>
   <si>
@@ -1835,21 +1850,6 @@
     <t>Reajuste dissidio</t>
   </si>
   <si>
-    <t>R$  2.219,85</t>
-  </si>
-  <si>
-    <t>18/03/26</t>
-  </si>
-  <si>
-    <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -1916,19 +1916,19 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT abr26/1</t>
+  </si>
+  <si>
+    <t>R$  290,65</t>
+  </si>
+  <si>
+    <t>31/03/26</t>
+  </si>
+  <si>
     <t>VT abr26/4</t>
   </si>
   <si>
     <t>R$  411,36</t>
-  </si>
-  <si>
-    <t>31/03/26</t>
-  </si>
-  <si>
-    <t>VT abr26/1</t>
-  </si>
-  <si>
-    <t>R$  290,65</t>
   </si>
   <si>
     <t>4.04.01.07 Uniformes e crachás</t>
@@ -2110,18 +2110,6 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
-    <t>646/1</t>
-  </si>
-  <si>
-    <t>Oxxo</t>
-  </si>
-  <si>
-    <t>R$  90,07</t>
-  </si>
-  <si>
-    <t>Cafés loja</t>
-  </si>
-  <si>
     <t>644/1</t>
   </si>
   <si>
@@ -2141,15 +2129,6 @@
   </si>
   <si>
     <t>Envelope</t>
-  </si>
-  <si>
-    <t>648/1</t>
-  </si>
-  <si>
-    <t>Chaveiro Rouxinol</t>
-  </si>
-  <si>
-    <t>R$  90,00</t>
   </si>
   <si>
     <t>643/1</t>
@@ -2168,6 +2147,27 @@
 </t>
   </si>
   <si>
+    <t>646/1</t>
+  </si>
+  <si>
+    <t>Oxxo</t>
+  </si>
+  <si>
+    <t>R$  90,07</t>
+  </si>
+  <si>
+    <t>Cafés loja</t>
+  </si>
+  <si>
+    <t>648/1</t>
+  </si>
+  <si>
+    <t>Chaveiro Rouxinol</t>
+  </si>
+  <si>
+    <t>R$  90,00</t>
+  </si>
+  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2249,22 +2249,22 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
+    <t>3/3</t>
+  </si>
+  <si>
+    <t>R$  1.248,76</t>
+  </si>
+  <si>
+    <t>13/02/26</t>
+  </si>
+  <si>
+    <t>Promob 2026/2</t>
+  </si>
+  <si>
     <t>R$  599,00</t>
   </si>
   <si>
     <t>Promob 2026</t>
-  </si>
-  <si>
-    <t>3/3</t>
-  </si>
-  <si>
-    <t>R$  1.248,76</t>
-  </si>
-  <si>
-    <t>13/02/26</t>
-  </si>
-  <si>
-    <t>Promob 2026/2</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -6373,22 +6373,22 @@
         <v>230</v>
       </c>
       <c r="F76" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G76" t="s">
         <v>41</v>
       </c>
       <c r="H76" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" t="s">
         <v>231</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>232</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>233</v>
-      </c>
-      <c r="K76" t="s">
-        <v>88</v>
       </c>
       <c r="L76" t="s">
         <v>234</v>
@@ -6403,7 +6403,7 @@
         <v>48</v>
       </c>
       <c r="P76" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q76" t="s">
         <v>47</v>
@@ -6435,10 +6435,10 @@
         <v>41</v>
       </c>
       <c r="H77" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I77" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J77" t="s">
         <v>119</v>
@@ -6447,7 +6447,7 @@
         <v>119</v>
       </c>
       <c r="L77" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M77" t="s">
         <v>228</v>
@@ -6459,7 +6459,7 @@
         <v>48</v>
       </c>
       <c r="P77" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q77" t="s">
         <v>47</v>
@@ -6482,7 +6482,7 @@
         <v>34</v>
       </c>
       <c r="E78" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F78" t="s">
         <v>52</v>
@@ -6491,19 +6491,19 @@
         <v>41</v>
       </c>
       <c r="H78" t="s">
-        <v>238</v>
+        <v>42</v>
       </c>
       <c r="I78" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J78" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="K78" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L78" t="s">
-        <v>34</v>
+        <v>242</v>
       </c>
       <c r="M78" t="s">
         <v>228</v>
@@ -6515,7 +6515,7 @@
         <v>48</v>
       </c>
       <c r="P78" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q78" t="s">
         <v>47</v>
@@ -6538,7 +6538,7 @@
         <v>34</v>
       </c>
       <c r="E79" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F79" t="s">
         <v>52</v>
@@ -6547,19 +6547,19 @@
         <v>41</v>
       </c>
       <c r="H79" t="s">
-        <v>42</v>
+        <v>244</v>
       </c>
       <c r="I79" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J79" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="K79" t="s">
-        <v>71</v>
+        <v>246</v>
       </c>
       <c r="L79" t="s">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="M79" t="s">
         <v>228</v>
@@ -6571,7 +6571,7 @@
         <v>48</v>
       </c>
       <c r="P79" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q79" t="s">
         <v>47</v>
@@ -6594,10 +6594,10 @@
         <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F80" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G80" t="s">
         <v>41</v>
@@ -6606,16 +6606,16 @@
         <v>42</v>
       </c>
       <c r="I80" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="J80" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="K80" t="s">
-        <v>247</v>
+        <v>71</v>
       </c>
       <c r="L80" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M80" t="s">
         <v>228</v>
@@ -6627,7 +6627,7 @@
         <v>48</v>
       </c>
       <c r="P80" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q80" t="s">
         <v>47</v>
@@ -6650,7 +6650,7 @@
         <v>34</v>
       </c>
       <c r="E81" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F81" t="s">
         <v>52</v>
@@ -6659,19 +6659,19 @@
         <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>42</v>
+        <v>236</v>
       </c>
       <c r="I81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J81" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="K81" t="s">
-        <v>251</v>
+        <v>88</v>
       </c>
       <c r="L81" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="M81" t="s">
         <v>228</v>
@@ -6683,7 +6683,7 @@
         <v>48</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q81" t="s">
         <v>47</v>
@@ -9226,7 +9226,7 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="F127" t="s">
         <v>183</v>
@@ -9244,7 +9244,7 @@
         <v>129</v>
       </c>
       <c r="K127" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="L127" t="s">
         <v>34</v>
@@ -9256,7 +9256,7 @@
         <v>47</v>
       </c>
       <c r="O127" t="s">
-        <v>292</v>
+        <v>213</v>
       </c>
       <c r="P127" t="s">
         <v>337</v>
@@ -9282,7 +9282,7 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F128" t="s">
         <v>183</v>
@@ -9300,7 +9300,7 @@
         <v>129</v>
       </c>
       <c r="K128" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="L128" t="s">
         <v>34</v>
@@ -9312,7 +9312,7 @@
         <v>47</v>
       </c>
       <c r="O128" t="s">
-        <v>72</v>
+        <v>292</v>
       </c>
       <c r="P128" t="s">
         <v>338</v>
@@ -9338,7 +9338,7 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F129" t="s">
         <v>183</v>
@@ -9368,7 +9368,7 @@
         <v>47</v>
       </c>
       <c r="O129" t="s">
-        <v>305</v>
+        <v>72</v>
       </c>
       <c r="P129" t="s">
         <v>339</v>
@@ -9394,7 +9394,7 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F130" t="s">
         <v>183</v>
@@ -9412,7 +9412,7 @@
         <v>129</v>
       </c>
       <c r="K130" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="L130" t="s">
         <v>34</v>
@@ -9424,7 +9424,7 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="P130" t="s">
         <v>340</v>
@@ -9450,7 +9450,7 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F131" t="s">
         <v>183</v>
@@ -9468,7 +9468,7 @@
         <v>129</v>
       </c>
       <c r="K131" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="L131" t="s">
         <v>34</v>
@@ -9480,7 +9480,7 @@
         <v>47</v>
       </c>
       <c r="O131" t="s">
-        <v>104</v>
+        <v>287</v>
       </c>
       <c r="P131" t="s">
         <v>341</v>
@@ -9506,7 +9506,7 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="F132" t="s">
         <v>183</v>
@@ -9524,7 +9524,7 @@
         <v>129</v>
       </c>
       <c r="K132" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="L132" t="s">
         <v>34</v>
@@ -9536,7 +9536,7 @@
         <v>47</v>
       </c>
       <c r="O132" t="s">
-        <v>292</v>
+        <v>104</v>
       </c>
       <c r="P132" t="s">
         <v>342</v>
@@ -9562,7 +9562,7 @@
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F133" t="s">
         <v>183</v>
@@ -9580,7 +9580,7 @@
         <v>129</v>
       </c>
       <c r="K133" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="L133" t="s">
         <v>34</v>
@@ -9592,7 +9592,7 @@
         <v>47</v>
       </c>
       <c r="O133" t="s">
-        <v>188</v>
+        <v>292</v>
       </c>
       <c r="P133" t="s">
         <v>343</v>
@@ -9618,7 +9618,7 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F134" t="s">
         <v>183</v>
@@ -9648,7 +9648,7 @@
         <v>47</v>
       </c>
       <c r="O134" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="P134" t="s">
         <v>344</v>
@@ -9674,7 +9674,7 @@
         <v>34</v>
       </c>
       <c r="E135" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="F135" t="s">
         <v>183</v>
@@ -9692,7 +9692,7 @@
         <v>129</v>
       </c>
       <c r="K135" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L135" t="s">
         <v>34</v>
@@ -9704,7 +9704,7 @@
         <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>209</v>
+        <v>77</v>
       </c>
       <c r="P135" t="s">
         <v>345</v>
@@ -9730,7 +9730,7 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F136" t="s">
         <v>183</v>
@@ -9748,7 +9748,7 @@
         <v>129</v>
       </c>
       <c r="K136" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L136" t="s">
         <v>34</v>
@@ -9760,7 +9760,7 @@
         <v>47</v>
       </c>
       <c r="O136" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P136" t="s">
         <v>346</v>
@@ -10750,7 +10750,7 @@
         <v>369</v>
       </c>
       <c r="I154" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J154" t="s">
         <v>129</v>
@@ -10771,7 +10771,7 @@
         <v>305</v>
       </c>
       <c r="P154" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q154" t="s">
         <v>47</v>
@@ -10806,7 +10806,7 @@
         <v>369</v>
       </c>
       <c r="I155" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J155" t="s">
         <v>129</v>
@@ -10827,7 +10827,7 @@
         <v>72</v>
       </c>
       <c r="P155" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q155" t="s">
         <v>47</v>
@@ -10862,7 +10862,7 @@
         <v>369</v>
       </c>
       <c r="I156" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J156" t="s">
         <v>129</v>
@@ -10883,7 +10883,7 @@
         <v>96</v>
       </c>
       <c r="P156" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q156" t="s">
         <v>47</v>
@@ -10974,7 +10974,7 @@
         <v>369</v>
       </c>
       <c r="I158" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J158" t="s">
         <v>129</v>
@@ -10995,7 +10995,7 @@
         <v>77</v>
       </c>
       <c r="P158" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q158" t="s">
         <v>47</v>
@@ -11030,7 +11030,7 @@
         <v>369</v>
       </c>
       <c r="I159" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J159" t="s">
         <v>129</v>
@@ -11051,7 +11051,7 @@
         <v>209</v>
       </c>
       <c r="P159" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q159" t="s">
         <v>47</v>
@@ -11086,7 +11086,7 @@
         <v>369</v>
       </c>
       <c r="I160" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="J160" t="s">
         <v>129</v>
@@ -11107,7 +11107,7 @@
         <v>213</v>
       </c>
       <c r="P160" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="Q160" t="s">
         <v>47</v>
@@ -11142,7 +11142,7 @@
         <v>369</v>
       </c>
       <c r="I161" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J161" t="s">
         <v>129</v>
@@ -11163,7 +11163,7 @@
         <v>287</v>
       </c>
       <c r="P161" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q161" t="s">
         <v>47</v>
@@ -11198,7 +11198,7 @@
         <v>369</v>
       </c>
       <c r="I162" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J162" t="s">
         <v>129</v>
@@ -11219,7 +11219,7 @@
         <v>104</v>
       </c>
       <c r="P162" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q162" t="s">
         <v>47</v>
@@ -11254,7 +11254,7 @@
         <v>369</v>
       </c>
       <c r="I163" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J163" t="s">
         <v>129</v>
@@ -11275,7 +11275,7 @@
         <v>292</v>
       </c>
       <c r="P163" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q163" t="s">
         <v>47</v>
@@ -11310,7 +11310,7 @@
         <v>369</v>
       </c>
       <c r="I164" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J164" t="s">
         <v>129</v>
@@ -11331,7 +11331,7 @@
         <v>188</v>
       </c>
       <c r="P164" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q164" t="s">
         <v>47</v>
@@ -11858,10 +11858,10 @@
         <v>33</v>
       </c>
       <c r="E174" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="F174" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="G174" t="s">
         <v>41</v>
@@ -11873,10 +11873,10 @@
         <v>387</v>
       </c>
       <c r="J174" t="s">
-        <v>119</v>
+        <v>388</v>
       </c>
       <c r="K174" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="L174" t="s">
         <v>34</v>
@@ -11888,7 +11888,7 @@
         <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>292</v>
+        <v>209</v>
       </c>
       <c r="P174" t="s">
         <v>387</v>
@@ -11914,7 +11914,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F175" t="s">
         <v>183</v>
@@ -11923,16 +11923,16 @@
         <v>41</v>
       </c>
       <c r="H175" t="s">
+        <v>386</v>
+      </c>
+      <c r="I175" t="s">
+        <v>389</v>
+      </c>
+      <c r="J175" t="s">
         <v>388</v>
       </c>
-      <c r="I175" t="s">
-        <v>370</v>
-      </c>
-      <c r="J175" t="s">
-        <v>389</v>
-      </c>
       <c r="K175" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -11944,10 +11944,10 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>120</v>
+        <v>287</v>
       </c>
       <c r="P175" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="Q175" t="s">
         <v>47</v>
@@ -11970,7 +11970,7 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F176" t="s">
         <v>183</v>
@@ -11979,16 +11979,16 @@
         <v>41</v>
       </c>
       <c r="H176" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I176" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="J176" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K176" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -12000,10 +12000,10 @@
         <v>47</v>
       </c>
       <c r="O176" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="P176" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="Q176" t="s">
         <v>47</v>
@@ -12026,7 +12026,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F177" t="s">
         <v>183</v>
@@ -12035,16 +12035,16 @@
         <v>41</v>
       </c>
       <c r="H177" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="I177" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="J177" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K177" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -12056,10 +12056,10 @@
         <v>47</v>
       </c>
       <c r="O177" t="s">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="P177" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="Q177" t="s">
         <v>47</v>
@@ -12082,7 +12082,7 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F178" t="s">
         <v>183</v>
@@ -12091,16 +12091,16 @@
         <v>41</v>
       </c>
       <c r="H178" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="I178" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="J178" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K178" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -12112,10 +12112,10 @@
         <v>47</v>
       </c>
       <c r="O178" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="P178" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="Q178" t="s">
         <v>47</v>
@@ -12138,7 +12138,7 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F179" t="s">
         <v>183</v>
@@ -12147,16 +12147,16 @@
         <v>41</v>
       </c>
       <c r="H179" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="I179" t="s">
+        <v>337</v>
+      </c>
+      <c r="J179" t="s">
         <v>393</v>
       </c>
-      <c r="J179" t="s">
-        <v>394</v>
-      </c>
       <c r="K179" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12168,10 +12168,10 @@
         <v>47</v>
       </c>
       <c r="O179" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="P179" t="s">
-        <v>393</v>
+        <v>337</v>
       </c>
       <c r="Q179" t="s">
         <v>47</v>
@@ -12194,7 +12194,7 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F180" t="s">
         <v>183</v>
@@ -12203,16 +12203,16 @@
         <v>41</v>
       </c>
       <c r="H180" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I180" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J180" t="s">
-        <v>394</v>
+        <v>129</v>
       </c>
       <c r="K180" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12224,10 +12224,10 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="P180" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Q180" t="s">
         <v>47</v>
@@ -12250,7 +12250,7 @@
         <v>34</v>
       </c>
       <c r="E181" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F181" t="s">
         <v>183</v>
@@ -12259,16 +12259,16 @@
         <v>41</v>
       </c>
       <c r="H181" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="I181" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J181" t="s">
         <v>129</v>
       </c>
       <c r="K181" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="L181" t="s">
         <v>34</v>
@@ -12280,10 +12280,10 @@
         <v>47</v>
       </c>
       <c r="O181" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P181" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q181" t="s">
         <v>47</v>
@@ -12306,7 +12306,7 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>195</v>
+        <v>396</v>
       </c>
       <c r="F182" t="s">
         <v>183</v>
@@ -12315,7 +12315,7 @@
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I182" t="s">
         <v>397</v>
@@ -12324,7 +12324,7 @@
         <v>129</v>
       </c>
       <c r="K182" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12336,7 +12336,7 @@
         <v>47</v>
       </c>
       <c r="O182" t="s">
-        <v>72</v>
+        <v>398</v>
       </c>
       <c r="P182" t="s">
         <v>397</v>
@@ -12362,25 +12362,25 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>398</v>
+        <v>182</v>
       </c>
       <c r="F183" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="G183" t="s">
         <v>41</v>
       </c>
       <c r="H183" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="I183" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J183" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="K183" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="L183" t="s">
         <v>34</v>
@@ -12392,10 +12392,10 @@
         <v>47</v>
       </c>
       <c r="O183" t="s">
+        <v>292</v>
+      </c>
+      <c r="P183" t="s">
         <v>400</v>
-      </c>
-      <c r="P183" t="s">
-        <v>399</v>
       </c>
       <c r="Q183" t="s">
         <v>47</v>
@@ -12881,7 +12881,7 @@
         <v>421</v>
       </c>
       <c r="J192" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="K192" t="s">
         <v>125</v>
@@ -12937,7 +12937,7 @@
         <v>419</v>
       </c>
       <c r="J193" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="K193" t="s">
         <v>125</v>
@@ -13379,16 +13379,16 @@
         <v>41</v>
       </c>
       <c r="H201" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="I201" t="s">
         <v>436</v>
       </c>
       <c r="J201" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="K201" t="s">
-        <v>89</v>
+        <v>246</v>
       </c>
       <c r="L201" t="s">
         <v>34</v>
@@ -13435,16 +13435,16 @@
         <v>41</v>
       </c>
       <c r="H202" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I202" t="s">
         <v>437</v>
       </c>
       <c r="J202" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K202" t="s">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="L202" t="s">
         <v>34</v>
@@ -13609,10 +13609,10 @@
         <v>445</v>
       </c>
       <c r="J205" t="s">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="K205" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="L205" t="s">
         <v>34</v>
@@ -13624,7 +13624,7 @@
         <v>47</v>
       </c>
       <c r="O205" t="s">
-        <v>292</v>
+        <v>48</v>
       </c>
       <c r="P205" t="s">
         <v>445</v>
@@ -13650,7 +13650,7 @@
         <v>34</v>
       </c>
       <c r="E206" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F206" t="s">
         <v>52</v>
@@ -13662,13 +13662,13 @@
         <v>444</v>
       </c>
       <c r="I206" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J206" t="s">
-        <v>448</v>
+        <v>83</v>
       </c>
       <c r="K206" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13680,10 +13680,10 @@
         <v>47</v>
       </c>
       <c r="O206" t="s">
-        <v>48</v>
+        <v>292</v>
       </c>
       <c r="P206" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q206" t="s">
         <v>47</v>
@@ -13939,19 +13939,19 @@
         <v>41</v>
       </c>
       <c r="H211" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="I211" t="s">
         <v>457</v>
       </c>
       <c r="J211" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="K211" t="s">
-        <v>119</v>
+        <v>241</v>
       </c>
       <c r="L211" t="s">
-        <v>34</v>
+        <v>458</v>
       </c>
       <c r="M211" t="s">
         <v>442</v>
@@ -13986,7 +13986,7 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F212" t="s">
         <v>52</v>
@@ -13998,7 +13998,7 @@
         <v>444</v>
       </c>
       <c r="I212" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J212" t="s">
         <v>119</v>
@@ -14016,10 +14016,10 @@
         <v>47</v>
       </c>
       <c r="O212" t="s">
+        <v>461</v>
+      </c>
+      <c r="P212" t="s">
         <v>460</v>
-      </c>
-      <c r="P212" t="s">
-        <v>459</v>
       </c>
       <c r="Q212" t="s">
         <v>47</v>
@@ -14042,7 +14042,7 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F213" t="s">
         <v>52</v>
@@ -14054,7 +14054,7 @@
         <v>444</v>
       </c>
       <c r="I213" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J213" t="s">
         <v>119</v>
@@ -14072,10 +14072,10 @@
         <v>47</v>
       </c>
       <c r="O213" t="s">
+        <v>464</v>
+      </c>
+      <c r="P213" t="s">
         <v>463</v>
-      </c>
-      <c r="P213" t="s">
-        <v>462</v>
       </c>
       <c r="Q213" t="s">
         <v>47</v>
@@ -14098,7 +14098,7 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F214" t="s">
         <v>52</v>
@@ -14110,7 +14110,7 @@
         <v>444</v>
       </c>
       <c r="I214" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J214" t="s">
         <v>119</v>
@@ -14128,10 +14128,10 @@
         <v>47</v>
       </c>
       <c r="O214" t="s">
+        <v>467</v>
+      </c>
+      <c r="P214" t="s">
         <v>466</v>
-      </c>
-      <c r="P214" t="s">
-        <v>465</v>
       </c>
       <c r="Q214" t="s">
         <v>47</v>
@@ -14154,7 +14154,7 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F215" t="s">
         <v>52</v>
@@ -14166,7 +14166,7 @@
         <v>444</v>
       </c>
       <c r="I215" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J215" t="s">
         <v>119</v>
@@ -14184,10 +14184,10 @@
         <v>47</v>
       </c>
       <c r="O215" t="s">
+        <v>470</v>
+      </c>
+      <c r="P215" t="s">
         <v>469</v>
-      </c>
-      <c r="P215" t="s">
-        <v>468</v>
       </c>
       <c r="Q215" t="s">
         <v>47</v>
@@ -14210,7 +14210,7 @@
         <v>34</v>
       </c>
       <c r="E216" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F216" t="s">
         <v>52</v>
@@ -14219,19 +14219,19 @@
         <v>41</v>
       </c>
       <c r="H216" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I216" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J216" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="K216" t="s">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="L216" t="s">
-        <v>472</v>
+        <v>34</v>
       </c>
       <c r="M216" t="s">
         <v>442</v>
@@ -14240,10 +14240,10 @@
         <v>47</v>
       </c>
       <c r="O216" t="s">
-        <v>48</v>
+        <v>473</v>
       </c>
       <c r="P216" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q216" t="s">
         <v>47</v>
@@ -14266,7 +14266,7 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F217" t="s">
         <v>52</v>
@@ -14278,7 +14278,7 @@
         <v>444</v>
       </c>
       <c r="I217" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J217" t="s">
         <v>119</v>
@@ -14296,10 +14296,10 @@
         <v>47</v>
       </c>
       <c r="O217" t="s">
+        <v>476</v>
+      </c>
+      <c r="P217" t="s">
         <v>475</v>
-      </c>
-      <c r="P217" t="s">
-        <v>474</v>
       </c>
       <c r="Q217" t="s">
         <v>47</v>
@@ -14322,7 +14322,7 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F218" t="s">
         <v>52</v>
@@ -14334,7 +14334,7 @@
         <v>444</v>
       </c>
       <c r="I218" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J218" t="s">
         <v>119</v>
@@ -14352,10 +14352,10 @@
         <v>47</v>
       </c>
       <c r="O218" t="s">
+        <v>48</v>
+      </c>
+      <c r="P218" t="s">
         <v>478</v>
-      </c>
-      <c r="P218" t="s">
-        <v>477</v>
       </c>
       <c r="Q218" t="s">
         <v>47</v>
@@ -14464,7 +14464,7 @@
         <v>47</v>
       </c>
       <c r="O220" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P220" t="s">
         <v>483</v>
@@ -14670,7 +14670,7 @@
         <v>444</v>
       </c>
       <c r="I224" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="J224" t="s">
         <v>119</v>
@@ -14688,10 +14688,10 @@
         <v>47</v>
       </c>
       <c r="O224" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="P224" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="Q224" t="s">
         <v>47</v>
@@ -14714,7 +14714,7 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F225" t="s">
         <v>52</v>
@@ -14726,7 +14726,7 @@
         <v>444</v>
       </c>
       <c r="I225" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J225" t="s">
         <v>119</v>
@@ -14744,10 +14744,10 @@
         <v>47</v>
       </c>
       <c r="O225" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="P225" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Q225" t="s">
         <v>47</v>
@@ -14770,7 +14770,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F226" t="s">
         <v>52</v>
@@ -14782,7 +14782,7 @@
         <v>444</v>
       </c>
       <c r="I226" t="s">
-        <v>498</v>
+        <v>469</v>
       </c>
       <c r="J226" t="s">
         <v>119</v>
@@ -14800,10 +14800,10 @@
         <v>47</v>
       </c>
       <c r="O226" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="P226" t="s">
-        <v>498</v>
+        <v>469</v>
       </c>
       <c r="Q226" t="s">
         <v>47</v>
@@ -15009,10 +15009,10 @@
         <v>511</v>
       </c>
       <c r="J230" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K230" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L230" t="s">
         <v>512</v>
@@ -15065,10 +15065,10 @@
         <v>511</v>
       </c>
       <c r="J231" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K231" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L231" t="s">
         <v>512</v>
@@ -15121,10 +15121,10 @@
         <v>511</v>
       </c>
       <c r="J232" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K232" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L232" t="s">
         <v>512</v>
@@ -15274,7 +15274,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F235" t="s">
         <v>40</v>
@@ -15289,10 +15289,10 @@
         <v>519</v>
       </c>
       <c r="J235" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="K235" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15304,7 +15304,7 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="P235" t="s">
         <v>519</v>
@@ -15330,7 +15330,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F236" t="s">
         <v>40</v>
@@ -15345,10 +15345,10 @@
         <v>519</v>
       </c>
       <c r="J236" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="K236" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15360,7 +15360,7 @@
         <v>47</v>
       </c>
       <c r="O236" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="P236" t="s">
         <v>519</v>
@@ -15386,7 +15386,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F237" t="s">
         <v>40</v>
@@ -15401,10 +15401,10 @@
         <v>519</v>
       </c>
       <c r="J237" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="K237" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L237" t="s">
         <v>34</v>
@@ -15416,7 +15416,7 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="P237" t="s">
         <v>519</v>
@@ -15442,7 +15442,7 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F238" t="s">
         <v>40</v>
@@ -15457,10 +15457,10 @@
         <v>519</v>
       </c>
       <c r="J238" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K238" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15472,7 +15472,7 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="P238" t="s">
         <v>519</v>
@@ -15498,7 +15498,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="F239" t="s">
         <v>40</v>
@@ -15510,13 +15510,13 @@
         <v>518</v>
       </c>
       <c r="I239" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J239" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K239" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15528,10 +15528,10 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>287</v>
+        <v>209</v>
       </c>
       <c r="P239" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q239" t="s">
         <v>47</v>
@@ -15554,7 +15554,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F240" t="s">
         <v>40</v>
@@ -15569,10 +15569,10 @@
         <v>519</v>
       </c>
       <c r="J240" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="K240" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15584,7 +15584,7 @@
         <v>47</v>
       </c>
       <c r="O240" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="P240" t="s">
         <v>519</v>
@@ -15610,7 +15610,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F241" t="s">
         <v>40</v>
@@ -15622,13 +15622,13 @@
         <v>518</v>
       </c>
       <c r="I241" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J241" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="K241" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15640,10 +15640,10 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>96</v>
+        <v>287</v>
       </c>
       <c r="P241" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q241" t="s">
         <v>47</v>
@@ -15666,10 +15666,10 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F242" t="s">
-        <v>521</v>
+        <v>40</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
@@ -15681,10 +15681,10 @@
         <v>519</v>
       </c>
       <c r="J242" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="K242" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -15696,13 +15696,13 @@
         <v>47</v>
       </c>
       <c r="O242" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="P242" t="s">
-        <v>34</v>
+        <v>519</v>
       </c>
       <c r="Q242" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15778,10 +15778,10 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F244" t="s">
-        <v>40</v>
+        <v>521</v>
       </c>
       <c r="G244" t="s">
         <v>41</v>
@@ -15793,10 +15793,10 @@
         <v>519</v>
       </c>
       <c r="J244" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="K244" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -15808,13 +15808,13 @@
         <v>47</v>
       </c>
       <c r="O244" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="P244" t="s">
-        <v>519</v>
+        <v>34</v>
       </c>
       <c r="Q244" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R244" t="s">
         <v>34</v>
@@ -15905,10 +15905,10 @@
         <v>527</v>
       </c>
       <c r="J246" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K246" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L246" t="s">
         <v>528</v>
@@ -15961,10 +15961,10 @@
         <v>527</v>
       </c>
       <c r="J247" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K247" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L247" t="s">
         <v>528</v>
@@ -16017,10 +16017,10 @@
         <v>527</v>
       </c>
       <c r="J248" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K248" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L248" t="s">
         <v>528</v>
@@ -16185,13 +16185,13 @@
         <v>540</v>
       </c>
       <c r="J251" t="s">
+        <v>232</v>
+      </c>
+      <c r="K251" t="s">
+        <v>233</v>
+      </c>
+      <c r="L251" t="s">
         <v>541</v>
-      </c>
-      <c r="K251" t="s">
-        <v>240</v>
-      </c>
-      <c r="L251" t="s">
-        <v>542</v>
       </c>
       <c r="M251" t="s">
         <v>533</v>
@@ -16226,7 +16226,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F252" t="s">
         <v>40</v>
@@ -16235,19 +16235,19 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
+        <v>542</v>
+      </c>
+      <c r="I252" t="s">
+        <v>543</v>
+      </c>
+      <c r="J252" t="s">
         <v>544</v>
       </c>
-      <c r="I252" t="s">
-        <v>94</v>
-      </c>
-      <c r="J252" t="s">
+      <c r="K252" t="s">
+        <v>246</v>
+      </c>
+      <c r="L252" t="s">
         <v>545</v>
-      </c>
-      <c r="K252" t="s">
-        <v>119</v>
-      </c>
-      <c r="L252" t="s">
-        <v>546</v>
       </c>
       <c r="M252" t="s">
         <v>533</v>
@@ -16259,7 +16259,7 @@
         <v>48</v>
       </c>
       <c r="P252" t="s">
-        <v>94</v>
+        <v>543</v>
       </c>
       <c r="Q252" t="s">
         <v>47</v>
@@ -16282,7 +16282,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="F253" t="s">
         <v>40</v>
@@ -16294,13 +16294,13 @@
         <v>547</v>
       </c>
       <c r="I253" t="s">
+        <v>94</v>
+      </c>
+      <c r="J253" t="s">
         <v>548</v>
       </c>
-      <c r="J253" t="s">
-        <v>246</v>
-      </c>
       <c r="K253" t="s">
-        <v>247</v>
+        <v>119</v>
       </c>
       <c r="L253" t="s">
         <v>549</v>
@@ -16315,7 +16315,7 @@
         <v>48</v>
       </c>
       <c r="P253" t="s">
-        <v>548</v>
+        <v>94</v>
       </c>
       <c r="Q253" t="s">
         <v>47</v>
@@ -16521,10 +16521,10 @@
         <v>557</v>
       </c>
       <c r="J257" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K257" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L257" t="s">
         <v>558</v>
@@ -16692,7 +16692,7 @@
         <v>567</v>
       </c>
       <c r="K260" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L260" t="s">
         <v>34</v>
@@ -16730,28 +16730,28 @@
         <v>34</v>
       </c>
       <c r="E261" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="F261" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G261" t="s">
         <v>41</v>
       </c>
       <c r="H261" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I261" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J261" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="K261" t="s">
-        <v>247</v>
+        <v>124</v>
       </c>
       <c r="L261" t="s">
-        <v>570</v>
+        <v>34</v>
       </c>
       <c r="M261" t="s">
         <v>563</v>
@@ -16763,7 +16763,7 @@
         <v>48</v>
       </c>
       <c r="P261" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Q261" t="s">
         <v>47</v>
@@ -16786,7 +16786,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>136</v>
+        <v>538</v>
       </c>
       <c r="F262" t="s">
         <v>40</v>
@@ -16795,19 +16795,19 @@
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="I262" t="s">
+        <v>557</v>
+      </c>
+      <c r="J262" t="s">
+        <v>232</v>
+      </c>
+      <c r="K262" t="s">
+        <v>233</v>
+      </c>
+      <c r="L262" t="s">
         <v>571</v>
-      </c>
-      <c r="J262" t="s">
-        <v>572</v>
-      </c>
-      <c r="K262" t="s">
-        <v>247</v>
-      </c>
-      <c r="L262" t="s">
-        <v>573</v>
       </c>
       <c r="M262" t="s">
         <v>563</v>
@@ -16819,7 +16819,7 @@
         <v>48</v>
       </c>
       <c r="P262" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="Q262" t="s">
         <v>47</v>
@@ -16842,7 +16842,7 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>538</v>
+        <v>136</v>
       </c>
       <c r="F263" t="s">
         <v>40</v>
@@ -16851,16 +16851,16 @@
         <v>41</v>
       </c>
       <c r="H263" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="I263" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="J263" t="s">
-        <v>246</v>
+        <v>573</v>
       </c>
       <c r="K263" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L263" t="s">
         <v>574</v>
@@ -16875,7 +16875,7 @@
         <v>48</v>
       </c>
       <c r="P263" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="Q263" t="s">
         <v>47</v>
@@ -16907,19 +16907,19 @@
         <v>41</v>
       </c>
       <c r="H264" t="s">
-        <v>388</v>
+        <v>575</v>
       </c>
       <c r="I264" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="J264" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="K264" t="s">
-        <v>247</v>
+        <v>576</v>
       </c>
       <c r="L264" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M264" t="s">
         <v>563</v>
@@ -16931,7 +16931,7 @@
         <v>48</v>
       </c>
       <c r="P264" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="Q264" t="s">
         <v>47</v>
@@ -16963,16 +16963,16 @@
         <v>41</v>
       </c>
       <c r="H265" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I265" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="J265" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K265" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L265" t="s">
         <v>579</v>
@@ -16987,7 +16987,7 @@
         <v>48</v>
       </c>
       <c r="P265" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="Q265" t="s">
         <v>47</v>
@@ -17010,7 +17010,7 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>136</v>
+        <v>538</v>
       </c>
       <c r="F266" t="s">
         <v>40</v>
@@ -17022,13 +17022,13 @@
         <v>580</v>
       </c>
       <c r="I266" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="J266" t="s">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="K266" t="s">
-        <v>581</v>
+        <v>233</v>
       </c>
       <c r="L266" t="s">
         <v>582</v>
@@ -17043,7 +17043,7 @@
         <v>48</v>
       </c>
       <c r="P266" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="Q266" t="s">
         <v>47</v>
@@ -17066,28 +17066,28 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
+        <v>538</v>
+      </c>
+      <c r="F267" t="s">
+        <v>40</v>
+      </c>
+      <c r="G267" t="s">
+        <v>41</v>
+      </c>
+      <c r="H267" t="s">
         <v>583</v>
       </c>
-      <c r="F267" t="s">
-        <v>52</v>
-      </c>
-      <c r="G267" t="s">
-        <v>41</v>
-      </c>
-      <c r="H267" t="s">
+      <c r="I267" t="s">
         <v>584</v>
       </c>
-      <c r="I267" t="s">
+      <c r="J267" t="s">
+        <v>544</v>
+      </c>
+      <c r="K267" t="s">
+        <v>233</v>
+      </c>
+      <c r="L267" t="s">
         <v>585</v>
-      </c>
-      <c r="J267" t="s">
-        <v>586</v>
-      </c>
-      <c r="K267" t="s">
-        <v>586</v>
-      </c>
-      <c r="L267" t="s">
-        <v>587</v>
       </c>
       <c r="M267" t="s">
         <v>563</v>
@@ -17099,7 +17099,7 @@
         <v>48</v>
       </c>
       <c r="P267" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Q267" t="s">
         <v>47</v>
@@ -17122,28 +17122,28 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
+        <v>546</v>
+      </c>
+      <c r="F268" t="s">
+        <v>40</v>
+      </c>
+      <c r="G268" t="s">
+        <v>41</v>
+      </c>
+      <c r="H268" t="s">
+        <v>336</v>
+      </c>
+      <c r="I268" t="s">
+        <v>586</v>
+      </c>
+      <c r="J268" t="s">
+        <v>587</v>
+      </c>
+      <c r="K268" t="s">
+        <v>233</v>
+      </c>
+      <c r="L268" t="s">
         <v>588</v>
-      </c>
-      <c r="F268" t="s">
-        <v>52</v>
-      </c>
-      <c r="G268" t="s">
-        <v>41</v>
-      </c>
-      <c r="H268" t="s">
-        <v>589</v>
-      </c>
-      <c r="I268" t="s">
-        <v>590</v>
-      </c>
-      <c r="J268" t="s">
-        <v>567</v>
-      </c>
-      <c r="K268" t="s">
-        <v>119</v>
-      </c>
-      <c r="L268" t="s">
-        <v>34</v>
       </c>
       <c r="M268" t="s">
         <v>563</v>
@@ -17155,7 +17155,7 @@
         <v>48</v>
       </c>
       <c r="P268" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="Q268" t="s">
         <v>47</v>
@@ -17178,7 +17178,7 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>538</v>
+        <v>136</v>
       </c>
       <c r="F269" t="s">
         <v>40</v>
@@ -17187,19 +17187,19 @@
         <v>41</v>
       </c>
       <c r="H269" t="s">
-        <v>591</v>
+        <v>386</v>
       </c>
       <c r="I269" t="s">
         <v>557</v>
       </c>
       <c r="J269" t="s">
-        <v>541</v>
+        <v>589</v>
       </c>
       <c r="K269" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L269" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="M269" t="s">
         <v>563</v>
@@ -17243,19 +17243,19 @@
         <v>41</v>
       </c>
       <c r="H270" t="s">
+        <v>591</v>
+      </c>
+      <c r="I270" t="s">
+        <v>592</v>
+      </c>
+      <c r="J270" t="s">
+        <v>544</v>
+      </c>
+      <c r="K270" t="s">
+        <v>233</v>
+      </c>
+      <c r="L270" t="s">
         <v>593</v>
-      </c>
-      <c r="I270" t="s">
-        <v>594</v>
-      </c>
-      <c r="J270" t="s">
-        <v>541</v>
-      </c>
-      <c r="K270" t="s">
-        <v>247</v>
-      </c>
-      <c r="L270" t="s">
-        <v>595</v>
       </c>
       <c r="M270" t="s">
         <v>563</v>
@@ -17267,7 +17267,7 @@
         <v>48</v>
       </c>
       <c r="P270" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="Q270" t="s">
         <v>47</v>
@@ -17299,19 +17299,19 @@
         <v>41</v>
       </c>
       <c r="H271" t="s">
+        <v>594</v>
+      </c>
+      <c r="I271" t="s">
+        <v>595</v>
+      </c>
+      <c r="J271" t="s">
+        <v>544</v>
+      </c>
+      <c r="K271" t="s">
+        <v>233</v>
+      </c>
+      <c r="L271" t="s">
         <v>596</v>
-      </c>
-      <c r="I271" t="s">
-        <v>597</v>
-      </c>
-      <c r="J271" t="s">
-        <v>541</v>
-      </c>
-      <c r="K271" t="s">
-        <v>247</v>
-      </c>
-      <c r="L271" t="s">
-        <v>598</v>
       </c>
       <c r="M271" t="s">
         <v>563</v>
@@ -17323,7 +17323,7 @@
         <v>48</v>
       </c>
       <c r="P271" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="Q271" t="s">
         <v>47</v>
@@ -17346,28 +17346,28 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>599</v>
+        <v>538</v>
       </c>
       <c r="F272" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G272" t="s">
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>568</v>
+        <v>597</v>
       </c>
       <c r="I272" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="J272" t="s">
-        <v>60</v>
+        <v>544</v>
       </c>
       <c r="K272" t="s">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="L272" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="M272" t="s">
         <v>563</v>
@@ -17379,7 +17379,7 @@
         <v>48</v>
       </c>
       <c r="P272" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="Q272" t="s">
         <v>47</v>
@@ -17402,28 +17402,28 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>543</v>
+        <v>599</v>
       </c>
       <c r="F273" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
       </c>
       <c r="H273" t="s">
-        <v>336</v>
+        <v>600</v>
       </c>
       <c r="I273" t="s">
+        <v>601</v>
+      </c>
+      <c r="J273" t="s">
         <v>602</v>
       </c>
-      <c r="J273" t="s">
+      <c r="K273" t="s">
+        <v>602</v>
+      </c>
+      <c r="L273" t="s">
         <v>603</v>
-      </c>
-      <c r="K273" t="s">
-        <v>247</v>
-      </c>
-      <c r="L273" t="s">
-        <v>604</v>
       </c>
       <c r="M273" t="s">
         <v>563</v>
@@ -17435,7 +17435,7 @@
         <v>48</v>
       </c>
       <c r="P273" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17458,25 +17458,25 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>538</v>
+        <v>604</v>
       </c>
       <c r="F274" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G274" t="s">
         <v>41</v>
       </c>
       <c r="H274" t="s">
+        <v>580</v>
+      </c>
+      <c r="I274" t="s">
         <v>605</v>
       </c>
-      <c r="I274" t="s">
-        <v>597</v>
-      </c>
       <c r="J274" t="s">
-        <v>541</v>
+        <v>60</v>
       </c>
       <c r="K274" t="s">
-        <v>247</v>
+        <v>56</v>
       </c>
       <c r="L274" t="s">
         <v>606</v>
@@ -17491,7 +17491,7 @@
         <v>48</v>
       </c>
       <c r="P274" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="Q274" t="s">
         <v>47</v>
@@ -18083,7 +18083,7 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="I285" t="s">
         <v>630</v>
@@ -18092,7 +18092,7 @@
         <v>631</v>
       </c>
       <c r="K285" t="s">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18139,7 +18139,7 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I286" t="s">
         <v>633</v>
@@ -18148,7 +18148,7 @@
         <v>631</v>
       </c>
       <c r="K286" t="s">
-        <v>71</v>
+        <v>246</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -18425,10 +18425,10 @@
         <v>650</v>
       </c>
       <c r="J291" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K291" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L291" t="s">
         <v>651</v>
@@ -18705,10 +18705,10 @@
         <v>669</v>
       </c>
       <c r="J296" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K296" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L296" t="s">
         <v>670</v>
@@ -18873,7 +18873,7 @@
         <v>681</v>
       </c>
       <c r="J299" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K299" t="s">
         <v>682</v>
@@ -18985,10 +18985,10 @@
         <v>688</v>
       </c>
       <c r="J301" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K301" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L301" t="s">
         <v>689</v>
@@ -19100,7 +19100,7 @@
         <v>129</v>
       </c>
       <c r="K303" t="s">
-        <v>251</v>
+        <v>71</v>
       </c>
       <c r="L303" t="s">
         <v>696</v>
@@ -19141,25 +19141,25 @@
         <v>697</v>
       </c>
       <c r="F304" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G304" t="s">
         <v>41</v>
       </c>
       <c r="H304" t="s">
+        <v>42</v>
+      </c>
+      <c r="I304" t="s">
         <v>698</v>
       </c>
-      <c r="I304" t="s">
+      <c r="J304" t="s">
+        <v>246</v>
+      </c>
+      <c r="K304" t="s">
+        <v>246</v>
+      </c>
+      <c r="L304" t="s">
         <v>699</v>
-      </c>
-      <c r="J304" t="s">
-        <v>129</v>
-      </c>
-      <c r="K304" t="s">
-        <v>71</v>
-      </c>
-      <c r="L304" t="s">
-        <v>700</v>
       </c>
       <c r="M304" t="s">
         <v>692</v>
@@ -19171,7 +19171,7 @@
         <v>48</v>
       </c>
       <c r="P304" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="Q304" t="s">
         <v>47</v>
@@ -19194,25 +19194,25 @@
         <v>34</v>
       </c>
       <c r="E305" t="s">
+        <v>700</v>
+      </c>
+      <c r="F305" t="s">
+        <v>52</v>
+      </c>
+      <c r="G305" t="s">
+        <v>41</v>
+      </c>
+      <c r="H305" t="s">
         <v>701</v>
-      </c>
-      <c r="F305" t="s">
-        <v>40</v>
-      </c>
-      <c r="G305" t="s">
-        <v>41</v>
-      </c>
-      <c r="H305" t="s">
-        <v>42</v>
       </c>
       <c r="I305" t="s">
         <v>702</v>
       </c>
       <c r="J305" t="s">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="K305" t="s">
-        <v>240</v>
+        <v>115</v>
       </c>
       <c r="L305" t="s">
         <v>703</v>
@@ -19268,10 +19268,10 @@
         <v>129</v>
       </c>
       <c r="K306" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L306" t="s">
-        <v>34</v>
+        <v>707</v>
       </c>
       <c r="M306" t="s">
         <v>692</v>
@@ -19306,7 +19306,7 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F307" t="s">
         <v>52</v>
@@ -19315,19 +19315,19 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I307" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="J307" t="s">
         <v>129</v>
       </c>
       <c r="K307" t="s">
-        <v>115</v>
+        <v>241</v>
       </c>
       <c r="L307" t="s">
-        <v>710</v>
+        <v>34</v>
       </c>
       <c r="M307" t="s">
         <v>692</v>
@@ -19339,7 +19339,7 @@
         <v>48</v>
       </c>
       <c r="P307" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Q307" t="s">
         <v>47</v>
@@ -19433,10 +19433,10 @@
         <v>716</v>
       </c>
       <c r="J309" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K309" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L309" t="s">
         <v>717</v>
@@ -19548,7 +19548,7 @@
         <v>44</v>
       </c>
       <c r="K311" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L311" t="s">
         <v>727</v>
@@ -19657,10 +19657,10 @@
         <v>734</v>
       </c>
       <c r="J313" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K313" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L313" t="s">
         <v>733</v>
@@ -19713,10 +19713,10 @@
         <v>736</v>
       </c>
       <c r="J314" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="K314" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L314" t="s">
         <v>737</v>
@@ -19754,7 +19754,7 @@
         <v>34</v>
       </c>
       <c r="E315" t="s">
-        <v>538</v>
+        <v>738</v>
       </c>
       <c r="F315" t="s">
         <v>40</v>
@@ -19766,16 +19766,16 @@
         <v>727</v>
       </c>
       <c r="I315" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J315" t="s">
-        <v>246</v>
+        <v>740</v>
       </c>
       <c r="K315" t="s">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="L315" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="M315" t="s">
         <v>731</v>
@@ -19787,7 +19787,7 @@
         <v>48</v>
       </c>
       <c r="P315" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -19810,7 +19810,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>740</v>
+        <v>538</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -19822,13 +19822,13 @@
         <v>727</v>
       </c>
       <c r="I316" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="J316" t="s">
-        <v>742</v>
+        <v>232</v>
       </c>
       <c r="K316" t="s">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="L316" t="s">
         <v>743</v>
@@ -19843,7 +19843,7 @@
         <v>48</v>
       </c>
       <c r="P316" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -19937,10 +19937,10 @@
         <v>749</v>
       </c>
       <c r="J318" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K318" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L318" t="s">
         <v>750</v>
@@ -20161,10 +20161,10 @@
         <v>766</v>
       </c>
       <c r="J322" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K322" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L322" t="s">
         <v>767</v>
@@ -20329,7 +20329,7 @@
         <v>779</v>
       </c>
       <c r="J325" t="s">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="K325" t="s">
         <v>124</v>
@@ -20441,10 +20441,10 @@
         <v>787</v>
       </c>
       <c r="J327" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="K327" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L327" t="s">
         <v>788</v>
@@ -20497,10 +20497,10 @@
         <v>792</v>
       </c>
       <c r="J328" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="K328" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="L328" t="s">
         <v>793</v>
@@ -20650,7 +20650,7 @@
         <v>33</v>
       </c>
       <c r="E331" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F331" t="s">
         <v>40</v>

--- a/xlsx/dre/DRE_04_2026.xlsx
+++ b/xlsx/dre/DRE_04_2026.xlsx
@@ -705,6 +705,53 @@
     <t>R$ 2.125,39</t>
   </si>
   <si>
+    <t>637/1</t>
+  </si>
+  <si>
+    <t>FERRAGENS FLORESTA EIRELI EPP</t>
+  </si>
+  <si>
+    <t>R$  209,68</t>
+  </si>
+  <si>
+    <t>15/05/26</t>
+  </si>
+  <si>
+    <t>estoque</t>
+  </si>
+  <si>
+    <t>633/1</t>
+  </si>
+  <si>
+    <t>R$  205,50</t>
+  </si>
+  <si>
+    <t>632/1</t>
+  </si>
+  <si>
+    <t>Leo Madeiras</t>
+  </si>
+  <si>
+    <t>R$  284,50</t>
+  </si>
+  <si>
+    <t>01/04/26</t>
+  </si>
+  <si>
+    <t>642/1</t>
+  </si>
+  <si>
+    <t>R$  720,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor	Fornecedor	Descrição
+189	Mercado livre	caixa de tomada cliente erro Antônio
+144,36	Mercado Livre	mini rodízio estoque
+153,6	Mercado Livre	rodízios estoque
+234	Mercado Livre	caixas Bin estoque
+</t>
+  </si>
+  <si>
     <t>9/4</t>
   </si>
   <si>
@@ -718,18 +765,6 @@
   </si>
   <si>
     <t>Grapa</t>
-  </si>
-  <si>
-    <t>633/1</t>
-  </si>
-  <si>
-    <t>FERRAGENS FLORESTA EIRELI EPP</t>
-  </si>
-  <si>
-    <t>R$  205,50</t>
-  </si>
-  <si>
-    <t>estoque</t>
   </si>
   <si>
     <t>649/1</t>
@@ -750,41 +785,6 @@
 </t>
   </si>
   <si>
-    <t>632/1</t>
-  </si>
-  <si>
-    <t>Leo Madeiras</t>
-  </si>
-  <si>
-    <t>R$  284,50</t>
-  </si>
-  <si>
-    <t>01/04/26</t>
-  </si>
-  <si>
-    <t>642/1</t>
-  </si>
-  <si>
-    <t>R$  720,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor	Fornecedor	Descrição
-189	Mercado livre	caixa de tomada cliente erro Antônio
-144,36	Mercado Livre	mini rodízio estoque
-153,6	Mercado Livre	rodízios estoque
-234	Mercado Livre	caixas Bin estoque
-</t>
-  </si>
-  <si>
-    <t>637/1</t>
-  </si>
-  <si>
-    <t>R$  209,68</t>
-  </si>
-  <si>
-    <t>15/05/26</t>
-  </si>
-  <si>
     <t>4.02.02 CUSTO DE TRANSPORTE</t>
   </si>
   <si>
@@ -1040,36 +1040,36 @@
     <t>FELIPE DOMINGOS BARBOSA</t>
   </si>
   <si>
+    <t>R$  272,79</t>
+  </si>
+  <si>
+    <t>R$  277,04</t>
+  </si>
+  <si>
+    <t>R$  119,03</t>
+  </si>
+  <si>
+    <t>R$  424,54</t>
+  </si>
+  <si>
+    <t>R$  504,92</t>
+  </si>
+  <si>
+    <t>R$  758,34</t>
+  </si>
+  <si>
+    <t>R$  1.333,55</t>
+  </si>
+  <si>
+    <t>R$  401,21</t>
+  </si>
+  <si>
+    <t>R$  404,69</t>
+  </si>
+  <si>
     <t>R$  417,35</t>
   </si>
   <si>
-    <t>R$  272,79</t>
-  </si>
-  <si>
-    <t>R$  277,04</t>
-  </si>
-  <si>
-    <t>R$  119,03</t>
-  </si>
-  <si>
-    <t>R$  424,54</t>
-  </si>
-  <si>
-    <t>R$  504,92</t>
-  </si>
-  <si>
-    <t>R$  758,34</t>
-  </si>
-  <si>
-    <t>R$  1.333,55</t>
-  </si>
-  <si>
-    <t>R$  401,21</t>
-  </si>
-  <si>
-    <t>R$  404,69</t>
-  </si>
-  <si>
     <t>4.03.01.02.02 Comissões vendas</t>
   </si>
   <si>
@@ -1187,9 +1187,27 @@
     <t>R$ 5.521,58</t>
   </si>
   <si>
+    <t>RAYSSA BARBOSA LEMOS</t>
+  </si>
+  <si>
+    <t>R$  758,36</t>
+  </si>
+  <si>
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
+    <t>01/06/26</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>R$  1.333,58</t>
+  </si>
+  <si>
+    <t>06/02/26</t>
+  </si>
+  <si>
     <t>R$  404,67</t>
   </si>
   <si>
@@ -1199,18 +1217,6 @@
     <t>R$  424,52</t>
   </si>
   <si>
-    <t>Rubens Felipe de Siqueira Costa</t>
-  </si>
-  <si>
-    <t>R$  1.333,58</t>
-  </si>
-  <si>
-    <t>06/02/26</t>
-  </si>
-  <si>
-    <t>01/06/26</t>
-  </si>
-  <si>
     <t>R$  401,23</t>
   </si>
   <si>
@@ -1226,12 +1232,6 @@
     <t>23801AndersonLS</t>
   </si>
   <si>
-    <t>RAYSSA BARBOSA LEMOS</t>
-  </si>
-  <si>
-    <t>R$  758,36</t>
-  </si>
-  <si>
     <t>4.03.01.02.08 Comissões montagem - provisão</t>
   </si>
   <si>
@@ -1337,12 +1337,12 @@
     <t>DSR abr26/1</t>
   </si>
   <si>
+    <t>R$  549,59</t>
+  </si>
+  <si>
     <t>R$  736,46</t>
   </si>
   <si>
-    <t>R$  549,59</t>
-  </si>
-  <si>
     <t>4.03.03 GASTOS GERAIS COM VENDAS</t>
   </si>
   <si>
@@ -1559,21 +1559,21 @@
     <t>R$ 277,65</t>
   </si>
   <si>
+    <t>5/2</t>
+  </si>
+  <si>
+    <t>R$  92,55</t>
+  </si>
+  <si>
+    <t>Mercado Livre</t>
+  </si>
+  <si>
+    <t>5/3</t>
+  </si>
+  <si>
     <t>5/1</t>
   </si>
   <si>
-    <t>R$  92,55</t>
-  </si>
-  <si>
-    <t>Mercado Livre</t>
-  </si>
-  <si>
-    <t>5/3</t>
-  </si>
-  <si>
-    <t>5/2</t>
-  </si>
-  <si>
     <t>4.03.03.02.05 Assistência técnica - custo loja</t>
   </si>
   <si>
@@ -1604,24 +1604,24 @@
     <t>4.03.03.08.01 Brindes para clientes (CV)</t>
   </si>
   <si>
+    <t>2/2</t>
+  </si>
+  <si>
+    <t>Licoretto Bebidas</t>
+  </si>
+  <si>
+    <t>R$  79,98</t>
+  </si>
+  <si>
+    <t>Brindes clientes</t>
+  </si>
+  <si>
+    <t>2/1</t>
+  </si>
+  <si>
     <t>2/3</t>
   </si>
   <si>
-    <t>Licoretto Bebidas</t>
-  </si>
-  <si>
-    <t>R$  79,98</t>
-  </si>
-  <si>
-    <t>Brindes clientes</t>
-  </si>
-  <si>
-    <t>2/1</t>
-  </si>
-  <si>
-    <t>2/2</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -1646,6 +1646,30 @@
     <t>12/4</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>1/2</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>03/02/26</t>
+  </si>
+  <si>
+    <t>Facebook 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -1655,30 +1679,6 @@
     <t>Google 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
-    <t>1/2</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>03/02/26</t>
-  </si>
-  <si>
-    <t>Facebook 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -1721,6 +1721,78 @@
     <t>4.04.01.02.01.01 Salário fixo</t>
   </si>
   <si>
+    <t>658/1</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>07/05/26</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.422,07</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>R$  2.536,00</t>
+  </si>
+  <si>
+    <t>19/02/26</t>
+  </si>
+  <si>
+    <t>Bianca Rodrigues - Salário fixo 2026</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>19/04/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>627/1</t>
+  </si>
+  <si>
+    <t>Leandro Henrique Simoes Campos</t>
+  </si>
+  <si>
+    <t>R$  566,67</t>
+  </si>
+  <si>
+    <t>24/04/26</t>
+  </si>
+  <si>
+    <t>17 dias</t>
+  </si>
+  <si>
     <t>659/1</t>
   </si>
   <si>
@@ -1730,61 +1802,37 @@
     <t>R$  1.287,09</t>
   </si>
   <si>
-    <t>07/05/26</t>
-  </si>
-  <si>
-    <t>658/1</t>
-  </si>
-  <si>
-    <t>EFRAIM RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>R$  2.536,00</t>
-  </si>
-  <si>
-    <t>19/02/26</t>
-  </si>
-  <si>
-    <t>Bianca Rodrigues - Salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>19/04/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
     <t>Teresinha Elvira Maximino de Menezes</t>
   </si>
   <si>
     <t>Tucha - Fixo 2026</t>
   </si>
   <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.422,07</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.795,57</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Danielle Martins da Silva</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Danielle - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>616/1</t>
+  </si>
+  <si>
+    <t>R$  241,20</t>
+  </si>
+  <si>
+    <t>Reajuste dissidio</t>
   </si>
   <si>
     <t>R$  2.219,85</t>
@@ -1796,60 +1844,12 @@
     <t>Felipe Domingos - salário fixo 2026</t>
   </si>
   <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
     <t>CARINA PEREIRA</t>
   </si>
   <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
     <t>Carina - Pagamento 2026</t>
   </si>
   <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.795,57</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Danielle Martins da Silva</t>
-  </si>
-  <si>
-    <t>Danielle - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>627/1</t>
-  </si>
-  <si>
-    <t>Leandro Henrique Simoes Campos</t>
-  </si>
-  <si>
-    <t>R$  566,67</t>
-  </si>
-  <si>
-    <t>24/04/26</t>
-  </si>
-  <si>
-    <t>17 dias</t>
-  </si>
-  <si>
-    <t>616/1</t>
-  </si>
-  <si>
-    <t>R$  241,20</t>
-  </si>
-  <si>
-    <t>Reajuste dissidio</t>
-  </si>
-  <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
   </si>
   <si>
@@ -1916,19 +1916,19 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT abr26/4</t>
+  </si>
+  <si>
+    <t>R$  411,36</t>
+  </si>
+  <si>
+    <t>31/03/26</t>
+  </si>
+  <si>
     <t>VT abr26/1</t>
   </si>
   <si>
     <t>R$  290,65</t>
-  </si>
-  <si>
-    <t>31/03/26</t>
-  </si>
-  <si>
-    <t>VT abr26/4</t>
-  </si>
-  <si>
-    <t>R$  411,36</t>
   </si>
   <si>
     <t>4.04.01.07 Uniformes e crachás</t>
@@ -2110,6 +2110,18 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
+    <t>646/1</t>
+  </si>
+  <si>
+    <t>Oxxo</t>
+  </si>
+  <si>
+    <t>R$  90,07</t>
+  </si>
+  <si>
+    <t>Cafés loja</t>
+  </si>
+  <si>
     <t>644/1</t>
   </si>
   <si>
@@ -2129,6 +2141,15 @@
   </si>
   <si>
     <t>Envelope</t>
+  </si>
+  <si>
+    <t>648/1</t>
+  </si>
+  <si>
+    <t>Chaveiro Rouxinol</t>
+  </si>
+  <si>
+    <t>R$  90,00</t>
   </si>
   <si>
     <t>643/1</t>
@@ -2147,27 +2168,6 @@
 </t>
   </si>
   <si>
-    <t>646/1</t>
-  </si>
-  <si>
-    <t>Oxxo</t>
-  </si>
-  <si>
-    <t>R$  90,07</t>
-  </si>
-  <si>
-    <t>Cafés loja</t>
-  </si>
-  <si>
-    <t>648/1</t>
-  </si>
-  <si>
-    <t>Chaveiro Rouxinol</t>
-  </si>
-  <si>
-    <t>R$  90,00</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2249,6 +2249,12 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>3/3</t>
   </si>
   <si>
@@ -2259,12 +2265,6 @@
   </si>
   <si>
     <t>Promob 2026/2</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -6373,22 +6373,22 @@
         <v>230</v>
       </c>
       <c r="F76" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G76" t="s">
         <v>41</v>
       </c>
       <c r="H76" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="I76" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K76" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="L76" t="s">
         <v>234</v>
@@ -6403,7 +6403,7 @@
         <v>48</v>
       </c>
       <c r="P76" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q76" t="s">
         <v>47</v>
@@ -6435,10 +6435,10 @@
         <v>41</v>
       </c>
       <c r="H77" t="s">
+        <v>231</v>
+      </c>
+      <c r="I77" t="s">
         <v>236</v>
-      </c>
-      <c r="I77" t="s">
-        <v>237</v>
       </c>
       <c r="J77" t="s">
         <v>119</v>
@@ -6447,7 +6447,7 @@
         <v>119</v>
       </c>
       <c r="L77" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="M77" t="s">
         <v>228</v>
@@ -6459,7 +6459,7 @@
         <v>48</v>
       </c>
       <c r="P77" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q77" t="s">
         <v>47</v>
@@ -6482,7 +6482,7 @@
         <v>34</v>
       </c>
       <c r="E78" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F78" t="s">
         <v>52</v>
@@ -6491,19 +6491,19 @@
         <v>41</v>
       </c>
       <c r="H78" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="I78" t="s">
+        <v>239</v>
+      </c>
+      <c r="J78" t="s">
+        <v>114</v>
+      </c>
+      <c r="K78" t="s">
         <v>240</v>
       </c>
-      <c r="J78" t="s">
-        <v>129</v>
-      </c>
-      <c r="K78" t="s">
-        <v>241</v>
-      </c>
       <c r="L78" t="s">
-        <v>242</v>
+        <v>34</v>
       </c>
       <c r="M78" t="s">
         <v>228</v>
@@ -6515,7 +6515,7 @@
         <v>48</v>
       </c>
       <c r="P78" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q78" t="s">
         <v>47</v>
@@ -6538,7 +6538,7 @@
         <v>34</v>
       </c>
       <c r="E79" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F79" t="s">
         <v>52</v>
@@ -6547,19 +6547,19 @@
         <v>41</v>
       </c>
       <c r="H79" t="s">
-        <v>244</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J79" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="K79" t="s">
-        <v>246</v>
+        <v>71</v>
       </c>
       <c r="L79" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="M79" t="s">
         <v>228</v>
@@ -6571,7 +6571,7 @@
         <v>48</v>
       </c>
       <c r="P79" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Q79" t="s">
         <v>47</v>
@@ -6594,10 +6594,10 @@
         <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F80" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G80" t="s">
         <v>41</v>
@@ -6606,16 +6606,16 @@
         <v>42</v>
       </c>
       <c r="I80" t="s">
+        <v>245</v>
+      </c>
+      <c r="J80" t="s">
+        <v>246</v>
+      </c>
+      <c r="K80" t="s">
+        <v>247</v>
+      </c>
+      <c r="L80" t="s">
         <v>248</v>
-      </c>
-      <c r="J80" t="s">
-        <v>129</v>
-      </c>
-      <c r="K80" t="s">
-        <v>71</v>
-      </c>
-      <c r="L80" t="s">
-        <v>249</v>
       </c>
       <c r="M80" t="s">
         <v>228</v>
@@ -6627,7 +6627,7 @@
         <v>48</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q80" t="s">
         <v>47</v>
@@ -6650,7 +6650,7 @@
         <v>34</v>
       </c>
       <c r="E81" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F81" t="s">
         <v>52</v>
@@ -6659,19 +6659,19 @@
         <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>236</v>
+        <v>42</v>
       </c>
       <c r="I81" t="s">
+        <v>250</v>
+      </c>
+      <c r="J81" t="s">
+        <v>129</v>
+      </c>
+      <c r="K81" t="s">
         <v>251</v>
       </c>
-      <c r="J81" t="s">
+      <c r="L81" t="s">
         <v>252</v>
-      </c>
-      <c r="K81" t="s">
-        <v>88</v>
-      </c>
-      <c r="L81" t="s">
-        <v>238</v>
       </c>
       <c r="M81" t="s">
         <v>228</v>
@@ -6683,7 +6683,7 @@
         <v>48</v>
       </c>
       <c r="P81" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q81" t="s">
         <v>47</v>
@@ -9226,7 +9226,7 @@
         <v>33</v>
       </c>
       <c r="E127" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="F127" t="s">
         <v>183</v>
@@ -9244,7 +9244,7 @@
         <v>129</v>
       </c>
       <c r="K127" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="L127" t="s">
         <v>34</v>
@@ -9256,7 +9256,7 @@
         <v>47</v>
       </c>
       <c r="O127" t="s">
-        <v>213</v>
+        <v>292</v>
       </c>
       <c r="P127" t="s">
         <v>337</v>
@@ -9282,7 +9282,7 @@
         <v>34</v>
       </c>
       <c r="E128" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F128" t="s">
         <v>183</v>
@@ -9300,7 +9300,7 @@
         <v>129</v>
       </c>
       <c r="K128" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="L128" t="s">
         <v>34</v>
@@ -9312,7 +9312,7 @@
         <v>47</v>
       </c>
       <c r="O128" t="s">
-        <v>292</v>
+        <v>72</v>
       </c>
       <c r="P128" t="s">
         <v>338</v>
@@ -9338,7 +9338,7 @@
         <v>34</v>
       </c>
       <c r="E129" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F129" t="s">
         <v>183</v>
@@ -9368,7 +9368,7 @@
         <v>47</v>
       </c>
       <c r="O129" t="s">
-        <v>72</v>
+        <v>305</v>
       </c>
       <c r="P129" t="s">
         <v>339</v>
@@ -9394,7 +9394,7 @@
         <v>34</v>
       </c>
       <c r="E130" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F130" t="s">
         <v>183</v>
@@ -9412,7 +9412,7 @@
         <v>129</v>
       </c>
       <c r="K130" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="L130" t="s">
         <v>34</v>
@@ -9424,7 +9424,7 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="P130" t="s">
         <v>340</v>
@@ -9450,7 +9450,7 @@
         <v>34</v>
       </c>
       <c r="E131" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F131" t="s">
         <v>183</v>
@@ -9468,7 +9468,7 @@
         <v>129</v>
       </c>
       <c r="K131" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="L131" t="s">
         <v>34</v>
@@ -9480,7 +9480,7 @@
         <v>47</v>
       </c>
       <c r="O131" t="s">
-        <v>287</v>
+        <v>104</v>
       </c>
       <c r="P131" t="s">
         <v>341</v>
@@ -9506,7 +9506,7 @@
         <v>34</v>
       </c>
       <c r="E132" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="F132" t="s">
         <v>183</v>
@@ -9524,7 +9524,7 @@
         <v>129</v>
       </c>
       <c r="K132" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="L132" t="s">
         <v>34</v>
@@ -9536,7 +9536,7 @@
         <v>47</v>
       </c>
       <c r="O132" t="s">
-        <v>104</v>
+        <v>292</v>
       </c>
       <c r="P132" t="s">
         <v>342</v>
@@ -9562,7 +9562,7 @@
         <v>34</v>
       </c>
       <c r="E133" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F133" t="s">
         <v>183</v>
@@ -9580,7 +9580,7 @@
         <v>129</v>
       </c>
       <c r="K133" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="L133" t="s">
         <v>34</v>
@@ -9592,7 +9592,7 @@
         <v>47</v>
       </c>
       <c r="O133" t="s">
-        <v>292</v>
+        <v>188</v>
       </c>
       <c r="P133" t="s">
         <v>343</v>
@@ -9618,7 +9618,7 @@
         <v>34</v>
       </c>
       <c r="E134" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F134" t="s">
         <v>183</v>
@@ -9648,7 +9648,7 @@
         <v>47</v>
       </c>
       <c r="O134" t="s">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="P134" t="s">
         <v>344</v>
@@ -9674,7 +9674,7 @@
         <v>34</v>
       </c>
       <c r="E135" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="F135" t="s">
         <v>183</v>
@@ -9692,7 +9692,7 @@
         <v>129</v>
       </c>
       <c r="K135" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L135" t="s">
         <v>34</v>
@@ -9704,7 +9704,7 @@
         <v>47</v>
       </c>
       <c r="O135" t="s">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="P135" t="s">
         <v>345</v>
@@ -9730,7 +9730,7 @@
         <v>34</v>
       </c>
       <c r="E136" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F136" t="s">
         <v>183</v>
@@ -9748,7 +9748,7 @@
         <v>129</v>
       </c>
       <c r="K136" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L136" t="s">
         <v>34</v>
@@ -9760,7 +9760,7 @@
         <v>47</v>
       </c>
       <c r="O136" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="P136" t="s">
         <v>346</v>
@@ -10750,7 +10750,7 @@
         <v>369</v>
       </c>
       <c r="I154" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J154" t="s">
         <v>129</v>
@@ -10771,7 +10771,7 @@
         <v>305</v>
       </c>
       <c r="P154" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q154" t="s">
         <v>47</v>
@@ -10806,7 +10806,7 @@
         <v>369</v>
       </c>
       <c r="I155" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J155" t="s">
         <v>129</v>
@@ -10827,7 +10827,7 @@
         <v>72</v>
       </c>
       <c r="P155" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q155" t="s">
         <v>47</v>
@@ -10862,7 +10862,7 @@
         <v>369</v>
       </c>
       <c r="I156" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J156" t="s">
         <v>129</v>
@@ -10883,7 +10883,7 @@
         <v>96</v>
       </c>
       <c r="P156" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q156" t="s">
         <v>47</v>
@@ -10974,7 +10974,7 @@
         <v>369</v>
       </c>
       <c r="I158" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J158" t="s">
         <v>129</v>
@@ -10995,7 +10995,7 @@
         <v>77</v>
       </c>
       <c r="P158" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q158" t="s">
         <v>47</v>
@@ -11030,7 +11030,7 @@
         <v>369</v>
       </c>
       <c r="I159" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J159" t="s">
         <v>129</v>
@@ -11051,7 +11051,7 @@
         <v>209</v>
       </c>
       <c r="P159" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q159" t="s">
         <v>47</v>
@@ -11086,7 +11086,7 @@
         <v>369</v>
       </c>
       <c r="I160" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="J160" t="s">
         <v>129</v>
@@ -11107,7 +11107,7 @@
         <v>213</v>
       </c>
       <c r="P160" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="Q160" t="s">
         <v>47</v>
@@ -11142,7 +11142,7 @@
         <v>369</v>
       </c>
       <c r="I161" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J161" t="s">
         <v>129</v>
@@ -11163,7 +11163,7 @@
         <v>287</v>
       </c>
       <c r="P161" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q161" t="s">
         <v>47</v>
@@ -11198,7 +11198,7 @@
         <v>369</v>
       </c>
       <c r="I162" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J162" t="s">
         <v>129</v>
@@ -11219,7 +11219,7 @@
         <v>104</v>
       </c>
       <c r="P162" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q162" t="s">
         <v>47</v>
@@ -11254,7 +11254,7 @@
         <v>369</v>
       </c>
       <c r="I163" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J163" t="s">
         <v>129</v>
@@ -11275,7 +11275,7 @@
         <v>292</v>
       </c>
       <c r="P163" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q163" t="s">
         <v>47</v>
@@ -11310,7 +11310,7 @@
         <v>369</v>
       </c>
       <c r="I164" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J164" t="s">
         <v>129</v>
@@ -11331,7 +11331,7 @@
         <v>188</v>
       </c>
       <c r="P164" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q164" t="s">
         <v>47</v>
@@ -11858,10 +11858,10 @@
         <v>33</v>
       </c>
       <c r="E174" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="F174" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="G174" t="s">
         <v>41</v>
@@ -11873,10 +11873,10 @@
         <v>387</v>
       </c>
       <c r="J174" t="s">
-        <v>388</v>
+        <v>119</v>
       </c>
       <c r="K174" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="L174" t="s">
         <v>34</v>
@@ -11888,7 +11888,7 @@
         <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>209</v>
+        <v>292</v>
       </c>
       <c r="P174" t="s">
         <v>387</v>
@@ -11914,7 +11914,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F175" t="s">
         <v>183</v>
@@ -11923,16 +11923,16 @@
         <v>41</v>
       </c>
       <c r="H175" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I175" t="s">
+        <v>370</v>
+      </c>
+      <c r="J175" t="s">
         <v>389</v>
       </c>
-      <c r="J175" t="s">
-        <v>388</v>
-      </c>
       <c r="K175" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -11944,10 +11944,10 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>287</v>
+        <v>120</v>
       </c>
       <c r="P175" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="Q175" t="s">
         <v>47</v>
@@ -11970,7 +11970,7 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F176" t="s">
         <v>183</v>
@@ -11979,16 +11979,16 @@
         <v>41</v>
       </c>
       <c r="H176" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I176" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="J176" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K176" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -12000,10 +12000,10 @@
         <v>47</v>
       </c>
       <c r="O176" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="P176" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="Q176" t="s">
         <v>47</v>
@@ -12026,7 +12026,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="F177" t="s">
         <v>183</v>
@@ -12035,16 +12035,16 @@
         <v>41</v>
       </c>
       <c r="H177" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I177" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="J177" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="K177" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -12056,10 +12056,10 @@
         <v>47</v>
       </c>
       <c r="O177" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="Q177" t="s">
         <v>47</v>
@@ -12082,7 +12082,7 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F178" t="s">
         <v>183</v>
@@ -12091,16 +12091,16 @@
         <v>41</v>
       </c>
       <c r="H178" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="I178" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="J178" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K178" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -12112,10 +12112,10 @@
         <v>47</v>
       </c>
       <c r="O178" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="P178" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="Q178" t="s">
         <v>47</v>
@@ -12138,7 +12138,7 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F179" t="s">
         <v>183</v>
@@ -12147,16 +12147,16 @@
         <v>41</v>
       </c>
       <c r="H179" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I179" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="J179" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K179" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12168,10 +12168,10 @@
         <v>47</v>
       </c>
       <c r="O179" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P179" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="Q179" t="s">
         <v>47</v>
@@ -12194,7 +12194,7 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F180" t="s">
         <v>183</v>
@@ -12203,16 +12203,16 @@
         <v>41</v>
       </c>
       <c r="H180" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I180" t="s">
+        <v>395</v>
+      </c>
+      <c r="J180" t="s">
         <v>394</v>
       </c>
-      <c r="J180" t="s">
-        <v>129</v>
-      </c>
       <c r="K180" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12224,10 +12224,10 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="P180" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q180" t="s">
         <v>47</v>
@@ -12250,7 +12250,7 @@
         <v>34</v>
       </c>
       <c r="E181" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F181" t="s">
         <v>183</v>
@@ -12259,16 +12259,16 @@
         <v>41</v>
       </c>
       <c r="H181" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="I181" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J181" t="s">
         <v>129</v>
       </c>
       <c r="K181" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="L181" t="s">
         <v>34</v>
@@ -12280,10 +12280,10 @@
         <v>47</v>
       </c>
       <c r="O181" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P181" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q181" t="s">
         <v>47</v>
@@ -12306,7 +12306,7 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>396</v>
+        <v>195</v>
       </c>
       <c r="F182" t="s">
         <v>183</v>
@@ -12315,7 +12315,7 @@
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I182" t="s">
         <v>397</v>
@@ -12324,7 +12324,7 @@
         <v>129</v>
       </c>
       <c r="K182" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12336,7 +12336,7 @@
         <v>47</v>
       </c>
       <c r="O182" t="s">
-        <v>398</v>
+        <v>72</v>
       </c>
       <c r="P182" t="s">
         <v>397</v>
@@ -12362,25 +12362,25 @@
         <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>182</v>
+        <v>398</v>
       </c>
       <c r="F183" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="G183" t="s">
         <v>41</v>
       </c>
       <c r="H183" t="s">
+        <v>390</v>
+      </c>
+      <c r="I183" t="s">
         <v>399</v>
       </c>
-      <c r="I183" t="s">
-        <v>400</v>
-      </c>
       <c r="J183" t="s">
+        <v>129</v>
+      </c>
+      <c r="K183" t="s">
         <v>119</v>
-      </c>
-      <c r="K183" t="s">
-        <v>83</v>
       </c>
       <c r="L183" t="s">
         <v>34</v>
@@ -12392,10 +12392,10 @@
         <v>47</v>
       </c>
       <c r="O183" t="s">
-        <v>292</v>
+        <v>400</v>
       </c>
       <c r="P183" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q183" t="s">
         <v>47</v>
@@ -12881,7 +12881,7 @@
         <v>421</v>
       </c>
       <c r="J192" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="K192" t="s">
         <v>125</v>
@@ -12937,7 +12937,7 @@
         <v>419</v>
       </c>
       <c r="J193" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="K193" t="s">
         <v>125</v>
@@ -13379,16 +13379,16 @@
         <v>41</v>
       </c>
       <c r="H201" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I201" t="s">
         <v>436</v>
       </c>
       <c r="J201" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K201" t="s">
-        <v>246</v>
+        <v>89</v>
       </c>
       <c r="L201" t="s">
         <v>34</v>
@@ -13435,16 +13435,16 @@
         <v>41</v>
       </c>
       <c r="H202" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="I202" t="s">
         <v>437</v>
       </c>
       <c r="J202" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K202" t="s">
-        <v>89</v>
+        <v>240</v>
       </c>
       <c r="L202" t="s">
         <v>34</v>
@@ -13948,7 +13948,7 @@
         <v>129</v>
       </c>
       <c r="K211" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="L211" t="s">
         <v>458</v>
@@ -15009,10 +15009,10 @@
         <v>511</v>
       </c>
       <c r="J230" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K230" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L230" t="s">
         <v>512</v>
@@ -15065,10 +15065,10 @@
         <v>511</v>
       </c>
       <c r="J231" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K231" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L231" t="s">
         <v>512</v>
@@ -15121,10 +15121,10 @@
         <v>511</v>
       </c>
       <c r="J232" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K232" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L232" t="s">
         <v>512</v>
@@ -15274,7 +15274,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F235" t="s">
         <v>40</v>
@@ -15289,10 +15289,10 @@
         <v>519</v>
       </c>
       <c r="J235" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="K235" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15304,7 +15304,7 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="P235" t="s">
         <v>519</v>
@@ -15330,7 +15330,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F236" t="s">
         <v>40</v>
@@ -15345,10 +15345,10 @@
         <v>519</v>
       </c>
       <c r="J236" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="K236" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15360,7 +15360,7 @@
         <v>47</v>
       </c>
       <c r="O236" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="P236" t="s">
         <v>519</v>
@@ -15386,7 +15386,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="F237" t="s">
         <v>40</v>
@@ -15401,10 +15401,10 @@
         <v>519</v>
       </c>
       <c r="J237" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K237" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L237" t="s">
         <v>34</v>
@@ -15416,7 +15416,7 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="P237" t="s">
         <v>519</v>
@@ -15442,7 +15442,7 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F238" t="s">
         <v>40</v>
@@ -15457,10 +15457,10 @@
         <v>519</v>
       </c>
       <c r="J238" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K238" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15472,7 +15472,7 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P238" t="s">
         <v>519</v>
@@ -15498,7 +15498,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="F239" t="s">
         <v>40</v>
@@ -15510,13 +15510,13 @@
         <v>518</v>
       </c>
       <c r="I239" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J239" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="K239" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15528,10 +15528,10 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="P239" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q239" t="s">
         <v>47</v>
@@ -15554,7 +15554,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F240" t="s">
         <v>40</v>
@@ -15569,10 +15569,10 @@
         <v>519</v>
       </c>
       <c r="J240" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="K240" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15584,7 +15584,7 @@
         <v>47</v>
       </c>
       <c r="O240" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="P240" t="s">
         <v>519</v>
@@ -15610,7 +15610,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F241" t="s">
         <v>40</v>
@@ -15622,13 +15622,13 @@
         <v>518</v>
       </c>
       <c r="I241" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J241" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K241" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15640,10 +15640,10 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>287</v>
+        <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q241" t="s">
         <v>47</v>
@@ -15666,10 +15666,10 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F242" t="s">
-        <v>40</v>
+        <v>521</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
@@ -15681,10 +15681,10 @@
         <v>519</v>
       </c>
       <c r="J242" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="K242" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -15696,13 +15696,13 @@
         <v>47</v>
       </c>
       <c r="O242" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="P242" t="s">
-        <v>519</v>
+        <v>34</v>
       </c>
       <c r="Q242" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15778,10 +15778,10 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F244" t="s">
-        <v>521</v>
+        <v>40</v>
       </c>
       <c r="G244" t="s">
         <v>41</v>
@@ -15793,10 +15793,10 @@
         <v>519</v>
       </c>
       <c r="J244" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="K244" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -15808,13 +15808,13 @@
         <v>47</v>
       </c>
       <c r="O244" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="P244" t="s">
-        <v>34</v>
+        <v>519</v>
       </c>
       <c r="Q244" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R244" t="s">
         <v>34</v>
@@ -15905,10 +15905,10 @@
         <v>527</v>
       </c>
       <c r="J246" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K246" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L246" t="s">
         <v>528</v>
@@ -15961,10 +15961,10 @@
         <v>527</v>
       </c>
       <c r="J247" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K247" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L247" t="s">
         <v>528</v>
@@ -16017,10 +16017,10 @@
         <v>527</v>
       </c>
       <c r="J248" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K248" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L248" t="s">
         <v>528</v>
@@ -16185,13 +16185,13 @@
         <v>540</v>
       </c>
       <c r="J251" t="s">
-        <v>232</v>
+        <v>541</v>
       </c>
       <c r="K251" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="L251" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M251" t="s">
         <v>533</v>
@@ -16226,7 +16226,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="F252" t="s">
         <v>40</v>
@@ -16235,19 +16235,19 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I252" t="s">
-        <v>543</v>
+        <v>94</v>
       </c>
       <c r="J252" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K252" t="s">
-        <v>246</v>
+        <v>119</v>
       </c>
       <c r="L252" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M252" t="s">
         <v>533</v>
@@ -16259,7 +16259,7 @@
         <v>48</v>
       </c>
       <c r="P252" t="s">
-        <v>543</v>
+        <v>94</v>
       </c>
       <c r="Q252" t="s">
         <v>47</v>
@@ -16282,7 +16282,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F253" t="s">
         <v>40</v>
@@ -16294,13 +16294,13 @@
         <v>547</v>
       </c>
       <c r="I253" t="s">
-        <v>94</v>
+        <v>548</v>
       </c>
       <c r="J253" t="s">
-        <v>548</v>
+        <v>246</v>
       </c>
       <c r="K253" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
       <c r="L253" t="s">
         <v>549</v>
@@ -16315,7 +16315,7 @@
         <v>48</v>
       </c>
       <c r="P253" t="s">
-        <v>94</v>
+        <v>548</v>
       </c>
       <c r="Q253" t="s">
         <v>47</v>
@@ -16521,10 +16521,10 @@
         <v>557</v>
       </c>
       <c r="J257" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K257" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L257" t="s">
         <v>558</v>
@@ -16692,7 +16692,7 @@
         <v>567</v>
       </c>
       <c r="K260" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L260" t="s">
         <v>34</v>
@@ -16730,28 +16730,28 @@
         <v>34</v>
       </c>
       <c r="E261" t="s">
+        <v>538</v>
+      </c>
+      <c r="F261" t="s">
+        <v>40</v>
+      </c>
+      <c r="G261" t="s">
+        <v>41</v>
+      </c>
+      <c r="H261" t="s">
         <v>568</v>
       </c>
-      <c r="F261" t="s">
-        <v>52</v>
-      </c>
-      <c r="G261" t="s">
-        <v>41</v>
-      </c>
-      <c r="H261" t="s">
+      <c r="I261" t="s">
         <v>569</v>
       </c>
-      <c r="I261" t="s">
+      <c r="J261" t="s">
+        <v>541</v>
+      </c>
+      <c r="K261" t="s">
+        <v>247</v>
+      </c>
+      <c r="L261" t="s">
         <v>570</v>
-      </c>
-      <c r="J261" t="s">
-        <v>567</v>
-      </c>
-      <c r="K261" t="s">
-        <v>124</v>
-      </c>
-      <c r="L261" t="s">
-        <v>34</v>
       </c>
       <c r="M261" t="s">
         <v>563</v>
@@ -16763,7 +16763,7 @@
         <v>48</v>
       </c>
       <c r="P261" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Q261" t="s">
         <v>47</v>
@@ -16786,7 +16786,7 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>538</v>
+        <v>136</v>
       </c>
       <c r="F262" t="s">
         <v>40</v>
@@ -16795,19 +16795,19 @@
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="I262" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="J262" t="s">
-        <v>232</v>
+        <v>572</v>
       </c>
       <c r="K262" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L262" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M262" t="s">
         <v>563</v>
@@ -16819,7 +16819,7 @@
         <v>48</v>
       </c>
       <c r="P262" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="Q262" t="s">
         <v>47</v>
@@ -16842,7 +16842,7 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>136</v>
+        <v>538</v>
       </c>
       <c r="F263" t="s">
         <v>40</v>
@@ -16851,16 +16851,16 @@
         <v>41</v>
       </c>
       <c r="H263" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="I263" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="J263" t="s">
-        <v>573</v>
+        <v>246</v>
       </c>
       <c r="K263" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L263" t="s">
         <v>574</v>
@@ -16875,7 +16875,7 @@
         <v>48</v>
       </c>
       <c r="P263" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="Q263" t="s">
         <v>47</v>
@@ -16907,19 +16907,19 @@
         <v>41</v>
       </c>
       <c r="H264" t="s">
+        <v>388</v>
+      </c>
+      <c r="I264" t="s">
+        <v>557</v>
+      </c>
+      <c r="J264" t="s">
         <v>575</v>
       </c>
-      <c r="I264" t="s">
-        <v>572</v>
-      </c>
-      <c r="J264" t="s">
-        <v>573</v>
-      </c>
       <c r="K264" t="s">
+        <v>247</v>
+      </c>
+      <c r="L264" t="s">
         <v>576</v>
-      </c>
-      <c r="L264" t="s">
-        <v>577</v>
       </c>
       <c r="M264" t="s">
         <v>563</v>
@@ -16931,7 +16931,7 @@
         <v>48</v>
       </c>
       <c r="P264" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="Q264" t="s">
         <v>47</v>
@@ -16963,16 +16963,16 @@
         <v>41</v>
       </c>
       <c r="H265" t="s">
+        <v>577</v>
+      </c>
+      <c r="I265" t="s">
         <v>578</v>
       </c>
-      <c r="I265" t="s">
-        <v>557</v>
-      </c>
       <c r="J265" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K265" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L265" t="s">
         <v>579</v>
@@ -16987,7 +16987,7 @@
         <v>48</v>
       </c>
       <c r="P265" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="Q265" t="s">
         <v>47</v>
@@ -17010,7 +17010,7 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>538</v>
+        <v>136</v>
       </c>
       <c r="F266" t="s">
         <v>40</v>
@@ -17022,13 +17022,13 @@
         <v>580</v>
       </c>
       <c r="I266" t="s">
+        <v>571</v>
+      </c>
+      <c r="J266" t="s">
+        <v>572</v>
+      </c>
+      <c r="K266" t="s">
         <v>581</v>
-      </c>
-      <c r="J266" t="s">
-        <v>544</v>
-      </c>
-      <c r="K266" t="s">
-        <v>233</v>
       </c>
       <c r="L266" t="s">
         <v>582</v>
@@ -17043,7 +17043,7 @@
         <v>48</v>
       </c>
       <c r="P266" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="Q266" t="s">
         <v>47</v>
@@ -17066,28 +17066,28 @@
         <v>34</v>
       </c>
       <c r="E267" t="s">
-        <v>538</v>
+        <v>583</v>
       </c>
       <c r="F267" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G267" t="s">
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I267" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J267" t="s">
-        <v>544</v>
+        <v>586</v>
       </c>
       <c r="K267" t="s">
-        <v>233</v>
+        <v>586</v>
       </c>
       <c r="L267" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M267" t="s">
         <v>563</v>
@@ -17099,7 +17099,7 @@
         <v>48</v>
       </c>
       <c r="P267" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q267" t="s">
         <v>47</v>
@@ -17122,28 +17122,28 @@
         <v>34</v>
       </c>
       <c r="E268" t="s">
-        <v>546</v>
+        <v>588</v>
       </c>
       <c r="F268" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G268" t="s">
         <v>41</v>
       </c>
       <c r="H268" t="s">
-        <v>336</v>
+        <v>589</v>
       </c>
       <c r="I268" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="J268" t="s">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="K268" t="s">
-        <v>233</v>
+        <v>119</v>
       </c>
       <c r="L268" t="s">
-        <v>588</v>
+        <v>34</v>
       </c>
       <c r="M268" t="s">
         <v>563</v>
@@ -17155,7 +17155,7 @@
         <v>48</v>
       </c>
       <c r="P268" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="Q268" t="s">
         <v>47</v>
@@ -17178,7 +17178,7 @@
         <v>34</v>
       </c>
       <c r="E269" t="s">
-        <v>136</v>
+        <v>538</v>
       </c>
       <c r="F269" t="s">
         <v>40</v>
@@ -17187,19 +17187,19 @@
         <v>41</v>
       </c>
       <c r="H269" t="s">
-        <v>386</v>
+        <v>591</v>
       </c>
       <c r="I269" t="s">
         <v>557</v>
       </c>
       <c r="J269" t="s">
-        <v>589</v>
+        <v>541</v>
       </c>
       <c r="K269" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L269" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M269" t="s">
         <v>563</v>
@@ -17243,19 +17243,19 @@
         <v>41</v>
       </c>
       <c r="H270" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I270" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J270" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K270" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L270" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M270" t="s">
         <v>563</v>
@@ -17267,7 +17267,7 @@
         <v>48</v>
       </c>
       <c r="P270" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="Q270" t="s">
         <v>47</v>
@@ -17299,19 +17299,19 @@
         <v>41</v>
       </c>
       <c r="H271" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I271" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="J271" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K271" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L271" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M271" t="s">
         <v>563</v>
@@ -17323,7 +17323,7 @@
         <v>48</v>
       </c>
       <c r="P271" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="Q271" t="s">
         <v>47</v>
@@ -17346,28 +17346,28 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>538</v>
+        <v>599</v>
       </c>
       <c r="F272" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G272" t="s">
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>597</v>
+        <v>568</v>
       </c>
       <c r="I272" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="J272" t="s">
-        <v>544</v>
+        <v>60</v>
       </c>
       <c r="K272" t="s">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="L272" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="M272" t="s">
         <v>563</v>
@@ -17379,7 +17379,7 @@
         <v>48</v>
       </c>
       <c r="P272" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="Q272" t="s">
         <v>47</v>
@@ -17402,28 +17402,28 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>599</v>
+        <v>543</v>
       </c>
       <c r="F273" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
       </c>
       <c r="H273" t="s">
-        <v>600</v>
+        <v>336</v>
       </c>
       <c r="I273" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="J273" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K273" t="s">
-        <v>602</v>
+        <v>247</v>
       </c>
       <c r="L273" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M273" t="s">
         <v>563</v>
@@ -17435,7 +17435,7 @@
         <v>48</v>
       </c>
       <c r="P273" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17458,25 +17458,25 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>604</v>
+        <v>538</v>
       </c>
       <c r="F274" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G274" t="s">
         <v>41</v>
       </c>
       <c r="H274" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
       <c r="I274" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="J274" t="s">
-        <v>60</v>
+        <v>541</v>
       </c>
       <c r="K274" t="s">
-        <v>56</v>
+        <v>247</v>
       </c>
       <c r="L274" t="s">
         <v>606</v>
@@ -17491,7 +17491,7 @@
         <v>48</v>
       </c>
       <c r="P274" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="Q274" t="s">
         <v>47</v>
@@ -18083,7 +18083,7 @@
         <v>41</v>
       </c>
       <c r="H285" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I285" t="s">
         <v>630</v>
@@ -18092,7 +18092,7 @@
         <v>631</v>
       </c>
       <c r="K285" t="s">
-        <v>71</v>
+        <v>240</v>
       </c>
       <c r="L285" t="s">
         <v>34</v>
@@ -18139,7 +18139,7 @@
         <v>41</v>
       </c>
       <c r="H286" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="I286" t="s">
         <v>633</v>
@@ -18148,7 +18148,7 @@
         <v>631</v>
       </c>
       <c r="K286" t="s">
-        <v>246</v>
+        <v>71</v>
       </c>
       <c r="L286" t="s">
         <v>34</v>
@@ -18425,10 +18425,10 @@
         <v>650</v>
       </c>
       <c r="J291" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K291" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L291" t="s">
         <v>651</v>
@@ -18705,10 +18705,10 @@
         <v>669</v>
       </c>
       <c r="J296" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K296" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L296" t="s">
         <v>670</v>
@@ -18873,7 +18873,7 @@
         <v>681</v>
       </c>
       <c r="J299" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K299" t="s">
         <v>682</v>
@@ -18985,10 +18985,10 @@
         <v>688</v>
       </c>
       <c r="J301" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K301" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L301" t="s">
         <v>689</v>
@@ -19100,7 +19100,7 @@
         <v>129</v>
       </c>
       <c r="K303" t="s">
-        <v>71</v>
+        <v>251</v>
       </c>
       <c r="L303" t="s">
         <v>696</v>
@@ -19141,25 +19141,25 @@
         <v>697</v>
       </c>
       <c r="F304" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G304" t="s">
         <v>41</v>
       </c>
       <c r="H304" t="s">
-        <v>42</v>
+        <v>698</v>
       </c>
       <c r="I304" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J304" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="K304" t="s">
-        <v>246</v>
+        <v>71</v>
       </c>
       <c r="L304" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M304" t="s">
         <v>692</v>
@@ -19171,7 +19171,7 @@
         <v>48</v>
       </c>
       <c r="P304" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Q304" t="s">
         <v>47</v>
@@ -19194,25 +19194,25 @@
         <v>34</v>
       </c>
       <c r="E305" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F305" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G305" t="s">
         <v>41</v>
       </c>
       <c r="H305" t="s">
-        <v>701</v>
+        <v>42</v>
       </c>
       <c r="I305" t="s">
         <v>702</v>
       </c>
       <c r="J305" t="s">
-        <v>129</v>
+        <v>240</v>
       </c>
       <c r="K305" t="s">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="L305" t="s">
         <v>703</v>
@@ -19268,10 +19268,10 @@
         <v>129</v>
       </c>
       <c r="K306" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="L306" t="s">
-        <v>707</v>
+        <v>34</v>
       </c>
       <c r="M306" t="s">
         <v>692</v>
@@ -19306,7 +19306,7 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F307" t="s">
         <v>52</v>
@@ -19315,19 +19315,19 @@
         <v>41</v>
       </c>
       <c r="H307" t="s">
+        <v>708</v>
+      </c>
+      <c r="I307" t="s">
         <v>709</v>
-      </c>
-      <c r="I307" t="s">
-        <v>710</v>
       </c>
       <c r="J307" t="s">
         <v>129</v>
       </c>
       <c r="K307" t="s">
-        <v>241</v>
+        <v>115</v>
       </c>
       <c r="L307" t="s">
-        <v>34</v>
+        <v>710</v>
       </c>
       <c r="M307" t="s">
         <v>692</v>
@@ -19339,7 +19339,7 @@
         <v>48</v>
       </c>
       <c r="P307" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="Q307" t="s">
         <v>47</v>
@@ -19433,10 +19433,10 @@
         <v>716</v>
       </c>
       <c r="J309" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K309" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L309" t="s">
         <v>717</v>
@@ -19548,7 +19548,7 @@
         <v>44</v>
       </c>
       <c r="K311" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L311" t="s">
         <v>727</v>
@@ -19657,10 +19657,10 @@
         <v>734</v>
       </c>
       <c r="J313" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K313" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L313" t="s">
         <v>733</v>
@@ -19713,10 +19713,10 @@
         <v>736</v>
       </c>
       <c r="J314" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="K314" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L314" t="s">
         <v>737</v>
@@ -19754,7 +19754,7 @@
         <v>34</v>
       </c>
       <c r="E315" t="s">
-        <v>738</v>
+        <v>538</v>
       </c>
       <c r="F315" t="s">
         <v>40</v>
@@ -19766,16 +19766,16 @@
         <v>727</v>
       </c>
       <c r="I315" t="s">
+        <v>738</v>
+      </c>
+      <c r="J315" t="s">
+        <v>246</v>
+      </c>
+      <c r="K315" t="s">
+        <v>82</v>
+      </c>
+      <c r="L315" t="s">
         <v>739</v>
-      </c>
-      <c r="J315" t="s">
-        <v>740</v>
-      </c>
-      <c r="K315" t="s">
-        <v>233</v>
-      </c>
-      <c r="L315" t="s">
-        <v>741</v>
       </c>
       <c r="M315" t="s">
         <v>731</v>
@@ -19787,7 +19787,7 @@
         <v>48</v>
       </c>
       <c r="P315" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q315" t="s">
         <v>47</v>
@@ -19810,7 +19810,7 @@
         <v>34</v>
       </c>
       <c r="E316" t="s">
-        <v>538</v>
+        <v>740</v>
       </c>
       <c r="F316" t="s">
         <v>40</v>
@@ -19822,13 +19822,13 @@
         <v>727</v>
       </c>
       <c r="I316" t="s">
+        <v>741</v>
+      </c>
+      <c r="J316" t="s">
         <v>742</v>
       </c>
-      <c r="J316" t="s">
-        <v>232</v>
-      </c>
       <c r="K316" t="s">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="L316" t="s">
         <v>743</v>
@@ -19843,7 +19843,7 @@
         <v>48</v>
       </c>
       <c r="P316" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="Q316" t="s">
         <v>47</v>
@@ -19937,10 +19937,10 @@
         <v>749</v>
       </c>
       <c r="J318" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K318" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L318" t="s">
         <v>750</v>
@@ -20161,10 +20161,10 @@
         <v>766</v>
       </c>
       <c r="J322" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K322" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L322" t="s">
         <v>767</v>
@@ -20329,7 +20329,7 @@
         <v>779</v>
       </c>
       <c r="J325" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="K325" t="s">
         <v>124</v>
@@ -20441,10 +20441,10 @@
         <v>787</v>
       </c>
       <c r="J327" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K327" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L327" t="s">
         <v>788</v>
@@ -20497,10 +20497,10 @@
         <v>792</v>
       </c>
       <c r="J328" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K328" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="L328" t="s">
         <v>793</v>
@@ -20650,7 +20650,7 @@
         <v>33</v>
       </c>
       <c r="E331" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F331" t="s">
         <v>40</v>

--- a/xlsx/dre/DRE_04_2026.xlsx
+++ b/xlsx/dre/DRE_04_2026.xlsx
@@ -797,10 +797,16 @@
     <t>4.02.02.01.01 Fretes sobre compra de mercadorias da marca - provisão</t>
   </si>
   <si>
+    <t>73501R/0</t>
+  </si>
+  <si>
+    <t>RODAG TRANSPORTES LTDA*</t>
+  </si>
+  <si>
+    <t>R$  12,03</t>
+  </si>
+  <si>
     <t>72501/3</t>
-  </si>
-  <si>
-    <t>RODAG TRANSPORTES LTDA*</t>
   </si>
   <si>
     <t>R$  595,25</t>
@@ -1007,12 +1013,6 @@
     <t>R$  8,02</t>
   </si>
   <si>
-    <t>73501R/0</t>
-  </si>
-  <si>
-    <t>R$  12,03</t>
-  </si>
-  <si>
     <t>4.03 DESPESAS DE VENDAS</t>
   </si>
   <si>
@@ -1337,12 +1337,12 @@
     <t>DSR abr26/1</t>
   </si>
   <si>
+    <t>R$  549,59</t>
+  </si>
+  <si>
     <t>R$  736,46</t>
   </si>
   <si>
-    <t>R$  549,59</t>
-  </si>
-  <si>
     <t>4.03.03 GASTOS GERAIS COM VENDAS</t>
   </si>
   <si>
@@ -1559,21 +1559,21 @@
     <t>R$ 277,65</t>
   </si>
   <si>
+    <t>5/2</t>
+  </si>
+  <si>
+    <t>R$  92,55</t>
+  </si>
+  <si>
+    <t>Mercado Livre</t>
+  </si>
+  <si>
+    <t>5/3</t>
+  </si>
+  <si>
     <t>5/1</t>
   </si>
   <si>
-    <t>R$  92,55</t>
-  </si>
-  <si>
-    <t>Mercado Livre</t>
-  </si>
-  <si>
-    <t>5/3</t>
-  </si>
-  <si>
-    <t>5/2</t>
-  </si>
-  <si>
     <t>4.03.03.02.05 Assistência técnica - custo loja</t>
   </si>
   <si>
@@ -1604,24 +1604,24 @@
     <t>4.03.03.08.01 Brindes para clientes (CV)</t>
   </si>
   <si>
+    <t>2/2</t>
+  </si>
+  <si>
+    <t>Licoretto Bebidas</t>
+  </si>
+  <si>
+    <t>R$  79,98</t>
+  </si>
+  <si>
+    <t>Brindes clientes</t>
+  </si>
+  <si>
+    <t>2/1</t>
+  </si>
+  <si>
     <t>2/3</t>
   </si>
   <si>
-    <t>Licoretto Bebidas</t>
-  </si>
-  <si>
-    <t>R$  79,98</t>
-  </si>
-  <si>
-    <t>Brindes clientes</t>
-  </si>
-  <si>
-    <t>2/1</t>
-  </si>
-  <si>
-    <t>2/2</t>
-  </si>
-  <si>
     <t>4.03.03.09 Marketing - mídias / ações comerciais / outros (CV)</t>
   </si>
   <si>
@@ -1646,6 +1646,30 @@
     <t>12/4</t>
   </si>
   <si>
+    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
+  </si>
+  <si>
+    <t>R$  808,50</t>
+  </si>
+  <si>
+    <t>08/01/26</t>
+  </si>
+  <si>
+    <t>MHM - Honorários 2026</t>
+  </si>
+  <si>
+    <t>1/2</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>03/02/26</t>
+  </si>
+  <si>
+    <t>Facebook 2026</t>
+  </si>
+  <si>
     <t>Google</t>
   </si>
   <si>
@@ -1655,30 +1679,6 @@
     <t>Google 2026</t>
   </si>
   <si>
-    <t>MARQUES MAIO MARKETING DIGITAL LTDA</t>
-  </si>
-  <si>
-    <t>R$  808,50</t>
-  </si>
-  <si>
-    <t>08/01/26</t>
-  </si>
-  <si>
-    <t>MHM - Honorários 2026</t>
-  </si>
-  <si>
-    <t>1/2</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>03/02/26</t>
-  </si>
-  <si>
-    <t>Facebook 2026</t>
-  </si>
-  <si>
     <t>4.04 DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
@@ -1931,19 +1931,19 @@
     <t>4.04.01.05.02.01 Vale transporte</t>
   </si>
   <si>
+    <t>VT abr26/4</t>
+  </si>
+  <si>
+    <t>R$  411,36</t>
+  </si>
+  <si>
+    <t>31/03/26</t>
+  </si>
+  <si>
     <t>VT abr26/1</t>
   </si>
   <si>
     <t>R$  290,65</t>
-  </si>
-  <si>
-    <t>31/03/26</t>
-  </si>
-  <si>
-    <t>VT abr26/4</t>
-  </si>
-  <si>
-    <t>R$  411,36</t>
   </si>
   <si>
     <t>4.04.01.07 Uniformes e crachás</t>
@@ -2125,6 +2125,18 @@
     <t>4.04.02.06.01 Material de escritório - uso e consumo</t>
   </si>
   <si>
+    <t>646/1</t>
+  </si>
+  <si>
+    <t>Oxxo</t>
+  </si>
+  <si>
+    <t>R$  90,07</t>
+  </si>
+  <si>
+    <t>Cafés loja</t>
+  </si>
+  <si>
     <t>644/1</t>
   </si>
   <si>
@@ -2144,6 +2156,15 @@
   </si>
   <si>
     <t>Envelope</t>
+  </si>
+  <si>
+    <t>648/1</t>
+  </si>
+  <si>
+    <t>Chaveiro Rouxinol</t>
+  </si>
+  <si>
+    <t>R$  90,00</t>
   </si>
   <si>
     <t>643/1</t>
@@ -2162,27 +2183,6 @@
 </t>
   </si>
   <si>
-    <t>646/1</t>
-  </si>
-  <si>
-    <t>Oxxo</t>
-  </si>
-  <si>
-    <t>R$  90,07</t>
-  </si>
-  <si>
-    <t>Cafés loja</t>
-  </si>
-  <si>
-    <t>648/1</t>
-  </si>
-  <si>
-    <t>Chaveiro Rouxinol</t>
-  </si>
-  <si>
-    <t>R$  90,00</t>
-  </si>
-  <si>
     <t>4.04.02.07 Informática</t>
   </si>
   <si>
@@ -2264,6 +2264,12 @@
     <t>D4 sign 2026</t>
   </si>
   <si>
+    <t>R$  599,00</t>
+  </si>
+  <si>
+    <t>Promob 2026</t>
+  </si>
+  <si>
     <t>3/3</t>
   </si>
   <si>
@@ -2274,12 +2280,6 @@
   </si>
   <si>
     <t>Promob 2026/2</t>
-  </si>
-  <si>
-    <t>R$  599,00</t>
-  </si>
-  <si>
-    <t>Promob 2026</t>
   </si>
   <si>
     <t>4.04.02.11 Manutenção de predio e equipamentos</t>
@@ -6836,7 +6836,7 @@
         <v>257</v>
       </c>
       <c r="F84" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="G84" t="s">
         <v>41</v>
@@ -6848,13 +6848,13 @@
         <v>259</v>
       </c>
       <c r="J84" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K84" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L84" t="s">
-        <v>260</v>
+        <v>34</v>
       </c>
       <c r="M84" t="s">
         <v>256</v>
@@ -6863,7 +6863,7 @@
         <v>47</v>
       </c>
       <c r="O84" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P84" t="s">
         <v>259</v>
@@ -6889,7 +6889,7 @@
         <v>34</v>
       </c>
       <c r="E85" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F85" t="s">
         <v>183</v>
@@ -6898,10 +6898,10 @@
         <v>41</v>
       </c>
       <c r="H85" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J85" t="s">
         <v>71</v>
@@ -6910,7 +6910,7 @@
         <v>71</v>
       </c>
       <c r="L85" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M85" t="s">
         <v>256</v>
@@ -6922,7 +6922,7 @@
         <v>72</v>
       </c>
       <c r="P85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Q85" t="s">
         <v>47</v>
@@ -6945,7 +6945,7 @@
         <v>34</v>
       </c>
       <c r="E86" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F86" t="s">
         <v>183</v>
@@ -6954,19 +6954,19 @@
         <v>41</v>
       </c>
       <c r="H86" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I86" t="s">
         <v>265</v>
       </c>
       <c r="J86" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="K86" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L86" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M86" t="s">
         <v>256</v>
@@ -6975,7 +6975,7 @@
         <v>47</v>
       </c>
       <c r="O86" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="P86" t="s">
         <v>265</v>
@@ -7016,13 +7016,13 @@
         <v>267</v>
       </c>
       <c r="J87" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="K87" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="L87" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M87" t="s">
         <v>256</v>
@@ -7031,7 +7031,7 @@
         <v>47</v>
       </c>
       <c r="O87" t="s">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="P87" t="s">
         <v>267</v>
@@ -7072,13 +7072,13 @@
         <v>269</v>
       </c>
       <c r="J88" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="K88" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="L88" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M88" t="s">
         <v>256</v>
@@ -7087,7 +7087,7 @@
         <v>47</v>
       </c>
       <c r="O88" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="P88" t="s">
         <v>269</v>
@@ -7128,13 +7128,13 @@
         <v>271</v>
       </c>
       <c r="J89" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="K89" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="L89" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M89" t="s">
         <v>256</v>
@@ -7143,7 +7143,7 @@
         <v>47</v>
       </c>
       <c r="O89" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="P89" t="s">
         <v>271</v>
@@ -7184,13 +7184,13 @@
         <v>273</v>
       </c>
       <c r="J90" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="K90" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="L90" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M90" t="s">
         <v>256</v>
@@ -7199,7 +7199,7 @@
         <v>47</v>
       </c>
       <c r="O90" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="P90" t="s">
         <v>273</v>
@@ -7234,19 +7234,19 @@
         <v>41</v>
       </c>
       <c r="H91" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I91" t="s">
         <v>275</v>
       </c>
       <c r="J91" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="K91" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="L91" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M91" t="s">
         <v>256</v>
@@ -7255,7 +7255,7 @@
         <v>47</v>
       </c>
       <c r="O91" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="P91" t="s">
         <v>275</v>
@@ -7290,19 +7290,19 @@
         <v>41</v>
       </c>
       <c r="H92" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I92" t="s">
         <v>277</v>
       </c>
       <c r="J92" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="K92" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L92" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M92" t="s">
         <v>256</v>
@@ -7311,7 +7311,7 @@
         <v>47</v>
       </c>
       <c r="O92" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="P92" t="s">
         <v>277</v>
@@ -7337,7 +7337,7 @@
         <v>34</v>
       </c>
       <c r="E93" t="s">
-        <v>214</v>
+        <v>278</v>
       </c>
       <c r="F93" t="s">
         <v>183</v>
@@ -7346,19 +7346,19 @@
         <v>41</v>
       </c>
       <c r="H93" t="s">
+        <v>264</v>
+      </c>
+      <c r="I93" t="s">
+        <v>279</v>
+      </c>
+      <c r="J93" t="s">
+        <v>119</v>
+      </c>
+      <c r="K93" t="s">
+        <v>119</v>
+      </c>
+      <c r="L93" t="s">
         <v>262</v>
-      </c>
-      <c r="I93" t="s">
-        <v>278</v>
-      </c>
-      <c r="J93" t="s">
-        <v>76</v>
-      </c>
-      <c r="K93" t="s">
-        <v>76</v>
-      </c>
-      <c r="L93" t="s">
-        <v>260</v>
       </c>
       <c r="M93" t="s">
         <v>256</v>
@@ -7367,10 +7367,10 @@
         <v>47</v>
       </c>
       <c r="O93" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="P93" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q93" t="s">
         <v>47</v>
@@ -7393,7 +7393,7 @@
         <v>34</v>
       </c>
       <c r="E94" t="s">
-        <v>279</v>
+        <v>214</v>
       </c>
       <c r="F94" t="s">
         <v>183</v>
@@ -7402,19 +7402,19 @@
         <v>41</v>
       </c>
       <c r="H94" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I94" t="s">
         <v>280</v>
       </c>
       <c r="J94" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="K94" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="L94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M94" t="s">
         <v>256</v>
@@ -7423,7 +7423,7 @@
         <v>47</v>
       </c>
       <c r="O94" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="P94" t="s">
         <v>280</v>
@@ -7458,19 +7458,19 @@
         <v>41</v>
       </c>
       <c r="H95" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I95" t="s">
         <v>282</v>
       </c>
       <c r="J95" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="K95" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="L95" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M95" t="s">
         <v>256</v>
@@ -7479,7 +7479,7 @@
         <v>47</v>
       </c>
       <c r="O95" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="P95" t="s">
         <v>282</v>
@@ -7514,19 +7514,19 @@
         <v>41</v>
       </c>
       <c r="H96" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I96" t="s">
         <v>284</v>
       </c>
       <c r="J96" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K96" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="L96" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M96" t="s">
         <v>256</v>
@@ -7535,7 +7535,7 @@
         <v>47</v>
       </c>
       <c r="O96" t="s">
-        <v>285</v>
+        <v>96</v>
       </c>
       <c r="P96" t="s">
         <v>284</v>
@@ -7561,7 +7561,7 @@
         <v>34</v>
       </c>
       <c r="E97" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F97" t="s">
         <v>183</v>
@@ -7570,10 +7570,10 @@
         <v>41</v>
       </c>
       <c r="H97" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I97" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J97" t="s">
         <v>108</v>
@@ -7582,7 +7582,7 @@
         <v>108</v>
       </c>
       <c r="L97" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M97" t="s">
         <v>256</v>
@@ -7591,10 +7591,10 @@
         <v>47</v>
       </c>
       <c r="O97" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P97" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q97" t="s">
         <v>47</v>
@@ -7626,19 +7626,19 @@
         <v>41</v>
       </c>
       <c r="H98" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I98" t="s">
         <v>289</v>
       </c>
       <c r="J98" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="K98" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="L98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M98" t="s">
         <v>256</v>
@@ -7647,7 +7647,7 @@
         <v>47</v>
       </c>
       <c r="O98" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P98" t="s">
         <v>289</v>
@@ -7673,7 +7673,7 @@
         <v>34</v>
       </c>
       <c r="E99" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F99" t="s">
         <v>183</v>
@@ -7682,10 +7682,10 @@
         <v>41</v>
       </c>
       <c r="H99" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I99" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J99" t="s">
         <v>83</v>
@@ -7694,7 +7694,7 @@
         <v>83</v>
       </c>
       <c r="L99" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M99" t="s">
         <v>256</v>
@@ -7703,10 +7703,10 @@
         <v>47</v>
       </c>
       <c r="O99" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P99" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q99" t="s">
         <v>47</v>
@@ -7732,25 +7732,25 @@
         <v>293</v>
       </c>
       <c r="F100" t="s">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="G100" t="s">
         <v>41</v>
       </c>
       <c r="H100" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I100" t="s">
         <v>294</v>
       </c>
       <c r="J100" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="K100" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="L100" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="M100" t="s">
         <v>256</v>
@@ -7759,7 +7759,7 @@
         <v>47</v>
       </c>
       <c r="O100" t="s">
-        <v>48</v>
+        <v>292</v>
       </c>
       <c r="P100" t="s">
         <v>294</v>
@@ -7785,7 +7785,7 @@
         <v>34</v>
       </c>
       <c r="E101" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F101" t="s">
         <v>52</v>
@@ -7794,19 +7794,19 @@
         <v>41</v>
       </c>
       <c r="H101" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I101" t="s">
+        <v>296</v>
+      </c>
+      <c r="J101" t="s">
+        <v>171</v>
+      </c>
+      <c r="K101" t="s">
+        <v>171</v>
+      </c>
+      <c r="L101" t="s">
         <v>297</v>
-      </c>
-      <c r="J101" t="s">
-        <v>89</v>
-      </c>
-      <c r="K101" t="s">
-        <v>71</v>
-      </c>
-      <c r="L101" t="s">
-        <v>34</v>
       </c>
       <c r="M101" t="s">
         <v>256</v>
@@ -7818,7 +7818,7 @@
         <v>48</v>
       </c>
       <c r="P101" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q101" t="s">
         <v>47</v>
@@ -7850,16 +7850,16 @@
         <v>41</v>
       </c>
       <c r="H102" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I102" t="s">
         <v>299</v>
       </c>
       <c r="J102" t="s">
-        <v>300</v>
+        <v>89</v>
       </c>
       <c r="K102" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="L102" t="s">
         <v>34</v>
@@ -7871,7 +7871,7 @@
         <v>47</v>
       </c>
       <c r="O102" t="s">
-        <v>213</v>
+        <v>48</v>
       </c>
       <c r="P102" t="s">
         <v>299</v>
@@ -7897,7 +7897,7 @@
         <v>34</v>
       </c>
       <c r="E103" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F103" t="s">
         <v>52</v>
@@ -7909,10 +7909,10 @@
         <v>258</v>
       </c>
       <c r="I103" t="s">
+        <v>301</v>
+      </c>
+      <c r="J103" t="s">
         <v>302</v>
-      </c>
-      <c r="J103" t="s">
-        <v>300</v>
       </c>
       <c r="K103" t="s">
         <v>125</v>
@@ -7927,10 +7927,10 @@
         <v>47</v>
       </c>
       <c r="O103" t="s">
-        <v>303</v>
+        <v>213</v>
       </c>
       <c r="P103" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q103" t="s">
         <v>47</v>
@@ -7953,7 +7953,7 @@
         <v>34</v>
       </c>
       <c r="E104" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F104" t="s">
         <v>52</v>
@@ -7962,13 +7962,13 @@
         <v>41</v>
       </c>
       <c r="H104" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I104" t="s">
         <v>304</v>
       </c>
       <c r="J104" t="s">
-        <v>125</v>
+        <v>302</v>
       </c>
       <c r="K104" t="s">
         <v>125</v>
@@ -7983,7 +7983,7 @@
         <v>47</v>
       </c>
       <c r="O104" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P104" t="s">
         <v>304</v>
@@ -8009,7 +8009,7 @@
         <v>34</v>
       </c>
       <c r="E105" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F105" t="s">
         <v>52</v>
@@ -8018,10 +8018,10 @@
         <v>41</v>
       </c>
       <c r="H105" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I105" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J105" t="s">
         <v>125</v>
@@ -8039,10 +8039,10 @@
         <v>47</v>
       </c>
       <c r="O105" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
       <c r="P105" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q105" t="s">
         <v>47</v>
@@ -8065,7 +8065,7 @@
         <v>34</v>
       </c>
       <c r="E106" t="s">
-        <v>67</v>
+        <v>300</v>
       </c>
       <c r="F106" t="s">
         <v>52</v>
@@ -8074,16 +8074,16 @@
         <v>41</v>
       </c>
       <c r="H106" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I106" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J106" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="K106" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="L106" t="s">
         <v>34</v>
@@ -8095,10 +8095,10 @@
         <v>47</v>
       </c>
       <c r="O106" t="s">
-        <v>72</v>
+        <v>213</v>
       </c>
       <c r="P106" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q106" t="s">
         <v>47</v>
@@ -8121,7 +8121,7 @@
         <v>34</v>
       </c>
       <c r="E107" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F107" t="s">
         <v>52</v>
@@ -8130,16 +8130,16 @@
         <v>41</v>
       </c>
       <c r="H107" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I107" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J107" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K107" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="L107" t="s">
         <v>34</v>
@@ -8151,10 +8151,10 @@
         <v>47</v>
       </c>
       <c r="O107" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="P107" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q107" t="s">
         <v>47</v>
@@ -8177,7 +8177,7 @@
         <v>34</v>
       </c>
       <c r="E108" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F108" t="s">
         <v>52</v>
@@ -8186,16 +8186,16 @@
         <v>41</v>
       </c>
       <c r="H108" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I108" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J108" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K108" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L108" t="s">
         <v>34</v>
@@ -8207,10 +8207,10 @@
         <v>47</v>
       </c>
       <c r="O108" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P108" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q108" t="s">
         <v>47</v>
@@ -8233,7 +8233,7 @@
         <v>34</v>
       </c>
       <c r="E109" t="s">
-        <v>309</v>
+        <v>67</v>
       </c>
       <c r="F109" t="s">
         <v>52</v>
@@ -8242,16 +8242,16 @@
         <v>41</v>
       </c>
       <c r="H109" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I109" t="s">
         <v>310</v>
       </c>
       <c r="J109" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="K109" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L109" t="s">
         <v>34</v>
@@ -8263,7 +8263,7 @@
         <v>47</v>
       </c>
       <c r="O109" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="P109" t="s">
         <v>310</v>
@@ -8289,7 +8289,7 @@
         <v>34</v>
       </c>
       <c r="E110" t="s">
-        <v>73</v>
+        <v>311</v>
       </c>
       <c r="F110" t="s">
         <v>52</v>
@@ -8298,16 +8298,16 @@
         <v>41</v>
       </c>
       <c r="H110" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I110" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J110" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K110" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="L110" t="s">
         <v>34</v>
@@ -8319,10 +8319,10 @@
         <v>47</v>
       </c>
       <c r="O110" t="s">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="P110" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q110" t="s">
         <v>47</v>
@@ -8345,7 +8345,7 @@
         <v>34</v>
       </c>
       <c r="E111" t="s">
-        <v>312</v>
+        <v>73</v>
       </c>
       <c r="F111" t="s">
         <v>52</v>
@@ -8354,7 +8354,7 @@
         <v>41</v>
       </c>
       <c r="H111" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I111" t="s">
         <v>313</v>
@@ -8401,7 +8401,7 @@
         <v>34</v>
       </c>
       <c r="E112" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F112" t="s">
         <v>52</v>
@@ -8410,16 +8410,16 @@
         <v>41</v>
       </c>
       <c r="H112" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I112" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J112" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="K112" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="L112" t="s">
         <v>34</v>
@@ -8431,10 +8431,10 @@
         <v>47</v>
       </c>
       <c r="O112" t="s">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="P112" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q112" t="s">
         <v>47</v>
@@ -8457,7 +8457,7 @@
         <v>34</v>
       </c>
       <c r="E113" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F113" t="s">
         <v>52</v>
@@ -8466,16 +8466,16 @@
         <v>41</v>
       </c>
       <c r="H113" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I113" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="J113" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="K113" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="L113" t="s">
         <v>34</v>
@@ -8487,10 +8487,10 @@
         <v>47</v>
       </c>
       <c r="O113" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="P113" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q113" t="s">
         <v>47</v>
@@ -8513,7 +8513,7 @@
         <v>34</v>
       </c>
       <c r="E114" t="s">
-        <v>92</v>
+        <v>317</v>
       </c>
       <c r="F114" t="s">
         <v>52</v>
@@ -8522,16 +8522,16 @@
         <v>41</v>
       </c>
       <c r="H114" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I114" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J114" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="K114" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="L114" t="s">
         <v>34</v>
@@ -8543,10 +8543,10 @@
         <v>47</v>
       </c>
       <c r="O114" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="P114" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q114" t="s">
         <v>47</v>
@@ -8569,7 +8569,7 @@
         <v>34</v>
       </c>
       <c r="E115" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F115" t="s">
         <v>52</v>
@@ -8578,16 +8578,16 @@
         <v>41</v>
       </c>
       <c r="H115" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I115" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J115" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="K115" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="L115" t="s">
         <v>34</v>
@@ -8599,10 +8599,10 @@
         <v>47</v>
       </c>
       <c r="O115" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="P115" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q115" t="s">
         <v>47</v>
@@ -8625,7 +8625,7 @@
         <v>34</v>
       </c>
       <c r="E116" t="s">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="F116" t="s">
         <v>52</v>
@@ -8634,10 +8634,10 @@
         <v>41</v>
       </c>
       <c r="H116" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I116" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J116" t="s">
         <v>55</v>
@@ -8658,7 +8658,7 @@
         <v>104</v>
       </c>
       <c r="P116" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="Q116" t="s">
         <v>47</v>
@@ -8681,7 +8681,7 @@
         <v>34</v>
       </c>
       <c r="E117" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F117" t="s">
         <v>52</v>
@@ -8690,16 +8690,16 @@
         <v>41</v>
       </c>
       <c r="H117" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I117" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="J117" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="K117" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="L117" t="s">
         <v>34</v>
@@ -8711,10 +8711,10 @@
         <v>47</v>
       </c>
       <c r="O117" t="s">
-        <v>290</v>
+        <v>104</v>
       </c>
       <c r="P117" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="Q117" t="s">
         <v>47</v>
@@ -8737,7 +8737,7 @@
         <v>34</v>
       </c>
       <c r="E118" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F118" t="s">
         <v>52</v>
@@ -8746,10 +8746,10 @@
         <v>41</v>
       </c>
       <c r="H118" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I118" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J118" t="s">
         <v>83</v>
@@ -8767,10 +8767,10 @@
         <v>47</v>
       </c>
       <c r="O118" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P118" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q118" t="s">
         <v>47</v>
@@ -8793,7 +8793,7 @@
         <v>34</v>
       </c>
       <c r="E119" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F119" t="s">
         <v>52</v>
@@ -8802,16 +8802,16 @@
         <v>41</v>
       </c>
       <c r="H119" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I119" t="s">
         <v>323</v>
       </c>
       <c r="J119" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K119" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="L119" t="s">
         <v>34</v>
@@ -8823,7 +8823,7 @@
         <v>47</v>
       </c>
       <c r="O119" t="s">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="P119" t="s">
         <v>323</v>
@@ -8849,7 +8849,7 @@
         <v>34</v>
       </c>
       <c r="E120" t="s">
-        <v>105</v>
+        <v>324</v>
       </c>
       <c r="F120" t="s">
         <v>52</v>
@@ -8858,16 +8858,16 @@
         <v>41</v>
       </c>
       <c r="H120" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I120" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J120" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="K120" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="L120" t="s">
         <v>34</v>
@@ -8879,10 +8879,10 @@
         <v>47</v>
       </c>
       <c r="O120" t="s">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="P120" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q120" t="s">
         <v>47</v>
@@ -8914,10 +8914,10 @@
         <v>41</v>
       </c>
       <c r="H121" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="I121" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J121" t="s">
         <v>108</v>
@@ -8935,10 +8935,10 @@
         <v>47</v>
       </c>
       <c r="O121" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P121" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q121" t="s">
         <v>47</v>
@@ -8961,7 +8961,7 @@
         <v>34</v>
       </c>
       <c r="E122" t="s">
-        <v>326</v>
+        <v>105</v>
       </c>
       <c r="F122" t="s">
         <v>52</v>
@@ -8976,10 +8976,10 @@
         <v>327</v>
       </c>
       <c r="J122" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="K122" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="L122" t="s">
         <v>34</v>
@@ -8991,7 +8991,7 @@
         <v>47</v>
       </c>
       <c r="O122" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="P122" t="s">
         <v>327</v>
@@ -9271,7 +9271,7 @@
         <v>47</v>
       </c>
       <c r="O127" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P127" t="s">
         <v>337</v>
@@ -9383,7 +9383,7 @@
         <v>47</v>
       </c>
       <c r="O129" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P129" t="s">
         <v>339</v>
@@ -9439,7 +9439,7 @@
         <v>47</v>
       </c>
       <c r="O130" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P130" t="s">
         <v>340</v>
@@ -9551,7 +9551,7 @@
         <v>47</v>
       </c>
       <c r="O132" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P132" t="s">
         <v>342</v>
@@ -10223,7 +10223,7 @@
         <v>47</v>
       </c>
       <c r="O144" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P144" t="s">
         <v>357</v>
@@ -10335,7 +10335,7 @@
         <v>47</v>
       </c>
       <c r="O146" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P146" t="s">
         <v>359</v>
@@ -10615,7 +10615,7 @@
         <v>47</v>
       </c>
       <c r="O151" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P151" t="s">
         <v>365</v>
@@ -10783,7 +10783,7 @@
         <v>47</v>
       </c>
       <c r="O154" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P154" t="s">
         <v>339</v>
@@ -11175,7 +11175,7 @@
         <v>47</v>
       </c>
       <c r="O161" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P161" t="s">
         <v>340</v>
@@ -11287,7 +11287,7 @@
         <v>47</v>
       </c>
       <c r="O163" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P163" t="s">
         <v>342</v>
@@ -11455,7 +11455,7 @@
         <v>47</v>
       </c>
       <c r="O166" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P166" t="s">
         <v>373</v>
@@ -11567,7 +11567,7 @@
         <v>47</v>
       </c>
       <c r="O168" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P168" t="s">
         <v>375</v>
@@ -11623,7 +11623,7 @@
         <v>47</v>
       </c>
       <c r="O169" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P169" t="s">
         <v>376</v>
@@ -11903,7 +11903,7 @@
         <v>47</v>
       </c>
       <c r="O174" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P174" t="s">
         <v>387</v>
@@ -12239,7 +12239,7 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P180" t="s">
         <v>395</v>
@@ -12601,7 +12601,7 @@
         <v>34</v>
       </c>
       <c r="E187" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F187" t="s">
         <v>52</v>
@@ -12631,7 +12631,7 @@
         <v>47</v>
       </c>
       <c r="O187" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P187" t="s">
         <v>404</v>
@@ -12687,7 +12687,7 @@
         <v>47</v>
       </c>
       <c r="O188" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P188" t="s">
         <v>412</v>
@@ -12855,7 +12855,7 @@
         <v>47</v>
       </c>
       <c r="O191" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P191" t="s">
         <v>419</v>
@@ -12881,7 +12881,7 @@
         <v>34</v>
       </c>
       <c r="E192" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F192" t="s">
         <v>52</v>
@@ -12937,7 +12937,7 @@
         <v>34</v>
       </c>
       <c r="E193" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F193" t="s">
         <v>52</v>
@@ -12967,7 +12967,7 @@
         <v>47</v>
       </c>
       <c r="O193" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P193" t="s">
         <v>419</v>
@@ -13049,7 +13049,7 @@
         <v>34</v>
       </c>
       <c r="E195" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F195" t="s">
         <v>52</v>
@@ -13394,16 +13394,16 @@
         <v>41</v>
       </c>
       <c r="H201" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I201" t="s">
         <v>436</v>
       </c>
       <c r="J201" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="K201" t="s">
-        <v>240</v>
+        <v>89</v>
       </c>
       <c r="L201" t="s">
         <v>34</v>
@@ -13450,16 +13450,16 @@
         <v>41</v>
       </c>
       <c r="H202" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="I202" t="s">
         <v>437</v>
       </c>
       <c r="J202" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="K202" t="s">
-        <v>89</v>
+        <v>240</v>
       </c>
       <c r="L202" t="s">
         <v>34</v>
@@ -13695,7 +13695,7 @@
         <v>47</v>
       </c>
       <c r="O206" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P206" t="s">
         <v>448</v>
@@ -13833,7 +13833,7 @@
         <v>34</v>
       </c>
       <c r="E209" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F209" t="s">
         <v>52</v>
@@ -13863,7 +13863,7 @@
         <v>47</v>
       </c>
       <c r="O209" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P209" t="s">
         <v>453</v>
@@ -15263,7 +15263,7 @@
         <v>47</v>
       </c>
       <c r="O234" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P234" t="s">
         <v>519</v>
@@ -15289,7 +15289,7 @@
         <v>34</v>
       </c>
       <c r="E235" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F235" t="s">
         <v>40</v>
@@ -15304,10 +15304,10 @@
         <v>519</v>
       </c>
       <c r="J235" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="K235" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="L235" t="s">
         <v>34</v>
@@ -15319,7 +15319,7 @@
         <v>47</v>
       </c>
       <c r="O235" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="P235" t="s">
         <v>519</v>
@@ -15345,7 +15345,7 @@
         <v>34</v>
       </c>
       <c r="E236" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F236" t="s">
         <v>40</v>
@@ -15360,10 +15360,10 @@
         <v>519</v>
       </c>
       <c r="J236" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="K236" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="L236" t="s">
         <v>34</v>
@@ -15375,7 +15375,7 @@
         <v>47</v>
       </c>
       <c r="O236" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="P236" t="s">
         <v>519</v>
@@ -15401,7 +15401,7 @@
         <v>34</v>
       </c>
       <c r="E237" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="F237" t="s">
         <v>40</v>
@@ -15416,10 +15416,10 @@
         <v>519</v>
       </c>
       <c r="J237" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K237" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L237" t="s">
         <v>34</v>
@@ -15431,7 +15431,7 @@
         <v>47</v>
       </c>
       <c r="O237" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="P237" t="s">
         <v>519</v>
@@ -15457,7 +15457,7 @@
         <v>34</v>
       </c>
       <c r="E238" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F238" t="s">
         <v>40</v>
@@ -15472,10 +15472,10 @@
         <v>519</v>
       </c>
       <c r="J238" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K238" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L238" t="s">
         <v>34</v>
@@ -15487,7 +15487,7 @@
         <v>47</v>
       </c>
       <c r="O238" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P238" t="s">
         <v>519</v>
@@ -15513,7 +15513,7 @@
         <v>34</v>
       </c>
       <c r="E239" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="F239" t="s">
         <v>40</v>
@@ -15525,13 +15525,13 @@
         <v>518</v>
       </c>
       <c r="I239" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J239" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="K239" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L239" t="s">
         <v>34</v>
@@ -15543,10 +15543,10 @@
         <v>47</v>
       </c>
       <c r="O239" t="s">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="P239" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q239" t="s">
         <v>47</v>
@@ -15569,7 +15569,7 @@
         <v>34</v>
       </c>
       <c r="E240" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F240" t="s">
         <v>40</v>
@@ -15584,10 +15584,10 @@
         <v>519</v>
       </c>
       <c r="J240" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="K240" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="L240" t="s">
         <v>34</v>
@@ -15599,7 +15599,7 @@
         <v>47</v>
       </c>
       <c r="O240" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="P240" t="s">
         <v>519</v>
@@ -15625,7 +15625,7 @@
         <v>34</v>
       </c>
       <c r="E241" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F241" t="s">
         <v>40</v>
@@ -15637,13 +15637,13 @@
         <v>518</v>
       </c>
       <c r="I241" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J241" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K241" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="L241" t="s">
         <v>34</v>
@@ -15655,10 +15655,10 @@
         <v>47</v>
       </c>
       <c r="O241" t="s">
-        <v>285</v>
+        <v>96</v>
       </c>
       <c r="P241" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q241" t="s">
         <v>47</v>
@@ -15681,10 +15681,10 @@
         <v>34</v>
       </c>
       <c r="E242" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F242" t="s">
-        <v>40</v>
+        <v>521</v>
       </c>
       <c r="G242" t="s">
         <v>41</v>
@@ -15696,10 +15696,10 @@
         <v>519</v>
       </c>
       <c r="J242" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="K242" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="L242" t="s">
         <v>34</v>
@@ -15711,13 +15711,13 @@
         <v>47</v>
       </c>
       <c r="O242" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="P242" t="s">
-        <v>519</v>
+        <v>34</v>
       </c>
       <c r="Q242" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="R242" t="s">
         <v>34</v>
@@ -15793,10 +15793,10 @@
         <v>34</v>
       </c>
       <c r="E244" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F244" t="s">
-        <v>521</v>
+        <v>40</v>
       </c>
       <c r="G244" t="s">
         <v>41</v>
@@ -15808,10 +15808,10 @@
         <v>519</v>
       </c>
       <c r="J244" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="K244" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="L244" t="s">
         <v>34</v>
@@ -15823,13 +15823,13 @@
         <v>47</v>
       </c>
       <c r="O244" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="P244" t="s">
-        <v>34</v>
+        <v>519</v>
       </c>
       <c r="Q244" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R244" t="s">
         <v>34</v>
@@ -16200,13 +16200,13 @@
         <v>540</v>
       </c>
       <c r="J251" t="s">
-        <v>246</v>
+        <v>541</v>
       </c>
       <c r="K251" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="L251" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M251" t="s">
         <v>533</v>
@@ -16241,7 +16241,7 @@
         <v>34</v>
       </c>
       <c r="E252" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="F252" t="s">
         <v>40</v>
@@ -16250,19 +16250,19 @@
         <v>41</v>
       </c>
       <c r="H252" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I252" t="s">
-        <v>543</v>
+        <v>94</v>
       </c>
       <c r="J252" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K252" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="L252" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M252" t="s">
         <v>533</v>
@@ -16274,7 +16274,7 @@
         <v>48</v>
       </c>
       <c r="P252" t="s">
-        <v>543</v>
+        <v>94</v>
       </c>
       <c r="Q252" t="s">
         <v>47</v>
@@ -16297,7 +16297,7 @@
         <v>34</v>
       </c>
       <c r="E253" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="F253" t="s">
         <v>40</v>
@@ -16309,13 +16309,13 @@
         <v>547</v>
       </c>
       <c r="I253" t="s">
-        <v>94</v>
+        <v>548</v>
       </c>
       <c r="J253" t="s">
-        <v>548</v>
+        <v>246</v>
       </c>
       <c r="K253" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
       <c r="L253" t="s">
         <v>549</v>
@@ -16330,7 +16330,7 @@
         <v>48</v>
       </c>
       <c r="P253" t="s">
-        <v>94</v>
+        <v>548</v>
       </c>
       <c r="Q253" t="s">
         <v>47</v>
@@ -16536,7 +16536,7 @@
         <v>557</v>
       </c>
       <c r="J257" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K257" t="s">
         <v>247</v>
@@ -16872,7 +16872,7 @@
         <v>574</v>
       </c>
       <c r="J263" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K263" t="s">
         <v>247</v>
@@ -16984,7 +16984,7 @@
         <v>574</v>
       </c>
       <c r="J265" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K265" t="s">
         <v>247</v>
@@ -17096,7 +17096,7 @@
         <v>585</v>
       </c>
       <c r="J267" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K267" t="s">
         <v>247</v>
@@ -17152,7 +17152,7 @@
         <v>588</v>
       </c>
       <c r="J268" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K268" t="s">
         <v>247</v>
@@ -17376,7 +17376,7 @@
         <v>601</v>
       </c>
       <c r="J272" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K272" t="s">
         <v>247</v>
@@ -17529,7 +17529,7 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F275" t="s">
         <v>40</v>
@@ -17600,7 +17600,7 @@
         <v>557</v>
       </c>
       <c r="J276" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K276" t="s">
         <v>247</v>
@@ -18210,7 +18210,7 @@
         <v>41</v>
       </c>
       <c r="H287" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I287" t="s">
         <v>635</v>
@@ -18219,7 +18219,7 @@
         <v>636</v>
       </c>
       <c r="K287" t="s">
-        <v>71</v>
+        <v>240</v>
       </c>
       <c r="L287" t="s">
         <v>34</v>
@@ -18266,7 +18266,7 @@
         <v>41</v>
       </c>
       <c r="H288" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="I288" t="s">
         <v>638</v>
@@ -18275,7 +18275,7 @@
         <v>636</v>
       </c>
       <c r="K288" t="s">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="L288" t="s">
         <v>34</v>
@@ -18552,7 +18552,7 @@
         <v>655</v>
       </c>
       <c r="J293" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K293" t="s">
         <v>240</v>
@@ -18832,7 +18832,7 @@
         <v>674</v>
       </c>
       <c r="J298" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K298" t="s">
         <v>247</v>
@@ -19000,7 +19000,7 @@
         <v>686</v>
       </c>
       <c r="J301" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K301" t="s">
         <v>687</v>
@@ -19112,7 +19112,7 @@
         <v>693</v>
       </c>
       <c r="J303" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K303" t="s">
         <v>240</v>
@@ -19227,7 +19227,7 @@
         <v>129</v>
       </c>
       <c r="K305" t="s">
-        <v>71</v>
+        <v>251</v>
       </c>
       <c r="L305" t="s">
         <v>701</v>
@@ -19268,25 +19268,25 @@
         <v>702</v>
       </c>
       <c r="F306" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G306" t="s">
         <v>41</v>
       </c>
       <c r="H306" t="s">
-        <v>42</v>
+        <v>703</v>
       </c>
       <c r="I306" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J306" t="s">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="K306" t="s">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="L306" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M306" t="s">
         <v>697</v>
@@ -19298,7 +19298,7 @@
         <v>48</v>
       </c>
       <c r="P306" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Q306" t="s">
         <v>47</v>
@@ -19321,25 +19321,25 @@
         <v>34</v>
       </c>
       <c r="E307" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F307" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G307" t="s">
         <v>41</v>
       </c>
       <c r="H307" t="s">
-        <v>706</v>
+        <v>42</v>
       </c>
       <c r="I307" t="s">
         <v>707</v>
       </c>
       <c r="J307" t="s">
-        <v>129</v>
+        <v>240</v>
       </c>
       <c r="K307" t="s">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="L307" t="s">
         <v>708</v>
@@ -19398,7 +19398,7 @@
         <v>251</v>
       </c>
       <c r="L308" t="s">
-        <v>712</v>
+        <v>34</v>
       </c>
       <c r="M308" t="s">
         <v>697</v>
@@ -19433,7 +19433,7 @@
         <v>34</v>
       </c>
       <c r="E309" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F309" t="s">
         <v>52</v>
@@ -19442,19 +19442,19 @@
         <v>41</v>
       </c>
       <c r="H309" t="s">
+        <v>713</v>
+      </c>
+      <c r="I309" t="s">
         <v>714</v>
-      </c>
-      <c r="I309" t="s">
-        <v>715</v>
       </c>
       <c r="J309" t="s">
         <v>129</v>
       </c>
       <c r="K309" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="L309" t="s">
-        <v>34</v>
+        <v>715</v>
       </c>
       <c r="M309" t="s">
         <v>697</v>
@@ -19466,7 +19466,7 @@
         <v>48</v>
       </c>
       <c r="P309" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Q309" t="s">
         <v>47</v>
@@ -19560,7 +19560,7 @@
         <v>721</v>
       </c>
       <c r="J311" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K311" t="s">
         <v>247</v>
@@ -19881,7 +19881,7 @@
         <v>34</v>
       </c>
       <c r="E317" t="s">
-        <v>743</v>
+        <v>538</v>
       </c>
       <c r="F317" t="s">
         <v>40</v>
@@ -19893,16 +19893,16 @@
         <v>732</v>
       </c>
       <c r="I317" t="s">
+        <v>743</v>
+      </c>
+      <c r="J317" t="s">
+        <v>246</v>
+      </c>
+      <c r="K317" t="s">
+        <v>82</v>
+      </c>
+      <c r="L317" t="s">
         <v>744</v>
-      </c>
-      <c r="J317" t="s">
-        <v>745</v>
-      </c>
-      <c r="K317" t="s">
-        <v>247</v>
-      </c>
-      <c r="L317" t="s">
-        <v>746</v>
       </c>
       <c r="M317" t="s">
         <v>736</v>
@@ -19914,7 +19914,7 @@
         <v>48</v>
       </c>
       <c r="P317" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="Q317" t="s">
         <v>47</v>
@@ -19937,7 +19937,7 @@
         <v>34</v>
       </c>
       <c r="E318" t="s">
-        <v>538</v>
+        <v>745</v>
       </c>
       <c r="F318" t="s">
         <v>40</v>
@@ -19949,13 +19949,13 @@
         <v>732</v>
       </c>
       <c r="I318" t="s">
+        <v>746</v>
+      </c>
+      <c r="J318" t="s">
         <v>747</v>
       </c>
-      <c r="J318" t="s">
-        <v>246</v>
-      </c>
       <c r="K318" t="s">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="L318" t="s">
         <v>748</v>
@@ -19970,7 +19970,7 @@
         <v>48</v>
       </c>
       <c r="P318" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="Q318" t="s">
         <v>47</v>
@@ -20288,7 +20288,7 @@
         <v>771</v>
       </c>
       <c r="J324" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K324" t="s">
         <v>247</v>
@@ -20568,7 +20568,7 @@
         <v>792</v>
       </c>
       <c r="J329" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="K329" t="s">
         <v>247</v>
@@ -20624,7 +20624,7 @@
         <v>797</v>
       </c>
       <c r="J330" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="K330" t="s">
         <v>247</v>
@@ -20777,7 +20777,7 @@
         <v>33</v>
       </c>
       <c r="E333" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F333" t="s">
         <v>40</v>
@@ -21311,7 +21311,7 @@
         <v>47</v>
       </c>
       <c r="O342" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P342" t="s">
         <v>824</v>
@@ -21703,7 +21703,7 @@
         <v>47</v>
       </c>
       <c r="O349" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P349" t="s">
         <v>832</v>
@@ -21815,7 +21815,7 @@
         <v>47</v>
       </c>
       <c r="O351" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P351" t="s">
         <v>834</v>

--- a/xlsx/dre/DRE_04_2026.xlsx
+++ b/xlsx/dre/DRE_04_2026.xlsx
@@ -1196,33 +1196,33 @@
     <t>FERNANDA DOCHVAT SILVA</t>
   </si>
   <si>
+    <t>R$  404,67</t>
+  </si>
+  <si>
+    <t>01/07/26</t>
+  </si>
+  <si>
+    <t>R$  424,52</t>
+  </si>
+  <si>
     <t>01/06/26</t>
   </si>
   <si>
+    <t>R$  272,80</t>
+  </si>
+  <si>
     <t>Rubens Felipe de Siqueira Costa</t>
   </si>
   <si>
+    <t>R$  401,23</t>
+  </si>
+  <si>
     <t>R$  1.333,58</t>
   </si>
   <si>
     <t>06/02/26</t>
   </si>
   <si>
-    <t>R$  404,67</t>
-  </si>
-  <si>
-    <t>01/07/26</t>
-  </si>
-  <si>
-    <t>R$  424,52</t>
-  </si>
-  <si>
-    <t>R$  401,23</t>
-  </si>
-  <si>
-    <t>R$  272,80</t>
-  </si>
-  <si>
     <t>23801/1</t>
   </si>
   <si>
@@ -1358,24 +1358,24 @@
     <t>4.03.03.01.01 Frete logístico - entrega a clientes</t>
   </si>
   <si>
+    <t>71901UB/0</t>
+  </si>
+  <si>
+    <t>Uber</t>
+  </si>
+  <si>
+    <t>R$  26,75</t>
+  </si>
+  <si>
     <t>ADM UBER/0</t>
   </si>
   <si>
-    <t>Uber</t>
-  </si>
-  <si>
     <t>R$  220,88</t>
   </si>
   <si>
     <t>05/10/26</t>
   </si>
   <si>
-    <t>71901UB/0</t>
-  </si>
-  <si>
-    <t>R$  26,75</t>
-  </si>
-  <si>
     <t>Lalamove/2</t>
   </si>
   <si>
@@ -1397,6 +1397,48 @@
     <t>16/06/26</t>
   </si>
   <si>
+    <t>ADM U/7</t>
+  </si>
+  <si>
+    <t>R$  219,14</t>
+  </si>
+  <si>
+    <t>50503/0</t>
+  </si>
+  <si>
+    <t>R$  62,55</t>
+  </si>
+  <si>
+    <t>50503FABIOTN</t>
+  </si>
+  <si>
+    <t>42701/0</t>
+  </si>
+  <si>
+    <t>R$  17,99</t>
+  </si>
+  <si>
+    <t>42701ERIKA</t>
+  </si>
+  <si>
+    <t>36902/0</t>
+  </si>
+  <si>
+    <t>R$  31,97</t>
+  </si>
+  <si>
+    <t>36902LeticiaOC</t>
+  </si>
+  <si>
+    <t>46401/0</t>
+  </si>
+  <si>
+    <t>R$  12,65</t>
+  </si>
+  <si>
+    <t>33201BRUNALESS</t>
+  </si>
+  <si>
     <t>647/1</t>
   </si>
   <si>
@@ -1406,31 +1448,13 @@
     <t>Recarga</t>
   </si>
   <si>
-    <t>50503/0</t>
-  </si>
-  <si>
-    <t>R$  62,55</t>
-  </si>
-  <si>
-    <t>50503FABIOTN</t>
-  </si>
-  <si>
-    <t>42701/0</t>
-  </si>
-  <si>
-    <t>R$  17,99</t>
-  </si>
-  <si>
-    <t>42701ERIKA</t>
-  </si>
-  <si>
-    <t>46401/0</t>
-  </si>
-  <si>
-    <t>R$  12,65</t>
-  </si>
-  <si>
-    <t>33201BRUNALESS</t>
+    <t>48801/2</t>
+  </si>
+  <si>
+    <t>R$  47,08</t>
+  </si>
+  <si>
+    <t>48801ANACASS</t>
   </si>
   <si>
     <t>45001/0</t>
@@ -1442,30 +1466,6 @@
     <t>45001ANACLARABLA</t>
   </si>
   <si>
-    <t>36902/0</t>
-  </si>
-  <si>
-    <t>R$  31,97</t>
-  </si>
-  <si>
-    <t>36902LeticiaOC</t>
-  </si>
-  <si>
-    <t>48801/2</t>
-  </si>
-  <si>
-    <t>R$  47,08</t>
-  </si>
-  <si>
-    <t>48801ANACASS</t>
-  </si>
-  <si>
-    <t>ADM U/7</t>
-  </si>
-  <si>
-    <t>R$  219,14</t>
-  </si>
-  <si>
     <t>15201/0</t>
   </si>
   <si>
@@ -1481,6 +1481,63 @@
     <t>R$  20,58</t>
   </si>
   <si>
+    <t>45901U/0</t>
+  </si>
+  <si>
+    <t>R$  13,97</t>
+  </si>
+  <si>
+    <t>45901ANAMARIDEO</t>
+  </si>
+  <si>
+    <t>35901/0</t>
+  </si>
+  <si>
+    <t>R$  29,93</t>
+  </si>
+  <si>
+    <t>35901TatianaLF</t>
+  </si>
+  <si>
+    <t>40701/0</t>
+  </si>
+  <si>
+    <t>R$  37,58</t>
+  </si>
+  <si>
+    <t>40701julianMac</t>
+  </si>
+  <si>
+    <t>630/1</t>
+  </si>
+  <si>
+    <t>47101U/0</t>
+  </si>
+  <si>
+    <t>R$  12,92</t>
+  </si>
+  <si>
+    <t>47101MarciaOA</t>
+  </si>
+  <si>
+    <t>46201U/0</t>
+  </si>
+  <si>
+    <t>R$  40,25</t>
+  </si>
+  <si>
+    <t>46201ANGELASC</t>
+  </si>
+  <si>
+    <t>43601U/0</t>
+  </si>
+  <si>
+    <t>R$  58,62</t>
+  </si>
+  <si>
+    <t>43601MICHELLDSP</t>
+  </si>
+  <si>
     <t>49701/0</t>
   </si>
   <si>
@@ -1490,63 +1547,6 @@
     <t>49701GABRIZANC</t>
   </si>
   <si>
-    <t>35901/0</t>
-  </si>
-  <si>
-    <t>R$  29,93</t>
-  </si>
-  <si>
-    <t>35901TatianaLF</t>
-  </si>
-  <si>
-    <t>45901U/0</t>
-  </si>
-  <si>
-    <t>R$  13,97</t>
-  </si>
-  <si>
-    <t>45901ANAMARIDEO</t>
-  </si>
-  <si>
-    <t>40701/0</t>
-  </si>
-  <si>
-    <t>R$  37,58</t>
-  </si>
-  <si>
-    <t>40701julianMac</t>
-  </si>
-  <si>
-    <t>43601U/0</t>
-  </si>
-  <si>
-    <t>R$  58,62</t>
-  </si>
-  <si>
-    <t>43601MICHELLDSP</t>
-  </si>
-  <si>
-    <t>630/1</t>
-  </si>
-  <si>
-    <t>47101U/0</t>
-  </si>
-  <si>
-    <t>R$  12,92</t>
-  </si>
-  <si>
-    <t>47101MarciaOA</t>
-  </si>
-  <si>
-    <t>46201U/0</t>
-  </si>
-  <si>
-    <t>R$  40,25</t>
-  </si>
-  <si>
-    <t>46201ANGELASC</t>
-  </si>
-  <si>
     <t>4.03.03.02 Agregados e outros gastos de montagens</t>
   </si>
   <si>
@@ -1730,6 +1730,93 @@
     <t>Bianca Rodrigues - Salário fixo 2026</t>
   </si>
   <si>
+    <t>Eric Kevin de Souza Serpa</t>
+  </si>
+  <si>
+    <t>19/04/26</t>
+  </si>
+  <si>
+    <t>Salário Fixo -Eric Serpa 2026</t>
+  </si>
+  <si>
+    <t>658/1</t>
+  </si>
+  <si>
+    <t>EFRAIM RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$  1.060,00</t>
+  </si>
+  <si>
+    <t>07/05/26</t>
+  </si>
+  <si>
+    <t>781/1</t>
+  </si>
+  <si>
+    <t>80/4</t>
+  </si>
+  <si>
+    <t>Mayara Silva Martins</t>
+  </si>
+  <si>
+    <t>R$  1.315,60</t>
+  </si>
+  <si>
+    <t>Fixo Mayara</t>
+  </si>
+  <si>
+    <t>CARINA PEREIRA</t>
+  </si>
+  <si>
+    <t>R$  2.090,00</t>
+  </si>
+  <si>
+    <t>Carina - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Rubens - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>Teresinha Elvira Maximino de Menezes</t>
+  </si>
+  <si>
+    <t>Tucha - Fixo 2026</t>
+  </si>
+  <si>
+    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
+  </si>
+  <si>
+    <t>R$  4.422,07</t>
+  </si>
+  <si>
+    <t>Sabrina Braunbeck - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>GUTEMBERG DIAS GOMES</t>
+  </si>
+  <si>
+    <t>R$  7.800,00</t>
+  </si>
+  <si>
+    <t>Gutemberg Dias - Pagamento</t>
+  </si>
+  <si>
+    <t>Denny Lucas do Carmo Pereira</t>
+  </si>
+  <si>
+    <t>R$  2.795,57</t>
+  </si>
+  <si>
+    <t>Denny Lucas - Pagamento 2026</t>
+  </si>
+  <si>
+    <t>12/02/26</t>
+  </si>
+  <si>
+    <t>Fernanda Dochvat - Fixo 2026</t>
+  </si>
+  <si>
     <t>659/1</t>
   </si>
   <si>
@@ -1739,81 +1826,12 @@
     <t>R$  1.287,09</t>
   </si>
   <si>
-    <t>07/05/26</t>
-  </si>
-  <si>
-    <t>12/02/26</t>
-  </si>
-  <si>
-    <t>Fernanda Dochvat - Fixo 2026</t>
-  </si>
-  <si>
     <t>Danielle Martins da Silva</t>
   </si>
   <si>
-    <t>R$  2.090,00</t>
-  </si>
-  <si>
     <t>Danielle - Pagamento 2026</t>
   </si>
   <si>
-    <t>Eric Kevin de Souza Serpa</t>
-  </si>
-  <si>
-    <t>19/04/26</t>
-  </si>
-  <si>
-    <t>Salário Fixo -Eric Serpa 2026</t>
-  </si>
-  <si>
-    <t>CARINA PEREIRA</t>
-  </si>
-  <si>
-    <t>Carina - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>781/1</t>
-  </si>
-  <si>
-    <t>EFRAIM RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$  1.060,00</t>
-  </si>
-  <si>
-    <t>GUTEMBERG DIAS GOMES</t>
-  </si>
-  <si>
-    <t>R$  7.800,00</t>
-  </si>
-  <si>
-    <t>Gutemberg Dias - Pagamento</t>
-  </si>
-  <si>
-    <t>SABRINA ALVES DE ABREU BRAUNBECK</t>
-  </si>
-  <si>
-    <t>R$  4.422,07</t>
-  </si>
-  <si>
-    <t>Sabrina Braunbeck - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>Rubens - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>80/4</t>
-  </si>
-  <si>
-    <t>Mayara Silva Martins</t>
-  </si>
-  <si>
-    <t>R$  1.315,60</t>
-  </si>
-  <si>
-    <t>Fixo Mayara</t>
-  </si>
-  <si>
     <t>627/1</t>
   </si>
   <si>
@@ -1829,18 +1847,6 @@
     <t>17 dias</t>
   </si>
   <si>
-    <t>Denny Lucas do Carmo Pereira</t>
-  </si>
-  <si>
-    <t>R$  2.795,57</t>
-  </si>
-  <si>
-    <t>Denny Lucas - Pagamento 2026</t>
-  </si>
-  <si>
-    <t>658/1</t>
-  </si>
-  <si>
     <t>616/1</t>
   </si>
   <si>
@@ -1857,12 +1863,6 @@
   </si>
   <si>
     <t>Felipe Domingos - salário fixo 2026</t>
-  </si>
-  <si>
-    <t>Teresinha Elvira Maximino de Menezes</t>
-  </si>
-  <si>
-    <t>Tucha - Fixo 2026</t>
   </si>
   <si>
     <t>4.04.01.02.05 IRRF sobre salários</t>
@@ -11929,7 +11929,7 @@
         <v>34</v>
       </c>
       <c r="E175" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F175" t="s">
         <v>183</v>
@@ -11941,13 +11941,13 @@
         <v>388</v>
       </c>
       <c r="I175" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="J175" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K175" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L175" t="s">
         <v>34</v>
@@ -11959,10 +11959,10 @@
         <v>47</v>
       </c>
       <c r="O175" t="s">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="P175" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="Q175" t="s">
         <v>47</v>
@@ -11985,7 +11985,7 @@
         <v>34</v>
       </c>
       <c r="E176" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F176" t="s">
         <v>183</v>
@@ -11997,13 +11997,13 @@
         <v>388</v>
       </c>
       <c r="I176" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="J176" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K176" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="L176" t="s">
         <v>34</v>
@@ -12015,10 +12015,10 @@
         <v>47</v>
       </c>
       <c r="O176" t="s">
-        <v>104</v>
+        <v>287</v>
       </c>
       <c r="P176" t="s">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="Q176" t="s">
         <v>47</v>
@@ -12041,7 +12041,7 @@
         <v>34</v>
       </c>
       <c r="E177" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F177" t="s">
         <v>183</v>
@@ -12053,13 +12053,13 @@
         <v>388</v>
       </c>
       <c r="I177" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="J177" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K177" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L177" t="s">
         <v>34</v>
@@ -12071,10 +12071,10 @@
         <v>47</v>
       </c>
       <c r="O177" t="s">
-        <v>213</v>
+        <v>120</v>
       </c>
       <c r="P177" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="Q177" t="s">
         <v>47</v>
@@ -12097,7 +12097,7 @@
         <v>34</v>
       </c>
       <c r="E178" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F178" t="s">
         <v>183</v>
@@ -12106,16 +12106,16 @@
         <v>41</v>
       </c>
       <c r="H178" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="I178" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="J178" t="s">
         <v>392</v>
       </c>
       <c r="K178" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="L178" t="s">
         <v>34</v>
@@ -12127,10 +12127,10 @@
         <v>47</v>
       </c>
       <c r="O178" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="P178" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="Q178" t="s">
         <v>47</v>
@@ -12153,7 +12153,7 @@
         <v>34</v>
       </c>
       <c r="E179" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F179" t="s">
         <v>183</v>
@@ -12165,13 +12165,13 @@
         <v>388</v>
       </c>
       <c r="I179" t="s">
-        <v>393</v>
+        <v>346</v>
       </c>
       <c r="J179" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="K179" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L179" t="s">
         <v>34</v>
@@ -12183,10 +12183,10 @@
         <v>47</v>
       </c>
       <c r="O179" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="P179" t="s">
-        <v>393</v>
+        <v>346</v>
       </c>
       <c r="Q179" t="s">
         <v>47</v>
@@ -12209,7 +12209,7 @@
         <v>34</v>
       </c>
       <c r="E180" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F180" t="s">
         <v>183</v>
@@ -12221,13 +12221,13 @@
         <v>388</v>
       </c>
       <c r="I180" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J180" t="s">
-        <v>394</v>
+        <v>129</v>
       </c>
       <c r="K180" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="L180" t="s">
         <v>34</v>
@@ -12239,10 +12239,10 @@
         <v>47</v>
       </c>
       <c r="O180" t="s">
-        <v>287</v>
+        <v>72</v>
       </c>
       <c r="P180" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q180" t="s">
         <v>47</v>
@@ -12274,10 +12274,10 @@
         <v>41</v>
       </c>
       <c r="H181" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I181" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J181" t="s">
         <v>129</v>
@@ -12298,7 +12298,7 @@
         <v>77</v>
       </c>
       <c r="P181" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Q181" t="s">
         <v>47</v>
@@ -12321,7 +12321,7 @@
         <v>34</v>
       </c>
       <c r="E182" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F182" t="s">
         <v>183</v>
@@ -12330,16 +12330,16 @@
         <v>41</v>
       </c>
       <c r="H182" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="I182" t="s">
+        <v>396</v>
+      </c>
+      <c r="J182" t="s">
         <v>397</v>
       </c>
-      <c r="J182" t="s">
-        <v>129</v>
-      </c>
       <c r="K182" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="L182" t="s">
         <v>34</v>
@@ -12351,10 +12351,10 @@
         <v>47</v>
       </c>
       <c r="O182" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="P182" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Q182" t="s">
         <v>47</v>
@@ -12386,7 +12386,7 @@
         <v>41</v>
       </c>
       <c r="H183" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I183" t="s">
         <v>399</v>
@@ -12896,7 +12896,7 @@
         <v>421</v>
       </c>
       <c r="J192" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="K192" t="s">
         <v>125</v>
@@ -12952,7 +12952,7 @@
         <v>419</v>
       </c>
       <c r="J193" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="K193" t="s">
         <v>125</v>
@@ -13624,10 +13624,10 @@
         <v>445</v>
       </c>
       <c r="J205" t="s">
-        <v>446</v>
+        <v>83</v>
       </c>
       <c r="K205" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="L205" t="s">
         <v>34</v>
@@ -13639,7 +13639,7 @@
         <v>47</v>
       </c>
       <c r="O205" t="s">
-        <v>48</v>
+        <v>292</v>
       </c>
       <c r="P205" t="s">
         <v>445</v>
@@ -13665,7 +13665,7 @@
         <v>34</v>
       </c>
       <c r="E206" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F206" t="s">
         <v>52</v>
@@ -13677,13 +13677,13 @@
         <v>444</v>
       </c>
       <c r="I206" t="s">
+        <v>447</v>
+      </c>
+      <c r="J206" t="s">
         <v>448</v>
       </c>
-      <c r="J206" t="s">
-        <v>83</v>
-      </c>
       <c r="K206" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="L206" t="s">
         <v>34</v>
@@ -13695,10 +13695,10 @@
         <v>47</v>
       </c>
       <c r="O206" t="s">
-        <v>292</v>
+        <v>48</v>
       </c>
       <c r="P206" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Q206" t="s">
         <v>47</v>
@@ -13954,19 +13954,19 @@
         <v>41</v>
       </c>
       <c r="H211" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I211" t="s">
         <v>457</v>
       </c>
       <c r="J211" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="K211" t="s">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="L211" t="s">
-        <v>458</v>
+        <v>34</v>
       </c>
       <c r="M211" t="s">
         <v>442</v>
@@ -14001,7 +14001,7 @@
         <v>34</v>
       </c>
       <c r="E212" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F212" t="s">
         <v>52</v>
@@ -14013,7 +14013,7 @@
         <v>444</v>
       </c>
       <c r="I212" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J212" t="s">
         <v>119</v>
@@ -14031,10 +14031,10 @@
         <v>47</v>
       </c>
       <c r="O212" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P212" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q212" t="s">
         <v>47</v>
@@ -14057,7 +14057,7 @@
         <v>34</v>
       </c>
       <c r="E213" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F213" t="s">
         <v>52</v>
@@ -14069,7 +14069,7 @@
         <v>444</v>
       </c>
       <c r="I213" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J213" t="s">
         <v>119</v>
@@ -14087,10 +14087,10 @@
         <v>47</v>
       </c>
       <c r="O213" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P213" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q213" t="s">
         <v>47</v>
@@ -14113,7 +14113,7 @@
         <v>34</v>
       </c>
       <c r="E214" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F214" t="s">
         <v>52</v>
@@ -14125,7 +14125,7 @@
         <v>444</v>
       </c>
       <c r="I214" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J214" t="s">
         <v>119</v>
@@ -14143,10 +14143,10 @@
         <v>47</v>
       </c>
       <c r="O214" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P214" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Q214" t="s">
         <v>47</v>
@@ -14169,7 +14169,7 @@
         <v>34</v>
       </c>
       <c r="E215" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F215" t="s">
         <v>52</v>
@@ -14181,7 +14181,7 @@
         <v>444</v>
       </c>
       <c r="I215" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J215" t="s">
         <v>119</v>
@@ -14199,10 +14199,10 @@
         <v>47</v>
       </c>
       <c r="O215" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P215" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Q215" t="s">
         <v>47</v>
@@ -14225,7 +14225,7 @@
         <v>34</v>
       </c>
       <c r="E216" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F216" t="s">
         <v>52</v>
@@ -14234,19 +14234,19 @@
         <v>41</v>
       </c>
       <c r="H216" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="I216" t="s">
+        <v>471</v>
+      </c>
+      <c r="J216" t="s">
+        <v>129</v>
+      </c>
+      <c r="K216" t="s">
+        <v>251</v>
+      </c>
+      <c r="L216" t="s">
         <v>472</v>
-      </c>
-      <c r="J216" t="s">
-        <v>119</v>
-      </c>
-      <c r="K216" t="s">
-        <v>119</v>
-      </c>
-      <c r="L216" t="s">
-        <v>34</v>
       </c>
       <c r="M216" t="s">
         <v>442</v>
@@ -14255,10 +14255,10 @@
         <v>47</v>
       </c>
       <c r="O216" t="s">
-        <v>473</v>
+        <v>48</v>
       </c>
       <c r="P216" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q216" t="s">
         <v>47</v>
@@ -14281,7 +14281,7 @@
         <v>34</v>
       </c>
       <c r="E217" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F217" t="s">
         <v>52</v>
@@ -14293,7 +14293,7 @@
         <v>444</v>
       </c>
       <c r="I217" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J217" t="s">
         <v>119</v>
@@ -14311,10 +14311,10 @@
         <v>47</v>
       </c>
       <c r="O217" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="P217" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q217" t="s">
         <v>47</v>
@@ -14337,7 +14337,7 @@
         <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F218" t="s">
         <v>52</v>
@@ -14349,7 +14349,7 @@
         <v>444</v>
       </c>
       <c r="I218" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J218" t="s">
         <v>119</v>
@@ -14367,10 +14367,10 @@
         <v>47</v>
       </c>
       <c r="O218" t="s">
-        <v>48</v>
+        <v>478</v>
       </c>
       <c r="P218" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q218" t="s">
         <v>47</v>
@@ -14479,7 +14479,7 @@
         <v>47</v>
       </c>
       <c r="O220" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="P220" t="s">
         <v>483</v>
@@ -14685,7 +14685,7 @@
         <v>444</v>
       </c>
       <c r="I224" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="J224" t="s">
         <v>119</v>
@@ -14703,10 +14703,10 @@
         <v>47</v>
       </c>
       <c r="O224" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="P224" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="Q224" t="s">
         <v>47</v>
@@ -14729,7 +14729,7 @@
         <v>34</v>
       </c>
       <c r="E225" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F225" t="s">
         <v>52</v>
@@ -14741,7 +14741,7 @@
         <v>444</v>
       </c>
       <c r="I225" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J225" t="s">
         <v>119</v>
@@ -14759,10 +14759,10 @@
         <v>47</v>
       </c>
       <c r="O225" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="P225" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Q225" t="s">
         <v>47</v>
@@ -14785,7 +14785,7 @@
         <v>34</v>
       </c>
       <c r="E226" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F226" t="s">
         <v>52</v>
@@ -14797,7 +14797,7 @@
         <v>444</v>
       </c>
       <c r="I226" t="s">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="J226" t="s">
         <v>119</v>
@@ -14815,10 +14815,10 @@
         <v>47</v>
       </c>
       <c r="O226" t="s">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="P226" t="s">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="Q226" t="s">
         <v>47</v>
@@ -16745,28 +16745,28 @@
         <v>34</v>
       </c>
       <c r="E261" t="s">
+        <v>136</v>
+      </c>
+      <c r="F261" t="s">
+        <v>40</v>
+      </c>
+      <c r="G261" t="s">
+        <v>41</v>
+      </c>
+      <c r="H261" t="s">
         <v>567</v>
       </c>
-      <c r="F261" t="s">
-        <v>52</v>
-      </c>
-      <c r="G261" t="s">
-        <v>41</v>
-      </c>
-      <c r="H261" t="s">
+      <c r="I261" t="s">
+        <v>564</v>
+      </c>
+      <c r="J261" t="s">
+        <v>565</v>
+      </c>
+      <c r="K261" t="s">
         <v>568</v>
       </c>
-      <c r="I261" t="s">
+      <c r="L261" t="s">
         <v>569</v>
-      </c>
-      <c r="J261" t="s">
-        <v>570</v>
-      </c>
-      <c r="K261" t="s">
-        <v>119</v>
-      </c>
-      <c r="L261" t="s">
-        <v>34</v>
       </c>
       <c r="M261" t="s">
         <v>563</v>
@@ -16778,7 +16778,7 @@
         <v>48</v>
       </c>
       <c r="P261" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="Q261" t="s">
         <v>47</v>
@@ -16801,28 +16801,28 @@
         <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>136</v>
+        <v>570</v>
       </c>
       <c r="F262" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G262" t="s">
         <v>41</v>
       </c>
       <c r="H262" t="s">
-        <v>388</v>
+        <v>571</v>
       </c>
       <c r="I262" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="J262" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K262" t="s">
-        <v>247</v>
+        <v>124</v>
       </c>
       <c r="L262" t="s">
-        <v>572</v>
+        <v>34</v>
       </c>
       <c r="M262" t="s">
         <v>563</v>
@@ -16834,7 +16834,7 @@
         <v>48</v>
       </c>
       <c r="P262" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="Q262" t="s">
         <v>47</v>
@@ -16857,28 +16857,28 @@
         <v>34</v>
       </c>
       <c r="E263" t="s">
-        <v>538</v>
+        <v>574</v>
       </c>
       <c r="F263" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G263" t="s">
         <v>41</v>
       </c>
       <c r="H263" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="I263" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J263" t="s">
-        <v>541</v>
+        <v>226</v>
       </c>
       <c r="K263" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="L263" t="s">
-        <v>575</v>
+        <v>34</v>
       </c>
       <c r="M263" t="s">
         <v>563</v>
@@ -16890,7 +16890,7 @@
         <v>48</v>
       </c>
       <c r="P263" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="Q263" t="s">
         <v>47</v>
@@ -16913,7 +16913,7 @@
         <v>34</v>
       </c>
       <c r="E264" t="s">
-        <v>136</v>
+        <v>575</v>
       </c>
       <c r="F264" t="s">
         <v>40</v>
@@ -16925,13 +16925,13 @@
         <v>576</v>
       </c>
       <c r="I264" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="J264" t="s">
-        <v>565</v>
+        <v>240</v>
       </c>
       <c r="K264" t="s">
-        <v>577</v>
+        <v>240</v>
       </c>
       <c r="L264" t="s">
         <v>578</v>
@@ -16946,7 +16946,7 @@
         <v>48</v>
       </c>
       <c r="P264" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="Q264" t="s">
         <v>47</v>
@@ -16981,7 +16981,7 @@
         <v>579</v>
       </c>
       <c r="I265" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="J265" t="s">
         <v>541</v>
@@ -16990,7 +16990,7 @@
         <v>247</v>
       </c>
       <c r="L265" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M265" t="s">
         <v>563</v>
@@ -17002,7 +17002,7 @@
         <v>48</v>
       </c>
       <c r="P265" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="Q265" t="s">
         <v>47</v>
@@ -17025,28 +17025,28 @@
         <v>34</v>
       </c>
       <c r="E266" t="s">
-        <v>581</v>
+        <v>538</v>
       </c>
       <c r="F266" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G266" t="s">
         <v>41</v>
       </c>
       <c r="H266" t="s">
+        <v>394</v>
+      </c>
+      <c r="I266" t="s">
+        <v>557</v>
+      </c>
+      <c r="J266" t="s">
+        <v>246</v>
+      </c>
+      <c r="K266" t="s">
+        <v>247</v>
+      </c>
+      <c r="L266" t="s">
         <v>582</v>
-      </c>
-      <c r="I266" t="s">
-        <v>583</v>
-      </c>
-      <c r="J266" t="s">
-        <v>226</v>
-      </c>
-      <c r="K266" t="s">
-        <v>240</v>
-      </c>
-      <c r="L266" t="s">
-        <v>34</v>
       </c>
       <c r="M266" t="s">
         <v>563</v>
@@ -17058,7 +17058,7 @@
         <v>48</v>
       </c>
       <c r="P266" t="s">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="Q266" t="s">
         <v>47</v>
@@ -17090,10 +17090,10 @@
         <v>41</v>
       </c>
       <c r="H267" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="I267" t="s">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="J267" t="s">
         <v>541</v>
@@ -17102,7 +17102,7 @@
         <v>247</v>
       </c>
       <c r="L267" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M267" t="s">
         <v>563</v>
@@ -17114,7 +17114,7 @@
         <v>48</v>
       </c>
       <c r="P267" t="s">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="Q267" t="s">
         <v>47</v>
@@ -17146,10 +17146,10 @@
         <v>41</v>
       </c>
       <c r="H268" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I268" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="J268" t="s">
         <v>541</v>
@@ -17158,7 +17158,7 @@
         <v>247</v>
       </c>
       <c r="L268" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="M268" t="s">
         <v>563</v>
@@ -17170,7 +17170,7 @@
         <v>48</v>
       </c>
       <c r="P268" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Q268" t="s">
         <v>47</v>
@@ -17202,13 +17202,13 @@
         <v>41</v>
       </c>
       <c r="H269" t="s">
-        <v>390</v>
+        <v>588</v>
       </c>
       <c r="I269" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="J269" t="s">
-        <v>246</v>
+        <v>541</v>
       </c>
       <c r="K269" t="s">
         <v>247</v>
@@ -17226,7 +17226,7 @@
         <v>48</v>
       </c>
       <c r="P269" t="s">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="Q269" t="s">
         <v>47</v>
@@ -17249,7 +17249,7 @@
         <v>34</v>
       </c>
       <c r="E270" t="s">
-        <v>591</v>
+        <v>538</v>
       </c>
       <c r="F270" t="s">
         <v>40</v>
@@ -17258,19 +17258,19 @@
         <v>41</v>
       </c>
       <c r="H270" t="s">
+        <v>591</v>
+      </c>
+      <c r="I270" t="s">
         <v>592</v>
       </c>
-      <c r="I270" t="s">
+      <c r="J270" t="s">
+        <v>541</v>
+      </c>
+      <c r="K270" t="s">
+        <v>247</v>
+      </c>
+      <c r="L270" t="s">
         <v>593</v>
-      </c>
-      <c r="J270" t="s">
-        <v>240</v>
-      </c>
-      <c r="K270" t="s">
-        <v>240</v>
-      </c>
-      <c r="L270" t="s">
-        <v>594</v>
       </c>
       <c r="M270" t="s">
         <v>563</v>
@@ -17282,7 +17282,7 @@
         <v>48</v>
       </c>
       <c r="P270" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q270" t="s">
         <v>47</v>
@@ -17305,28 +17305,28 @@
         <v>34</v>
       </c>
       <c r="E271" t="s">
+        <v>136</v>
+      </c>
+      <c r="F271" t="s">
+        <v>40</v>
+      </c>
+      <c r="G271" t="s">
+        <v>41</v>
+      </c>
+      <c r="H271" t="s">
+        <v>388</v>
+      </c>
+      <c r="I271" t="s">
+        <v>557</v>
+      </c>
+      <c r="J271" t="s">
+        <v>594</v>
+      </c>
+      <c r="K271" t="s">
+        <v>247</v>
+      </c>
+      <c r="L271" t="s">
         <v>595</v>
-      </c>
-      <c r="F271" t="s">
-        <v>52</v>
-      </c>
-      <c r="G271" t="s">
-        <v>41</v>
-      </c>
-      <c r="H271" t="s">
-        <v>596</v>
-      </c>
-      <c r="I271" t="s">
-        <v>597</v>
-      </c>
-      <c r="J271" t="s">
-        <v>598</v>
-      </c>
-      <c r="K271" t="s">
-        <v>598</v>
-      </c>
-      <c r="L271" t="s">
-        <v>599</v>
       </c>
       <c r="M271" t="s">
         <v>563</v>
@@ -17338,7 +17338,7 @@
         <v>48</v>
       </c>
       <c r="P271" t="s">
-        <v>597</v>
+        <v>557</v>
       </c>
       <c r="Q271" t="s">
         <v>47</v>
@@ -17361,28 +17361,28 @@
         <v>34</v>
       </c>
       <c r="E272" t="s">
-        <v>538</v>
+        <v>596</v>
       </c>
       <c r="F272" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G272" t="s">
         <v>41</v>
       </c>
       <c r="H272" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="I272" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="J272" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="K272" t="s">
-        <v>247</v>
+        <v>119</v>
       </c>
       <c r="L272" t="s">
-        <v>602</v>
+        <v>34</v>
       </c>
       <c r="M272" t="s">
         <v>563</v>
@@ -17394,7 +17394,7 @@
         <v>48</v>
       </c>
       <c r="P272" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="Q272" t="s">
         <v>47</v>
@@ -17417,28 +17417,28 @@
         <v>34</v>
       </c>
       <c r="E273" t="s">
-        <v>603</v>
+        <v>538</v>
       </c>
       <c r="F273" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G273" t="s">
         <v>41</v>
       </c>
       <c r="H273" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="I273" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="J273" t="s">
-        <v>570</v>
+        <v>541</v>
       </c>
       <c r="K273" t="s">
-        <v>124</v>
+        <v>247</v>
       </c>
       <c r="L273" t="s">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="M273" t="s">
         <v>563</v>
@@ -17450,7 +17450,7 @@
         <v>48</v>
       </c>
       <c r="P273" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="Q273" t="s">
         <v>47</v>
@@ -17473,7 +17473,7 @@
         <v>34</v>
       </c>
       <c r="E274" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F274" t="s">
         <v>52</v>
@@ -17482,19 +17482,19 @@
         <v>41</v>
       </c>
       <c r="H274" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="I274" t="s">
+        <v>603</v>
+      </c>
+      <c r="J274" t="s">
+        <v>604</v>
+      </c>
+      <c r="K274" t="s">
+        <v>604</v>
+      </c>
+      <c r="L274" t="s">
         <v>605</v>
-      </c>
-      <c r="J274" t="s">
-        <v>60</v>
-      </c>
-      <c r="K274" t="s">
-        <v>56</v>
-      </c>
-      <c r="L274" t="s">
-        <v>606</v>
       </c>
       <c r="M274" t="s">
         <v>563</v>
@@ -17506,7 +17506,7 @@
         <v>48</v>
       </c>
       <c r="P274" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q274" t="s">
         <v>47</v>
@@ -17529,28 +17529,28 @@
         <v>34</v>
       </c>
       <c r="E275" t="s">
-        <v>543</v>
+        <v>606</v>
       </c>
       <c r="F275" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G275" t="s">
         <v>41</v>
       </c>
       <c r="H275" t="s">
-        <v>336</v>
+        <v>585</v>
       </c>
       <c r="I275" t="s">
         <v>607</v>
       </c>
       <c r="J275" t="s">
+        <v>60</v>
+      </c>
+      <c r="K275" t="s">
+        <v>56</v>
+      </c>
+      <c r="L275" t="s">
         <v>608</v>
-      </c>
-      <c r="K275" t="s">
-        <v>247</v>
-      </c>
-      <c r="L275" t="s">
-        <v>609</v>
       </c>
       <c r="M275" t="s">
         <v>563</v>
@@ -17585,7 +17585,7 @@
         <v>34</v>
       </c>
       <c r="E276" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="F276" t="s">
         <v>40</v>
@@ -17594,13 +17594,13 @@
         <v>41</v>
       </c>
       <c r="H276" t="s">
+        <v>336</v>
+      </c>
+      <c r="I276" t="s">
+        <v>609</v>
+      </c>
+      <c r="J276" t="s">
         <v>610</v>
-      </c>
-      <c r="I276" t="s">
-        <v>557</v>
-      </c>
-      <c r="J276" t="s">
-        <v>541</v>
       </c>
       <c r="K276" t="s">
         <v>247</v>
@@ -17618,7 +17618,7 @@
         <v>48</v>
       </c>
       <c r="P276" t="s">
-        <v>557</v>
+        <v>609</v>
       </c>
       <c r="Q276" t="s">
         <v>47</v>
@@ -20456,7 +20456,7 @@
         <v>784</v>
       </c>
       <c r="J327" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="K327" t="s">
         <v>124</v>
